--- a/3_TAI_LIEU/MAU_NHAP_HANG_LOAT/Mau_nhap_PO_doanh_thu.xlsx
+++ b/3_TAI_LIEU/MAU_NHAP_HANG_LOAT/Mau_nhap_PO_doanh_thu.xlsx
@@ -158,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -183,9 +183,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
@@ -245,7 +242,7 @@
     <tabColor rgb="FF0F766E"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L504"/>
+  <dimension ref="A1:M504"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -257,9 +254,10 @@
     <col min="7" max="7" width="24" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -279,6 +277,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
     </row>
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -297,6 +296,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -319,6 +319,7 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -363,22 +364,27 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SL container</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
+          <t xml:space="preserve">SL (số lượng)</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Số tiền trước thuế *</t>
         </is>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="L4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Thuế</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thu hộ (1/0)</t>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chi hộ (1/0)</t>
         </is>
       </c>
     </row>
@@ -391,10 +397,11 @@
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="9"/>
       <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
     </row>
     <row r="6">
       <c r="A6" s="8"/>
@@ -405,10 +412,11 @@
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="9"/>
       <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
     </row>
     <row r="7">
       <c r="A7" s="8"/>
@@ -419,10 +427,11 @@
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="9"/>
       <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
     </row>
     <row r="8">
       <c r="A8" s="8"/>
@@ -433,10 +442,11 @@
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="9"/>
       <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
     </row>
     <row r="9">
       <c r="A9" s="8"/>
@@ -447,10 +457,11 @@
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="9"/>
       <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
     </row>
     <row r="10">
       <c r="A10" s="8"/>
@@ -461,10 +472,11 @@
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="9"/>
       <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
     </row>
     <row r="11">
       <c r="A11" s="8"/>
@@ -475,10 +487,11 @@
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="9"/>
       <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
     </row>
     <row r="12">
       <c r="A12" s="8"/>
@@ -489,10 +502,11 @@
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="9"/>
       <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
     </row>
     <row r="13">
       <c r="A13" s="8"/>
@@ -503,10 +517,11 @@
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="9"/>
       <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
     </row>
     <row r="14">
       <c r="A14" s="8"/>
@@ -517,10 +532,11 @@
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="9"/>
       <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
     </row>
     <row r="15">
       <c r="A15" s="8"/>
@@ -531,10 +547,11 @@
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="9"/>
       <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
     </row>
     <row r="16">
       <c r="A16" s="8"/>
@@ -545,10 +562,11 @@
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="9"/>
       <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
     </row>
     <row r="17">
       <c r="A17" s="8"/>
@@ -559,10 +577,11 @@
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="9"/>
       <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
     </row>
     <row r="18">
       <c r="A18" s="8"/>
@@ -573,10 +592,11 @@
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="9"/>
       <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
     </row>
     <row r="19">
       <c r="A19" s="8"/>
@@ -587,10 +607,11 @@
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="9"/>
       <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
     </row>
     <row r="20">
       <c r="A20" s="8"/>
@@ -601,10 +622,11 @@
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="9"/>
       <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
     </row>
     <row r="21">
       <c r="A21" s="8"/>
@@ -615,10 +637,11 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="9"/>
       <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
     </row>
     <row r="22">
       <c r="A22" s="8"/>
@@ -629,10 +652,11 @@
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="9"/>
       <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
     </row>
     <row r="23">
       <c r="A23" s="8"/>
@@ -643,10 +667,11 @@
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="9"/>
       <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
     </row>
     <row r="24">
       <c r="A24" s="8"/>
@@ -657,10 +682,11 @@
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="9"/>
       <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
     </row>
     <row r="25">
       <c r="A25" s="8"/>
@@ -671,10 +697,11 @@
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="9"/>
       <c r="L25" s="8"/>
+      <c r="M25" s="8"/>
     </row>
     <row r="26">
       <c r="A26" s="8"/>
@@ -685,10 +712,11 @@
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="9"/>
       <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
     </row>
     <row r="27">
       <c r="A27" s="8"/>
@@ -699,10 +727,11 @@
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="9"/>
       <c r="L27" s="8"/>
+      <c r="M27" s="8"/>
     </row>
     <row r="28">
       <c r="A28" s="8"/>
@@ -713,10 +742,11 @@
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="9"/>
       <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
     </row>
     <row r="29">
       <c r="A29" s="8"/>
@@ -727,10 +757,11 @@
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="9"/>
       <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
     </row>
     <row r="30">
       <c r="A30" s="8"/>
@@ -741,10 +772,11 @@
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="9"/>
       <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
     </row>
     <row r="31">
       <c r="A31" s="8"/>
@@ -755,10 +787,11 @@
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="9"/>
       <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
     </row>
     <row r="32">
       <c r="A32" s="8"/>
@@ -769,10 +802,11 @@
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="9"/>
       <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
     </row>
     <row r="33">
       <c r="A33" s="8"/>
@@ -783,10 +817,11 @@
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="9"/>
       <c r="L33" s="8"/>
+      <c r="M33" s="8"/>
     </row>
     <row r="34">
       <c r="A34" s="8"/>
@@ -797,10 +832,11 @@
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="9"/>
       <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
     </row>
     <row r="35">
       <c r="A35" s="8"/>
@@ -811,10 +847,11 @@
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
-      <c r="I35" s="9"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="8"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="9"/>
       <c r="L35" s="8"/>
+      <c r="M35" s="8"/>
     </row>
     <row r="36">
       <c r="A36" s="8"/>
@@ -825,10 +862,11 @@
       <c r="F36" s="8"/>
       <c r="G36" s="8"/>
       <c r="H36" s="8"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="9"/>
       <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
     </row>
     <row r="37">
       <c r="A37" s="8"/>
@@ -839,10 +877,11 @@
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
       <c r="H37" s="8"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="9"/>
       <c r="L37" s="8"/>
+      <c r="M37" s="8"/>
     </row>
     <row r="38">
       <c r="A38" s="8"/>
@@ -853,10 +892,11 @@
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
       <c r="H38" s="8"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="9"/>
       <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
     </row>
     <row r="39">
       <c r="A39" s="8"/>
@@ -867,10 +907,11 @@
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="9"/>
       <c r="L39" s="8"/>
+      <c r="M39" s="8"/>
     </row>
     <row r="40">
       <c r="A40" s="8"/>
@@ -881,10 +922,11 @@
       <c r="F40" s="8"/>
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="9"/>
       <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
     </row>
     <row r="41">
       <c r="A41" s="8"/>
@@ -895,10 +937,11 @@
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="8"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="9"/>
       <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
     </row>
     <row r="42">
       <c r="A42" s="8"/>
@@ -909,10 +952,11 @@
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="9"/>
       <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
     </row>
     <row r="43">
       <c r="A43" s="8"/>
@@ -923,10 +967,11 @@
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="9"/>
       <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
     </row>
     <row r="44">
       <c r="A44" s="8"/>
@@ -937,10 +982,11 @@
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="9"/>
       <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
     </row>
     <row r="45">
       <c r="A45" s="8"/>
@@ -951,10 +997,11 @@
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="8"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="9"/>
       <c r="L45" s="8"/>
+      <c r="M45" s="8"/>
     </row>
     <row r="46">
       <c r="A46" s="8"/>
@@ -965,10 +1012,11 @@
       <c r="F46" s="8"/>
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
-      <c r="I46" s="9"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="9"/>
       <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
     </row>
     <row r="47">
       <c r="A47" s="8"/>
@@ -979,10 +1027,11 @@
       <c r="F47" s="8"/>
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
-      <c r="I47" s="9"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="8"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="9"/>
       <c r="L47" s="8"/>
+      <c r="M47" s="8"/>
     </row>
     <row r="48">
       <c r="A48" s="8"/>
@@ -993,10 +1042,11 @@
       <c r="F48" s="8"/>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
-      <c r="I48" s="9"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="9"/>
       <c r="L48" s="8"/>
+      <c r="M48" s="8"/>
     </row>
     <row r="49">
       <c r="A49" s="8"/>
@@ -1007,10 +1057,11 @@
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
-      <c r="I49" s="9"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="8"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="9"/>
       <c r="L49" s="8"/>
+      <c r="M49" s="8"/>
     </row>
     <row r="50">
       <c r="A50" s="8"/>
@@ -1021,10 +1072,11 @@
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
-      <c r="I50" s="9"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="9"/>
       <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
     </row>
     <row r="51">
       <c r="A51" s="8"/>
@@ -1035,10 +1087,11 @@
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
-      <c r="I51" s="9"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="9"/>
       <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
     </row>
     <row r="52">
       <c r="A52" s="8"/>
@@ -1049,10 +1102,11 @@
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
-      <c r="I52" s="9"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="9"/>
       <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
     </row>
     <row r="53">
       <c r="A53" s="8"/>
@@ -1063,10 +1117,11 @@
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
-      <c r="I53" s="9"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="9"/>
       <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
     </row>
     <row r="54">
       <c r="A54" s="8"/>
@@ -1077,10 +1132,11 @@
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
-      <c r="I54" s="9"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="9"/>
       <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
     </row>
     <row r="55">
       <c r="A55" s="8"/>
@@ -1091,10 +1147,11 @@
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="9"/>
       <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
     </row>
     <row r="56">
       <c r="A56" s="8"/>
@@ -1105,10 +1162,11 @@
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="8"/>
+      <c r="I56" s="8"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="9"/>
       <c r="L56" s="8"/>
+      <c r="M56" s="8"/>
     </row>
     <row r="57">
       <c r="A57" s="8"/>
@@ -1119,10 +1177,11 @@
       <c r="F57" s="8"/>
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
-      <c r="I57" s="9"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="8"/>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="9"/>
       <c r="L57" s="8"/>
+      <c r="M57" s="8"/>
     </row>
     <row r="58">
       <c r="A58" s="8"/>
@@ -1133,10 +1192,11 @@
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
-      <c r="I58" s="9"/>
-      <c r="J58" s="10"/>
-      <c r="K58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="9"/>
       <c r="L58" s="8"/>
+      <c r="M58" s="8"/>
     </row>
     <row r="59">
       <c r="A59" s="8"/>
@@ -1147,10 +1207,11 @@
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
-      <c r="I59" s="9"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="9"/>
       <c r="L59" s="8"/>
+      <c r="M59" s="8"/>
     </row>
     <row r="60">
       <c r="A60" s="8"/>
@@ -1161,10 +1222,11 @@
       <c r="F60" s="8"/>
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
-      <c r="I60" s="9"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="8"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="9"/>
       <c r="L60" s="8"/>
+      <c r="M60" s="8"/>
     </row>
     <row r="61">
       <c r="A61" s="8"/>
@@ -1175,10 +1237,11 @@
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
-      <c r="I61" s="9"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="8"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="9"/>
       <c r="L61" s="8"/>
+      <c r="M61" s="8"/>
     </row>
     <row r="62">
       <c r="A62" s="8"/>
@@ -1189,10 +1252,11 @@
       <c r="F62" s="8"/>
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
-      <c r="I62" s="9"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="9"/>
       <c r="L62" s="8"/>
+      <c r="M62" s="8"/>
     </row>
     <row r="63">
       <c r="A63" s="8"/>
@@ -1203,10 +1267,11 @@
       <c r="F63" s="8"/>
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
-      <c r="I63" s="9"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="8"/>
+      <c r="I63" s="8"/>
+      <c r="J63" s="8"/>
+      <c r="K63" s="9"/>
       <c r="L63" s="8"/>
+      <c r="M63" s="8"/>
     </row>
     <row r="64">
       <c r="A64" s="8"/>
@@ -1217,10 +1282,11 @@
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
       <c r="H64" s="8"/>
-      <c r="I64" s="9"/>
-      <c r="J64" s="10"/>
-      <c r="K64" s="8"/>
+      <c r="I64" s="8"/>
+      <c r="J64" s="8"/>
+      <c r="K64" s="9"/>
       <c r="L64" s="8"/>
+      <c r="M64" s="8"/>
     </row>
     <row r="65">
       <c r="A65" s="8"/>
@@ -1231,10 +1297,11 @@
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
-      <c r="I65" s="9"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="8"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="9"/>
       <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
     </row>
     <row r="66">
       <c r="A66" s="8"/>
@@ -1245,10 +1312,11 @@
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
       <c r="H66" s="8"/>
-      <c r="I66" s="9"/>
-      <c r="J66" s="10"/>
-      <c r="K66" s="8"/>
+      <c r="I66" s="8"/>
+      <c r="J66" s="8"/>
+      <c r="K66" s="9"/>
       <c r="L66" s="8"/>
+      <c r="M66" s="8"/>
     </row>
     <row r="67">
       <c r="A67" s="8"/>
@@ -1259,10 +1327,11 @@
       <c r="F67" s="8"/>
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
-      <c r="I67" s="9"/>
-      <c r="J67" s="10"/>
-      <c r="K67" s="8"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="9"/>
       <c r="L67" s="8"/>
+      <c r="M67" s="8"/>
     </row>
     <row r="68">
       <c r="A68" s="8"/>
@@ -1273,10 +1342,11 @@
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
-      <c r="I68" s="9"/>
-      <c r="J68" s="10"/>
-      <c r="K68" s="8"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="9"/>
       <c r="L68" s="8"/>
+      <c r="M68" s="8"/>
     </row>
     <row r="69">
       <c r="A69" s="8"/>
@@ -1287,10 +1357,11 @@
       <c r="F69" s="8"/>
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
-      <c r="I69" s="9"/>
-      <c r="J69" s="10"/>
-      <c r="K69" s="8"/>
+      <c r="I69" s="8"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="9"/>
       <c r="L69" s="8"/>
+      <c r="M69" s="8"/>
     </row>
     <row r="70">
       <c r="A70" s="8"/>
@@ -1301,10 +1372,11 @@
       <c r="F70" s="8"/>
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
-      <c r="I70" s="9"/>
-      <c r="J70" s="10"/>
-      <c r="K70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="9"/>
       <c r="L70" s="8"/>
+      <c r="M70" s="8"/>
     </row>
     <row r="71">
       <c r="A71" s="8"/>
@@ -1315,10 +1387,11 @@
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
-      <c r="I71" s="9"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="8"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="8"/>
+      <c r="K71" s="9"/>
       <c r="L71" s="8"/>
+      <c r="M71" s="8"/>
     </row>
     <row r="72">
       <c r="A72" s="8"/>
@@ -1329,10 +1402,11 @@
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
-      <c r="I72" s="9"/>
-      <c r="J72" s="10"/>
-      <c r="K72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="9"/>
       <c r="L72" s="8"/>
+      <c r="M72" s="8"/>
     </row>
     <row r="73">
       <c r="A73" s="8"/>
@@ -1343,10 +1417,11 @@
       <c r="F73" s="8"/>
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
-      <c r="I73" s="9"/>
-      <c r="J73" s="10"/>
-      <c r="K73" s="8"/>
+      <c r="I73" s="8"/>
+      <c r="J73" s="8"/>
+      <c r="K73" s="9"/>
       <c r="L73" s="8"/>
+      <c r="M73" s="8"/>
     </row>
     <row r="74">
       <c r="A74" s="8"/>
@@ -1357,10 +1432,11 @@
       <c r="F74" s="8"/>
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
-      <c r="I74" s="9"/>
-      <c r="J74" s="10"/>
-      <c r="K74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="9"/>
       <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
     </row>
     <row r="75">
       <c r="A75" s="8"/>
@@ -1371,10 +1447,11 @@
       <c r="F75" s="8"/>
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
-      <c r="I75" s="9"/>
-      <c r="J75" s="10"/>
-      <c r="K75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="9"/>
       <c r="L75" s="8"/>
+      <c r="M75" s="8"/>
     </row>
     <row r="76">
       <c r="A76" s="8"/>
@@ -1385,10 +1462,11 @@
       <c r="F76" s="8"/>
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
-      <c r="I76" s="9"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="9"/>
       <c r="L76" s="8"/>
+      <c r="M76" s="8"/>
     </row>
     <row r="77">
       <c r="A77" s="8"/>
@@ -1399,10 +1477,11 @@
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
-      <c r="I77" s="9"/>
-      <c r="J77" s="10"/>
-      <c r="K77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="9"/>
       <c r="L77" s="8"/>
+      <c r="M77" s="8"/>
     </row>
     <row r="78">
       <c r="A78" s="8"/>
@@ -1413,10 +1492,11 @@
       <c r="F78" s="8"/>
       <c r="G78" s="8"/>
       <c r="H78" s="8"/>
-      <c r="I78" s="9"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="9"/>
       <c r="L78" s="8"/>
+      <c r="M78" s="8"/>
     </row>
     <row r="79">
       <c r="A79" s="8"/>
@@ -1427,10 +1507,11 @@
       <c r="F79" s="8"/>
       <c r="G79" s="8"/>
       <c r="H79" s="8"/>
-      <c r="I79" s="9"/>
-      <c r="J79" s="10"/>
-      <c r="K79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="9"/>
       <c r="L79" s="8"/>
+      <c r="M79" s="8"/>
     </row>
     <row r="80">
       <c r="A80" s="8"/>
@@ -1441,10 +1522,11 @@
       <c r="F80" s="8"/>
       <c r="G80" s="8"/>
       <c r="H80" s="8"/>
-      <c r="I80" s="9"/>
-      <c r="J80" s="10"/>
-      <c r="K80" s="8"/>
+      <c r="I80" s="8"/>
+      <c r="J80" s="8"/>
+      <c r="K80" s="9"/>
       <c r="L80" s="8"/>
+      <c r="M80" s="8"/>
     </row>
     <row r="81">
       <c r="A81" s="8"/>
@@ -1455,10 +1537,11 @@
       <c r="F81" s="8"/>
       <c r="G81" s="8"/>
       <c r="H81" s="8"/>
-      <c r="I81" s="9"/>
-      <c r="J81" s="10"/>
-      <c r="K81" s="8"/>
+      <c r="I81" s="8"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="9"/>
       <c r="L81" s="8"/>
+      <c r="M81" s="8"/>
     </row>
     <row r="82">
       <c r="A82" s="8"/>
@@ -1469,10 +1552,11 @@
       <c r="F82" s="8"/>
       <c r="G82" s="8"/>
       <c r="H82" s="8"/>
-      <c r="I82" s="9"/>
-      <c r="J82" s="10"/>
-      <c r="K82" s="8"/>
+      <c r="I82" s="8"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="9"/>
       <c r="L82" s="8"/>
+      <c r="M82" s="8"/>
     </row>
     <row r="83">
       <c r="A83" s="8"/>
@@ -1483,10 +1567,11 @@
       <c r="F83" s="8"/>
       <c r="G83" s="8"/>
       <c r="H83" s="8"/>
-      <c r="I83" s="9"/>
-      <c r="J83" s="10"/>
-      <c r="K83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="9"/>
       <c r="L83" s="8"/>
+      <c r="M83" s="8"/>
     </row>
     <row r="84">
       <c r="A84" s="8"/>
@@ -1497,10 +1582,11 @@
       <c r="F84" s="8"/>
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
-      <c r="I84" s="9"/>
-      <c r="J84" s="10"/>
-      <c r="K84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="9"/>
       <c r="L84" s="8"/>
+      <c r="M84" s="8"/>
     </row>
     <row r="85">
       <c r="A85" s="8"/>
@@ -1511,10 +1597,11 @@
       <c r="F85" s="8"/>
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
-      <c r="I85" s="9"/>
-      <c r="J85" s="10"/>
-      <c r="K85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="9"/>
       <c r="L85" s="8"/>
+      <c r="M85" s="8"/>
     </row>
     <row r="86">
       <c r="A86" s="8"/>
@@ -1525,10 +1612,11 @@
       <c r="F86" s="8"/>
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
-      <c r="I86" s="9"/>
-      <c r="J86" s="10"/>
-      <c r="K86" s="8"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="9"/>
       <c r="L86" s="8"/>
+      <c r="M86" s="8"/>
     </row>
     <row r="87">
       <c r="A87" s="8"/>
@@ -1539,10 +1627,11 @@
       <c r="F87" s="8"/>
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
-      <c r="I87" s="9"/>
-      <c r="J87" s="10"/>
-      <c r="K87" s="8"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="9"/>
       <c r="L87" s="8"/>
+      <c r="M87" s="8"/>
     </row>
     <row r="88">
       <c r="A88" s="8"/>
@@ -1553,10 +1642,11 @@
       <c r="F88" s="8"/>
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
-      <c r="I88" s="9"/>
-      <c r="J88" s="10"/>
-      <c r="K88" s="8"/>
+      <c r="I88" s="8"/>
+      <c r="J88" s="8"/>
+      <c r="K88" s="9"/>
       <c r="L88" s="8"/>
+      <c r="M88" s="8"/>
     </row>
     <row r="89">
       <c r="A89" s="8"/>
@@ -1567,10 +1657,11 @@
       <c r="F89" s="8"/>
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
-      <c r="I89" s="9"/>
-      <c r="J89" s="10"/>
-      <c r="K89" s="8"/>
+      <c r="I89" s="8"/>
+      <c r="J89" s="8"/>
+      <c r="K89" s="9"/>
       <c r="L89" s="8"/>
+      <c r="M89" s="8"/>
     </row>
     <row r="90">
       <c r="A90" s="8"/>
@@ -1581,10 +1672,11 @@
       <c r="F90" s="8"/>
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
-      <c r="I90" s="9"/>
-      <c r="J90" s="10"/>
-      <c r="K90" s="8"/>
+      <c r="I90" s="8"/>
+      <c r="J90" s="8"/>
+      <c r="K90" s="9"/>
       <c r="L90" s="8"/>
+      <c r="M90" s="8"/>
     </row>
     <row r="91">
       <c r="A91" s="8"/>
@@ -1595,10 +1687,11 @@
       <c r="F91" s="8"/>
       <c r="G91" s="8"/>
       <c r="H91" s="8"/>
-      <c r="I91" s="9"/>
-      <c r="J91" s="10"/>
-      <c r="K91" s="8"/>
+      <c r="I91" s="8"/>
+      <c r="J91" s="8"/>
+      <c r="K91" s="9"/>
       <c r="L91" s="8"/>
+      <c r="M91" s="8"/>
     </row>
     <row r="92">
       <c r="A92" s="8"/>
@@ -1609,10 +1702,11 @@
       <c r="F92" s="8"/>
       <c r="G92" s="8"/>
       <c r="H92" s="8"/>
-      <c r="I92" s="9"/>
-      <c r="J92" s="10"/>
-      <c r="K92" s="8"/>
+      <c r="I92" s="8"/>
+      <c r="J92" s="8"/>
+      <c r="K92" s="9"/>
       <c r="L92" s="8"/>
+      <c r="M92" s="8"/>
     </row>
     <row r="93">
       <c r="A93" s="8"/>
@@ -1623,10 +1717,11 @@
       <c r="F93" s="8"/>
       <c r="G93" s="8"/>
       <c r="H93" s="8"/>
-      <c r="I93" s="9"/>
-      <c r="J93" s="10"/>
-      <c r="K93" s="8"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="9"/>
       <c r="L93" s="8"/>
+      <c r="M93" s="8"/>
     </row>
     <row r="94">
       <c r="A94" s="8"/>
@@ -1637,10 +1732,11 @@
       <c r="F94" s="8"/>
       <c r="G94" s="8"/>
       <c r="H94" s="8"/>
-      <c r="I94" s="9"/>
-      <c r="J94" s="10"/>
-      <c r="K94" s="8"/>
+      <c r="I94" s="8"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="9"/>
       <c r="L94" s="8"/>
+      <c r="M94" s="8"/>
     </row>
     <row r="95">
       <c r="A95" s="8"/>
@@ -1651,10 +1747,11 @@
       <c r="F95" s="8"/>
       <c r="G95" s="8"/>
       <c r="H95" s="8"/>
-      <c r="I95" s="9"/>
-      <c r="J95" s="10"/>
-      <c r="K95" s="8"/>
+      <c r="I95" s="8"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="9"/>
       <c r="L95" s="8"/>
+      <c r="M95" s="8"/>
     </row>
     <row r="96">
       <c r="A96" s="8"/>
@@ -1665,10 +1762,11 @@
       <c r="F96" s="8"/>
       <c r="G96" s="8"/>
       <c r="H96" s="8"/>
-      <c r="I96" s="9"/>
-      <c r="J96" s="10"/>
-      <c r="K96" s="8"/>
+      <c r="I96" s="8"/>
+      <c r="J96" s="8"/>
+      <c r="K96" s="9"/>
       <c r="L96" s="8"/>
+      <c r="M96" s="8"/>
     </row>
     <row r="97">
       <c r="A97" s="8"/>
@@ -1679,10 +1777,11 @@
       <c r="F97" s="8"/>
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
-      <c r="I97" s="9"/>
-      <c r="J97" s="10"/>
-      <c r="K97" s="8"/>
+      <c r="I97" s="8"/>
+      <c r="J97" s="8"/>
+      <c r="K97" s="9"/>
       <c r="L97" s="8"/>
+      <c r="M97" s="8"/>
     </row>
     <row r="98">
       <c r="A98" s="8"/>
@@ -1693,10 +1792,11 @@
       <c r="F98" s="8"/>
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
-      <c r="I98" s="9"/>
-      <c r="J98" s="10"/>
-      <c r="K98" s="8"/>
+      <c r="I98" s="8"/>
+      <c r="J98" s="8"/>
+      <c r="K98" s="9"/>
       <c r="L98" s="8"/>
+      <c r="M98" s="8"/>
     </row>
     <row r="99">
       <c r="A99" s="8"/>
@@ -1707,10 +1807,11 @@
       <c r="F99" s="8"/>
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
-      <c r="I99" s="9"/>
-      <c r="J99" s="10"/>
-      <c r="K99" s="8"/>
+      <c r="I99" s="8"/>
+      <c r="J99" s="8"/>
+      <c r="K99" s="9"/>
       <c r="L99" s="8"/>
+      <c r="M99" s="8"/>
     </row>
     <row r="100">
       <c r="A100" s="8"/>
@@ -1721,10 +1822,11 @@
       <c r="F100" s="8"/>
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
-      <c r="I100" s="9"/>
-      <c r="J100" s="10"/>
-      <c r="K100" s="8"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="8"/>
+      <c r="K100" s="9"/>
       <c r="L100" s="8"/>
+      <c r="M100" s="8"/>
     </row>
     <row r="101">
       <c r="A101" s="8"/>
@@ -1735,10 +1837,11 @@
       <c r="F101" s="8"/>
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
-      <c r="I101" s="9"/>
-      <c r="J101" s="10"/>
-      <c r="K101" s="8"/>
+      <c r="I101" s="8"/>
+      <c r="J101" s="8"/>
+      <c r="K101" s="9"/>
       <c r="L101" s="8"/>
+      <c r="M101" s="8"/>
     </row>
     <row r="102">
       <c r="A102" s="8"/>
@@ -1749,10 +1852,11 @@
       <c r="F102" s="8"/>
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
-      <c r="I102" s="9"/>
-      <c r="J102" s="10"/>
-      <c r="K102" s="8"/>
+      <c r="I102" s="8"/>
+      <c r="J102" s="8"/>
+      <c r="K102" s="9"/>
       <c r="L102" s="8"/>
+      <c r="M102" s="8"/>
     </row>
     <row r="103">
       <c r="A103" s="8"/>
@@ -1763,10 +1867,11 @@
       <c r="F103" s="8"/>
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
-      <c r="I103" s="9"/>
-      <c r="J103" s="10"/>
-      <c r="K103" s="8"/>
+      <c r="I103" s="8"/>
+      <c r="J103" s="8"/>
+      <c r="K103" s="9"/>
       <c r="L103" s="8"/>
+      <c r="M103" s="8"/>
     </row>
     <row r="104">
       <c r="A104" s="8"/>
@@ -1777,10 +1882,11 @@
       <c r="F104" s="8"/>
       <c r="G104" s="8"/>
       <c r="H104" s="8"/>
-      <c r="I104" s="9"/>
-      <c r="J104" s="10"/>
-      <c r="K104" s="8"/>
+      <c r="I104" s="8"/>
+      <c r="J104" s="8"/>
+      <c r="K104" s="9"/>
       <c r="L104" s="8"/>
+      <c r="M104" s="8"/>
     </row>
     <row r="105">
       <c r="A105" s="8"/>
@@ -1791,10 +1897,11 @@
       <c r="F105" s="8"/>
       <c r="G105" s="8"/>
       <c r="H105" s="8"/>
-      <c r="I105" s="9"/>
-      <c r="J105" s="10"/>
-      <c r="K105" s="8"/>
+      <c r="I105" s="8"/>
+      <c r="J105" s="8"/>
+      <c r="K105" s="9"/>
       <c r="L105" s="8"/>
+      <c r="M105" s="8"/>
     </row>
     <row r="106">
       <c r="A106" s="8"/>
@@ -1805,10 +1912,11 @@
       <c r="F106" s="8"/>
       <c r="G106" s="8"/>
       <c r="H106" s="8"/>
-      <c r="I106" s="9"/>
-      <c r="J106" s="10"/>
-      <c r="K106" s="8"/>
+      <c r="I106" s="8"/>
+      <c r="J106" s="8"/>
+      <c r="K106" s="9"/>
       <c r="L106" s="8"/>
+      <c r="M106" s="8"/>
     </row>
     <row r="107">
       <c r="A107" s="8"/>
@@ -1819,10 +1927,11 @@
       <c r="F107" s="8"/>
       <c r="G107" s="8"/>
       <c r="H107" s="8"/>
-      <c r="I107" s="9"/>
-      <c r="J107" s="10"/>
-      <c r="K107" s="8"/>
+      <c r="I107" s="8"/>
+      <c r="J107" s="8"/>
+      <c r="K107" s="9"/>
       <c r="L107" s="8"/>
+      <c r="M107" s="8"/>
     </row>
     <row r="108">
       <c r="A108" s="8"/>
@@ -1833,10 +1942,11 @@
       <c r="F108" s="8"/>
       <c r="G108" s="8"/>
       <c r="H108" s="8"/>
-      <c r="I108" s="9"/>
-      <c r="J108" s="10"/>
-      <c r="K108" s="8"/>
+      <c r="I108" s="8"/>
+      <c r="J108" s="8"/>
+      <c r="K108" s="9"/>
       <c r="L108" s="8"/>
+      <c r="M108" s="8"/>
     </row>
     <row r="109">
       <c r="A109" s="8"/>
@@ -1847,10 +1957,11 @@
       <c r="F109" s="8"/>
       <c r="G109" s="8"/>
       <c r="H109" s="8"/>
-      <c r="I109" s="9"/>
-      <c r="J109" s="10"/>
-      <c r="K109" s="8"/>
+      <c r="I109" s="8"/>
+      <c r="J109" s="8"/>
+      <c r="K109" s="9"/>
       <c r="L109" s="8"/>
+      <c r="M109" s="8"/>
     </row>
     <row r="110">
       <c r="A110" s="8"/>
@@ -1861,10 +1972,11 @@
       <c r="F110" s="8"/>
       <c r="G110" s="8"/>
       <c r="H110" s="8"/>
-      <c r="I110" s="9"/>
-      <c r="J110" s="10"/>
-      <c r="K110" s="8"/>
+      <c r="I110" s="8"/>
+      <c r="J110" s="8"/>
+      <c r="K110" s="9"/>
       <c r="L110" s="8"/>
+      <c r="M110" s="8"/>
     </row>
     <row r="111">
       <c r="A111" s="8"/>
@@ -1875,10 +1987,11 @@
       <c r="F111" s="8"/>
       <c r="G111" s="8"/>
       <c r="H111" s="8"/>
-      <c r="I111" s="9"/>
-      <c r="J111" s="10"/>
-      <c r="K111" s="8"/>
+      <c r="I111" s="8"/>
+      <c r="J111" s="8"/>
+      <c r="K111" s="9"/>
       <c r="L111" s="8"/>
+      <c r="M111" s="8"/>
     </row>
     <row r="112">
       <c r="A112" s="8"/>
@@ -1889,10 +2002,11 @@
       <c r="F112" s="8"/>
       <c r="G112" s="8"/>
       <c r="H112" s="8"/>
-      <c r="I112" s="9"/>
-      <c r="J112" s="10"/>
-      <c r="K112" s="8"/>
+      <c r="I112" s="8"/>
+      <c r="J112" s="8"/>
+      <c r="K112" s="9"/>
       <c r="L112" s="8"/>
+      <c r="M112" s="8"/>
     </row>
     <row r="113">
       <c r="A113" s="8"/>
@@ -1903,10 +2017,11 @@
       <c r="F113" s="8"/>
       <c r="G113" s="8"/>
       <c r="H113" s="8"/>
-      <c r="I113" s="9"/>
-      <c r="J113" s="10"/>
-      <c r="K113" s="8"/>
+      <c r="I113" s="8"/>
+      <c r="J113" s="8"/>
+      <c r="K113" s="9"/>
       <c r="L113" s="8"/>
+      <c r="M113" s="8"/>
     </row>
     <row r="114">
       <c r="A114" s="8"/>
@@ -1917,10 +2032,11 @@
       <c r="F114" s="8"/>
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
-      <c r="I114" s="9"/>
-      <c r="J114" s="10"/>
-      <c r="K114" s="8"/>
+      <c r="I114" s="8"/>
+      <c r="J114" s="8"/>
+      <c r="K114" s="9"/>
       <c r="L114" s="8"/>
+      <c r="M114" s="8"/>
     </row>
     <row r="115">
       <c r="A115" s="8"/>
@@ -1931,10 +2047,11 @@
       <c r="F115" s="8"/>
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
-      <c r="I115" s="9"/>
-      <c r="J115" s="10"/>
-      <c r="K115" s="8"/>
+      <c r="I115" s="8"/>
+      <c r="J115" s="8"/>
+      <c r="K115" s="9"/>
       <c r="L115" s="8"/>
+      <c r="M115" s="8"/>
     </row>
     <row r="116">
       <c r="A116" s="8"/>
@@ -1945,10 +2062,11 @@
       <c r="F116" s="8"/>
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
-      <c r="I116" s="9"/>
-      <c r="J116" s="10"/>
-      <c r="K116" s="8"/>
+      <c r="I116" s="8"/>
+      <c r="J116" s="8"/>
+      <c r="K116" s="9"/>
       <c r="L116" s="8"/>
+      <c r="M116" s="8"/>
     </row>
     <row r="117">
       <c r="A117" s="8"/>
@@ -1959,10 +2077,11 @@
       <c r="F117" s="8"/>
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
-      <c r="I117" s="9"/>
-      <c r="J117" s="10"/>
-      <c r="K117" s="8"/>
+      <c r="I117" s="8"/>
+      <c r="J117" s="8"/>
+      <c r="K117" s="9"/>
       <c r="L117" s="8"/>
+      <c r="M117" s="8"/>
     </row>
     <row r="118">
       <c r="A118" s="8"/>
@@ -1973,10 +2092,11 @@
       <c r="F118" s="8"/>
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
-      <c r="I118" s="9"/>
-      <c r="J118" s="10"/>
-      <c r="K118" s="8"/>
+      <c r="I118" s="8"/>
+      <c r="J118" s="8"/>
+      <c r="K118" s="9"/>
       <c r="L118" s="8"/>
+      <c r="M118" s="8"/>
     </row>
     <row r="119">
       <c r="A119" s="8"/>
@@ -1987,10 +2107,11 @@
       <c r="F119" s="8"/>
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
-      <c r="I119" s="9"/>
-      <c r="J119" s="10"/>
-      <c r="K119" s="8"/>
+      <c r="I119" s="8"/>
+      <c r="J119" s="8"/>
+      <c r="K119" s="9"/>
       <c r="L119" s="8"/>
+      <c r="M119" s="8"/>
     </row>
     <row r="120">
       <c r="A120" s="8"/>
@@ -2001,10 +2122,11 @@
       <c r="F120" s="8"/>
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
-      <c r="I120" s="9"/>
-      <c r="J120" s="10"/>
-      <c r="K120" s="8"/>
+      <c r="I120" s="8"/>
+      <c r="J120" s="8"/>
+      <c r="K120" s="9"/>
       <c r="L120" s="8"/>
+      <c r="M120" s="8"/>
     </row>
     <row r="121">
       <c r="A121" s="8"/>
@@ -2015,10 +2137,11 @@
       <c r="F121" s="8"/>
       <c r="G121" s="8"/>
       <c r="H121" s="8"/>
-      <c r="I121" s="9"/>
-      <c r="J121" s="10"/>
-      <c r="K121" s="8"/>
+      <c r="I121" s="8"/>
+      <c r="J121" s="8"/>
+      <c r="K121" s="9"/>
       <c r="L121" s="8"/>
+      <c r="M121" s="8"/>
     </row>
     <row r="122">
       <c r="A122" s="8"/>
@@ -2029,10 +2152,11 @@
       <c r="F122" s="8"/>
       <c r="G122" s="8"/>
       <c r="H122" s="8"/>
-      <c r="I122" s="9"/>
-      <c r="J122" s="10"/>
-      <c r="K122" s="8"/>
+      <c r="I122" s="8"/>
+      <c r="J122" s="8"/>
+      <c r="K122" s="9"/>
       <c r="L122" s="8"/>
+      <c r="M122" s="8"/>
     </row>
     <row r="123">
       <c r="A123" s="8"/>
@@ -2043,10 +2167,11 @@
       <c r="F123" s="8"/>
       <c r="G123" s="8"/>
       <c r="H123" s="8"/>
-      <c r="I123" s="9"/>
-      <c r="J123" s="10"/>
-      <c r="K123" s="8"/>
+      <c r="I123" s="8"/>
+      <c r="J123" s="8"/>
+      <c r="K123" s="9"/>
       <c r="L123" s="8"/>
+      <c r="M123" s="8"/>
     </row>
     <row r="124">
       <c r="A124" s="8"/>
@@ -2057,10 +2182,11 @@
       <c r="F124" s="8"/>
       <c r="G124" s="8"/>
       <c r="H124" s="8"/>
-      <c r="I124" s="9"/>
-      <c r="J124" s="10"/>
-      <c r="K124" s="8"/>
+      <c r="I124" s="8"/>
+      <c r="J124" s="8"/>
+      <c r="K124" s="9"/>
       <c r="L124" s="8"/>
+      <c r="M124" s="8"/>
     </row>
     <row r="125">
       <c r="A125" s="8"/>
@@ -2071,10 +2197,11 @@
       <c r="F125" s="8"/>
       <c r="G125" s="8"/>
       <c r="H125" s="8"/>
-      <c r="I125" s="9"/>
-      <c r="J125" s="10"/>
-      <c r="K125" s="8"/>
+      <c r="I125" s="8"/>
+      <c r="J125" s="8"/>
+      <c r="K125" s="9"/>
       <c r="L125" s="8"/>
+      <c r="M125" s="8"/>
     </row>
     <row r="126">
       <c r="A126" s="8"/>
@@ -2085,10 +2212,11 @@
       <c r="F126" s="8"/>
       <c r="G126" s="8"/>
       <c r="H126" s="8"/>
-      <c r="I126" s="9"/>
-      <c r="J126" s="10"/>
-      <c r="K126" s="8"/>
+      <c r="I126" s="8"/>
+      <c r="J126" s="8"/>
+      <c r="K126" s="9"/>
       <c r="L126" s="8"/>
+      <c r="M126" s="8"/>
     </row>
     <row r="127">
       <c r="A127" s="8"/>
@@ -2099,10 +2227,11 @@
       <c r="F127" s="8"/>
       <c r="G127" s="8"/>
       <c r="H127" s="8"/>
-      <c r="I127" s="9"/>
-      <c r="J127" s="10"/>
-      <c r="K127" s="8"/>
+      <c r="I127" s="8"/>
+      <c r="J127" s="8"/>
+      <c r="K127" s="9"/>
       <c r="L127" s="8"/>
+      <c r="M127" s="8"/>
     </row>
     <row r="128">
       <c r="A128" s="8"/>
@@ -2113,10 +2242,11 @@
       <c r="F128" s="8"/>
       <c r="G128" s="8"/>
       <c r="H128" s="8"/>
-      <c r="I128" s="9"/>
-      <c r="J128" s="10"/>
-      <c r="K128" s="8"/>
+      <c r="I128" s="8"/>
+      <c r="J128" s="8"/>
+      <c r="K128" s="9"/>
       <c r="L128" s="8"/>
+      <c r="M128" s="8"/>
     </row>
     <row r="129">
       <c r="A129" s="8"/>
@@ -2127,10 +2257,11 @@
       <c r="F129" s="8"/>
       <c r="G129" s="8"/>
       <c r="H129" s="8"/>
-      <c r="I129" s="9"/>
-      <c r="J129" s="10"/>
-      <c r="K129" s="8"/>
+      <c r="I129" s="8"/>
+      <c r="J129" s="8"/>
+      <c r="K129" s="9"/>
       <c r="L129" s="8"/>
+      <c r="M129" s="8"/>
     </row>
     <row r="130">
       <c r="A130" s="8"/>
@@ -2141,10 +2272,11 @@
       <c r="F130" s="8"/>
       <c r="G130" s="8"/>
       <c r="H130" s="8"/>
-      <c r="I130" s="9"/>
-      <c r="J130" s="10"/>
-      <c r="K130" s="8"/>
+      <c r="I130" s="8"/>
+      <c r="J130" s="8"/>
+      <c r="K130" s="9"/>
       <c r="L130" s="8"/>
+      <c r="M130" s="8"/>
     </row>
     <row r="131">
       <c r="A131" s="8"/>
@@ -2155,10 +2287,11 @@
       <c r="F131" s="8"/>
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
-      <c r="I131" s="9"/>
-      <c r="J131" s="10"/>
-      <c r="K131" s="8"/>
+      <c r="I131" s="8"/>
+      <c r="J131" s="8"/>
+      <c r="K131" s="9"/>
       <c r="L131" s="8"/>
+      <c r="M131" s="8"/>
     </row>
     <row r="132">
       <c r="A132" s="8"/>
@@ -2169,10 +2302,11 @@
       <c r="F132" s="8"/>
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
-      <c r="I132" s="9"/>
-      <c r="J132" s="10"/>
-      <c r="K132" s="8"/>
+      <c r="I132" s="8"/>
+      <c r="J132" s="8"/>
+      <c r="K132" s="9"/>
       <c r="L132" s="8"/>
+      <c r="M132" s="8"/>
     </row>
     <row r="133">
       <c r="A133" s="8"/>
@@ -2183,10 +2317,11 @@
       <c r="F133" s="8"/>
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
-      <c r="I133" s="9"/>
-      <c r="J133" s="10"/>
-      <c r="K133" s="8"/>
+      <c r="I133" s="8"/>
+      <c r="J133" s="8"/>
+      <c r="K133" s="9"/>
       <c r="L133" s="8"/>
+      <c r="M133" s="8"/>
     </row>
     <row r="134">
       <c r="A134" s="8"/>
@@ -2197,10 +2332,11 @@
       <c r="F134" s="8"/>
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
-      <c r="I134" s="9"/>
-      <c r="J134" s="10"/>
-      <c r="K134" s="8"/>
+      <c r="I134" s="8"/>
+      <c r="J134" s="8"/>
+      <c r="K134" s="9"/>
       <c r="L134" s="8"/>
+      <c r="M134" s="8"/>
     </row>
     <row r="135">
       <c r="A135" s="8"/>
@@ -2211,10 +2347,11 @@
       <c r="F135" s="8"/>
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
-      <c r="I135" s="9"/>
-      <c r="J135" s="10"/>
-      <c r="K135" s="8"/>
+      <c r="I135" s="8"/>
+      <c r="J135" s="8"/>
+      <c r="K135" s="9"/>
       <c r="L135" s="8"/>
+      <c r="M135" s="8"/>
     </row>
     <row r="136">
       <c r="A136" s="8"/>
@@ -2225,10 +2362,11 @@
       <c r="F136" s="8"/>
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
-      <c r="I136" s="9"/>
-      <c r="J136" s="10"/>
-      <c r="K136" s="8"/>
+      <c r="I136" s="8"/>
+      <c r="J136" s="8"/>
+      <c r="K136" s="9"/>
       <c r="L136" s="8"/>
+      <c r="M136" s="8"/>
     </row>
     <row r="137">
       <c r="A137" s="8"/>
@@ -2239,10 +2377,11 @@
       <c r="F137" s="8"/>
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
-      <c r="I137" s="9"/>
-      <c r="J137" s="10"/>
-      <c r="K137" s="8"/>
+      <c r="I137" s="8"/>
+      <c r="J137" s="8"/>
+      <c r="K137" s="9"/>
       <c r="L137" s="8"/>
+      <c r="M137" s="8"/>
     </row>
     <row r="138">
       <c r="A138" s="8"/>
@@ -2253,10 +2392,11 @@
       <c r="F138" s="8"/>
       <c r="G138" s="8"/>
       <c r="H138" s="8"/>
-      <c r="I138" s="9"/>
-      <c r="J138" s="10"/>
-      <c r="K138" s="8"/>
+      <c r="I138" s="8"/>
+      <c r="J138" s="8"/>
+      <c r="K138" s="9"/>
       <c r="L138" s="8"/>
+      <c r="M138" s="8"/>
     </row>
     <row r="139">
       <c r="A139" s="8"/>
@@ -2267,10 +2407,11 @@
       <c r="F139" s="8"/>
       <c r="G139" s="8"/>
       <c r="H139" s="8"/>
-      <c r="I139" s="9"/>
-      <c r="J139" s="10"/>
-      <c r="K139" s="8"/>
+      <c r="I139" s="8"/>
+      <c r="J139" s="8"/>
+      <c r="K139" s="9"/>
       <c r="L139" s="8"/>
+      <c r="M139" s="8"/>
     </row>
     <row r="140">
       <c r="A140" s="8"/>
@@ -2281,10 +2422,11 @@
       <c r="F140" s="8"/>
       <c r="G140" s="8"/>
       <c r="H140" s="8"/>
-      <c r="I140" s="9"/>
-      <c r="J140" s="10"/>
-      <c r="K140" s="8"/>
+      <c r="I140" s="8"/>
+      <c r="J140" s="8"/>
+      <c r="K140" s="9"/>
       <c r="L140" s="8"/>
+      <c r="M140" s="8"/>
     </row>
     <row r="141">
       <c r="A141" s="8"/>
@@ -2295,10 +2437,11 @@
       <c r="F141" s="8"/>
       <c r="G141" s="8"/>
       <c r="H141" s="8"/>
-      <c r="I141" s="9"/>
-      <c r="J141" s="10"/>
-      <c r="K141" s="8"/>
+      <c r="I141" s="8"/>
+      <c r="J141" s="8"/>
+      <c r="K141" s="9"/>
       <c r="L141" s="8"/>
+      <c r="M141" s="8"/>
     </row>
     <row r="142">
       <c r="A142" s="8"/>
@@ -2309,10 +2452,11 @@
       <c r="F142" s="8"/>
       <c r="G142" s="8"/>
       <c r="H142" s="8"/>
-      <c r="I142" s="9"/>
-      <c r="J142" s="10"/>
-      <c r="K142" s="8"/>
+      <c r="I142" s="8"/>
+      <c r="J142" s="8"/>
+      <c r="K142" s="9"/>
       <c r="L142" s="8"/>
+      <c r="M142" s="8"/>
     </row>
     <row r="143">
       <c r="A143" s="8"/>
@@ -2323,10 +2467,11 @@
       <c r="F143" s="8"/>
       <c r="G143" s="8"/>
       <c r="H143" s="8"/>
-      <c r="I143" s="9"/>
-      <c r="J143" s="10"/>
-      <c r="K143" s="8"/>
+      <c r="I143" s="8"/>
+      <c r="J143" s="8"/>
+      <c r="K143" s="9"/>
       <c r="L143" s="8"/>
+      <c r="M143" s="8"/>
     </row>
     <row r="144">
       <c r="A144" s="8"/>
@@ -2337,10 +2482,11 @@
       <c r="F144" s="8"/>
       <c r="G144" s="8"/>
       <c r="H144" s="8"/>
-      <c r="I144" s="9"/>
-      <c r="J144" s="10"/>
-      <c r="K144" s="8"/>
+      <c r="I144" s="8"/>
+      <c r="J144" s="8"/>
+      <c r="K144" s="9"/>
       <c r="L144" s="8"/>
+      <c r="M144" s="8"/>
     </row>
     <row r="145">
       <c r="A145" s="8"/>
@@ -2351,10 +2497,11 @@
       <c r="F145" s="8"/>
       <c r="G145" s="8"/>
       <c r="H145" s="8"/>
-      <c r="I145" s="9"/>
-      <c r="J145" s="10"/>
-      <c r="K145" s="8"/>
+      <c r="I145" s="8"/>
+      <c r="J145" s="8"/>
+      <c r="K145" s="9"/>
       <c r="L145" s="8"/>
+      <c r="M145" s="8"/>
     </row>
     <row r="146">
       <c r="A146" s="8"/>
@@ -2365,10 +2512,11 @@
       <c r="F146" s="8"/>
       <c r="G146" s="8"/>
       <c r="H146" s="8"/>
-      <c r="I146" s="9"/>
-      <c r="J146" s="10"/>
-      <c r="K146" s="8"/>
+      <c r="I146" s="8"/>
+      <c r="J146" s="8"/>
+      <c r="K146" s="9"/>
       <c r="L146" s="8"/>
+      <c r="M146" s="8"/>
     </row>
     <row r="147">
       <c r="A147" s="8"/>
@@ -2379,10 +2527,11 @@
       <c r="F147" s="8"/>
       <c r="G147" s="8"/>
       <c r="H147" s="8"/>
-      <c r="I147" s="9"/>
-      <c r="J147" s="10"/>
-      <c r="K147" s="8"/>
+      <c r="I147" s="8"/>
+      <c r="J147" s="8"/>
+      <c r="K147" s="9"/>
       <c r="L147" s="8"/>
+      <c r="M147" s="8"/>
     </row>
     <row r="148">
       <c r="A148" s="8"/>
@@ -2393,10 +2542,11 @@
       <c r="F148" s="8"/>
       <c r="G148" s="8"/>
       <c r="H148" s="8"/>
-      <c r="I148" s="9"/>
-      <c r="J148" s="10"/>
-      <c r="K148" s="8"/>
+      <c r="I148" s="8"/>
+      <c r="J148" s="8"/>
+      <c r="K148" s="9"/>
       <c r="L148" s="8"/>
+      <c r="M148" s="8"/>
     </row>
     <row r="149">
       <c r="A149" s="8"/>
@@ -2407,10 +2557,11 @@
       <c r="F149" s="8"/>
       <c r="G149" s="8"/>
       <c r="H149" s="8"/>
-      <c r="I149" s="9"/>
-      <c r="J149" s="10"/>
-      <c r="K149" s="8"/>
+      <c r="I149" s="8"/>
+      <c r="J149" s="8"/>
+      <c r="K149" s="9"/>
       <c r="L149" s="8"/>
+      <c r="M149" s="8"/>
     </row>
     <row r="150">
       <c r="A150" s="8"/>
@@ -2421,10 +2572,11 @@
       <c r="F150" s="8"/>
       <c r="G150" s="8"/>
       <c r="H150" s="8"/>
-      <c r="I150" s="9"/>
-      <c r="J150" s="10"/>
-      <c r="K150" s="8"/>
+      <c r="I150" s="8"/>
+      <c r="J150" s="8"/>
+      <c r="K150" s="9"/>
       <c r="L150" s="8"/>
+      <c r="M150" s="8"/>
     </row>
     <row r="151">
       <c r="A151" s="8"/>
@@ -2435,10 +2587,11 @@
       <c r="F151" s="8"/>
       <c r="G151" s="8"/>
       <c r="H151" s="8"/>
-      <c r="I151" s="9"/>
-      <c r="J151" s="10"/>
-      <c r="K151" s="8"/>
+      <c r="I151" s="8"/>
+      <c r="J151" s="8"/>
+      <c r="K151" s="9"/>
       <c r="L151" s="8"/>
+      <c r="M151" s="8"/>
     </row>
     <row r="152">
       <c r="A152" s="8"/>
@@ -2449,10 +2602,11 @@
       <c r="F152" s="8"/>
       <c r="G152" s="8"/>
       <c r="H152" s="8"/>
-      <c r="I152" s="9"/>
-      <c r="J152" s="10"/>
-      <c r="K152" s="8"/>
+      <c r="I152" s="8"/>
+      <c r="J152" s="8"/>
+      <c r="K152" s="9"/>
       <c r="L152" s="8"/>
+      <c r="M152" s="8"/>
     </row>
     <row r="153">
       <c r="A153" s="8"/>
@@ -2463,10 +2617,11 @@
       <c r="F153" s="8"/>
       <c r="G153" s="8"/>
       <c r="H153" s="8"/>
-      <c r="I153" s="9"/>
-      <c r="J153" s="10"/>
-      <c r="K153" s="8"/>
+      <c r="I153" s="8"/>
+      <c r="J153" s="8"/>
+      <c r="K153" s="9"/>
       <c r="L153" s="8"/>
+      <c r="M153" s="8"/>
     </row>
     <row r="154">
       <c r="A154" s="8"/>
@@ -2477,10 +2632,11 @@
       <c r="F154" s="8"/>
       <c r="G154" s="8"/>
       <c r="H154" s="8"/>
-      <c r="I154" s="9"/>
-      <c r="J154" s="10"/>
-      <c r="K154" s="8"/>
+      <c r="I154" s="8"/>
+      <c r="J154" s="8"/>
+      <c r="K154" s="9"/>
       <c r="L154" s="8"/>
+      <c r="M154" s="8"/>
     </row>
     <row r="155">
       <c r="A155" s="8"/>
@@ -2491,10 +2647,11 @@
       <c r="F155" s="8"/>
       <c r="G155" s="8"/>
       <c r="H155" s="8"/>
-      <c r="I155" s="9"/>
-      <c r="J155" s="10"/>
-      <c r="K155" s="8"/>
+      <c r="I155" s="8"/>
+      <c r="J155" s="8"/>
+      <c r="K155" s="9"/>
       <c r="L155" s="8"/>
+      <c r="M155" s="8"/>
     </row>
     <row r="156">
       <c r="A156" s="8"/>
@@ -2505,10 +2662,11 @@
       <c r="F156" s="8"/>
       <c r="G156" s="8"/>
       <c r="H156" s="8"/>
-      <c r="I156" s="9"/>
-      <c r="J156" s="10"/>
-      <c r="K156" s="8"/>
+      <c r="I156" s="8"/>
+      <c r="J156" s="8"/>
+      <c r="K156" s="9"/>
       <c r="L156" s="8"/>
+      <c r="M156" s="8"/>
     </row>
     <row r="157">
       <c r="A157" s="8"/>
@@ -2519,10 +2677,11 @@
       <c r="F157" s="8"/>
       <c r="G157" s="8"/>
       <c r="H157" s="8"/>
-      <c r="I157" s="9"/>
-      <c r="J157" s="10"/>
-      <c r="K157" s="8"/>
+      <c r="I157" s="8"/>
+      <c r="J157" s="8"/>
+      <c r="K157" s="9"/>
       <c r="L157" s="8"/>
+      <c r="M157" s="8"/>
     </row>
     <row r="158">
       <c r="A158" s="8"/>
@@ -2533,10 +2692,11 @@
       <c r="F158" s="8"/>
       <c r="G158" s="8"/>
       <c r="H158" s="8"/>
-      <c r="I158" s="9"/>
-      <c r="J158" s="10"/>
-      <c r="K158" s="8"/>
+      <c r="I158" s="8"/>
+      <c r="J158" s="8"/>
+      <c r="K158" s="9"/>
       <c r="L158" s="8"/>
+      <c r="M158" s="8"/>
     </row>
     <row r="159">
       <c r="A159" s="8"/>
@@ -2547,10 +2707,11 @@
       <c r="F159" s="8"/>
       <c r="G159" s="8"/>
       <c r="H159" s="8"/>
-      <c r="I159" s="9"/>
-      <c r="J159" s="10"/>
-      <c r="K159" s="8"/>
+      <c r="I159" s="8"/>
+      <c r="J159" s="8"/>
+      <c r="K159" s="9"/>
       <c r="L159" s="8"/>
+      <c r="M159" s="8"/>
     </row>
     <row r="160">
       <c r="A160" s="8"/>
@@ -2561,10 +2722,11 @@
       <c r="F160" s="8"/>
       <c r="G160" s="8"/>
       <c r="H160" s="8"/>
-      <c r="I160" s="9"/>
-      <c r="J160" s="10"/>
-      <c r="K160" s="8"/>
+      <c r="I160" s="8"/>
+      <c r="J160" s="8"/>
+      <c r="K160" s="9"/>
       <c r="L160" s="8"/>
+      <c r="M160" s="8"/>
     </row>
     <row r="161">
       <c r="A161" s="8"/>
@@ -2575,10 +2737,11 @@
       <c r="F161" s="8"/>
       <c r="G161" s="8"/>
       <c r="H161" s="8"/>
-      <c r="I161" s="9"/>
-      <c r="J161" s="10"/>
-      <c r="K161" s="8"/>
+      <c r="I161" s="8"/>
+      <c r="J161" s="8"/>
+      <c r="K161" s="9"/>
       <c r="L161" s="8"/>
+      <c r="M161" s="8"/>
     </row>
     <row r="162">
       <c r="A162" s="8"/>
@@ -2589,10 +2752,11 @@
       <c r="F162" s="8"/>
       <c r="G162" s="8"/>
       <c r="H162" s="8"/>
-      <c r="I162" s="9"/>
-      <c r="J162" s="10"/>
-      <c r="K162" s="8"/>
+      <c r="I162" s="8"/>
+      <c r="J162" s="8"/>
+      <c r="K162" s="9"/>
       <c r="L162" s="8"/>
+      <c r="M162" s="8"/>
     </row>
     <row r="163">
       <c r="A163" s="8"/>
@@ -2603,10 +2767,11 @@
       <c r="F163" s="8"/>
       <c r="G163" s="8"/>
       <c r="H163" s="8"/>
-      <c r="I163" s="9"/>
-      <c r="J163" s="10"/>
-      <c r="K163" s="8"/>
+      <c r="I163" s="8"/>
+      <c r="J163" s="8"/>
+      <c r="K163" s="9"/>
       <c r="L163" s="8"/>
+      <c r="M163" s="8"/>
     </row>
     <row r="164">
       <c r="A164" s="8"/>
@@ -2617,10 +2782,11 @@
       <c r="F164" s="8"/>
       <c r="G164" s="8"/>
       <c r="H164" s="8"/>
-      <c r="I164" s="9"/>
-      <c r="J164" s="10"/>
-      <c r="K164" s="8"/>
+      <c r="I164" s="8"/>
+      <c r="J164" s="8"/>
+      <c r="K164" s="9"/>
       <c r="L164" s="8"/>
+      <c r="M164" s="8"/>
     </row>
     <row r="165">
       <c r="A165" s="8"/>
@@ -2631,10 +2797,11 @@
       <c r="F165" s="8"/>
       <c r="G165" s="8"/>
       <c r="H165" s="8"/>
-      <c r="I165" s="9"/>
-      <c r="J165" s="10"/>
-      <c r="K165" s="8"/>
+      <c r="I165" s="8"/>
+      <c r="J165" s="8"/>
+      <c r="K165" s="9"/>
       <c r="L165" s="8"/>
+      <c r="M165" s="8"/>
     </row>
     <row r="166">
       <c r="A166" s="8"/>
@@ -2645,10 +2812,11 @@
       <c r="F166" s="8"/>
       <c r="G166" s="8"/>
       <c r="H166" s="8"/>
-      <c r="I166" s="9"/>
-      <c r="J166" s="10"/>
-      <c r="K166" s="8"/>
+      <c r="I166" s="8"/>
+      <c r="J166" s="8"/>
+      <c r="K166" s="9"/>
       <c r="L166" s="8"/>
+      <c r="M166" s="8"/>
     </row>
     <row r="167">
       <c r="A167" s="8"/>
@@ -2659,10 +2827,11 @@
       <c r="F167" s="8"/>
       <c r="G167" s="8"/>
       <c r="H167" s="8"/>
-      <c r="I167" s="9"/>
-      <c r="J167" s="10"/>
-      <c r="K167" s="8"/>
+      <c r="I167" s="8"/>
+      <c r="J167" s="8"/>
+      <c r="K167" s="9"/>
       <c r="L167" s="8"/>
+      <c r="M167" s="8"/>
     </row>
     <row r="168">
       <c r="A168" s="8"/>
@@ -2673,10 +2842,11 @@
       <c r="F168" s="8"/>
       <c r="G168" s="8"/>
       <c r="H168" s="8"/>
-      <c r="I168" s="9"/>
-      <c r="J168" s="10"/>
-      <c r="K168" s="8"/>
+      <c r="I168" s="8"/>
+      <c r="J168" s="8"/>
+      <c r="K168" s="9"/>
       <c r="L168" s="8"/>
+      <c r="M168" s="8"/>
     </row>
     <row r="169">
       <c r="A169" s="8"/>
@@ -2687,10 +2857,11 @@
       <c r="F169" s="8"/>
       <c r="G169" s="8"/>
       <c r="H169" s="8"/>
-      <c r="I169" s="9"/>
-      <c r="J169" s="10"/>
-      <c r="K169" s="8"/>
+      <c r="I169" s="8"/>
+      <c r="J169" s="8"/>
+      <c r="K169" s="9"/>
       <c r="L169" s="8"/>
+      <c r="M169" s="8"/>
     </row>
     <row r="170">
       <c r="A170" s="8"/>
@@ -2701,10 +2872,11 @@
       <c r="F170" s="8"/>
       <c r="G170" s="8"/>
       <c r="H170" s="8"/>
-      <c r="I170" s="9"/>
-      <c r="J170" s="10"/>
-      <c r="K170" s="8"/>
+      <c r="I170" s="8"/>
+      <c r="J170" s="8"/>
+      <c r="K170" s="9"/>
       <c r="L170" s="8"/>
+      <c r="M170" s="8"/>
     </row>
     <row r="171">
       <c r="A171" s="8"/>
@@ -2715,10 +2887,11 @@
       <c r="F171" s="8"/>
       <c r="G171" s="8"/>
       <c r="H171" s="8"/>
-      <c r="I171" s="9"/>
-      <c r="J171" s="10"/>
-      <c r="K171" s="8"/>
+      <c r="I171" s="8"/>
+      <c r="J171" s="8"/>
+      <c r="K171" s="9"/>
       <c r="L171" s="8"/>
+      <c r="M171" s="8"/>
     </row>
     <row r="172">
       <c r="A172" s="8"/>
@@ -2729,10 +2902,11 @@
       <c r="F172" s="8"/>
       <c r="G172" s="8"/>
       <c r="H172" s="8"/>
-      <c r="I172" s="9"/>
-      <c r="J172" s="10"/>
-      <c r="K172" s="8"/>
+      <c r="I172" s="8"/>
+      <c r="J172" s="8"/>
+      <c r="K172" s="9"/>
       <c r="L172" s="8"/>
+      <c r="M172" s="8"/>
     </row>
     <row r="173">
       <c r="A173" s="8"/>
@@ -2743,10 +2917,11 @@
       <c r="F173" s="8"/>
       <c r="G173" s="8"/>
       <c r="H173" s="8"/>
-      <c r="I173" s="9"/>
-      <c r="J173" s="10"/>
-      <c r="K173" s="8"/>
+      <c r="I173" s="8"/>
+      <c r="J173" s="8"/>
+      <c r="K173" s="9"/>
       <c r="L173" s="8"/>
+      <c r="M173" s="8"/>
     </row>
     <row r="174">
       <c r="A174" s="8"/>
@@ -2757,10 +2932,11 @@
       <c r="F174" s="8"/>
       <c r="G174" s="8"/>
       <c r="H174" s="8"/>
-      <c r="I174" s="9"/>
-      <c r="J174" s="10"/>
-      <c r="K174" s="8"/>
+      <c r="I174" s="8"/>
+      <c r="J174" s="8"/>
+      <c r="K174" s="9"/>
       <c r="L174" s="8"/>
+      <c r="M174" s="8"/>
     </row>
     <row r="175">
       <c r="A175" s="8"/>
@@ -2771,10 +2947,11 @@
       <c r="F175" s="8"/>
       <c r="G175" s="8"/>
       <c r="H175" s="8"/>
-      <c r="I175" s="9"/>
-      <c r="J175" s="10"/>
-      <c r="K175" s="8"/>
+      <c r="I175" s="8"/>
+      <c r="J175" s="8"/>
+      <c r="K175" s="9"/>
       <c r="L175" s="8"/>
+      <c r="M175" s="8"/>
     </row>
     <row r="176">
       <c r="A176" s="8"/>
@@ -2785,10 +2962,11 @@
       <c r="F176" s="8"/>
       <c r="G176" s="8"/>
       <c r="H176" s="8"/>
-      <c r="I176" s="9"/>
-      <c r="J176" s="10"/>
-      <c r="K176" s="8"/>
+      <c r="I176" s="8"/>
+      <c r="J176" s="8"/>
+      <c r="K176" s="9"/>
       <c r="L176" s="8"/>
+      <c r="M176" s="8"/>
     </row>
     <row r="177">
       <c r="A177" s="8"/>
@@ -2799,10 +2977,11 @@
       <c r="F177" s="8"/>
       <c r="G177" s="8"/>
       <c r="H177" s="8"/>
-      <c r="I177" s="9"/>
-      <c r="J177" s="10"/>
-      <c r="K177" s="8"/>
+      <c r="I177" s="8"/>
+      <c r="J177" s="8"/>
+      <c r="K177" s="9"/>
       <c r="L177" s="8"/>
+      <c r="M177" s="8"/>
     </row>
     <row r="178">
       <c r="A178" s="8"/>
@@ -2813,10 +2992,11 @@
       <c r="F178" s="8"/>
       <c r="G178" s="8"/>
       <c r="H178" s="8"/>
-      <c r="I178" s="9"/>
-      <c r="J178" s="10"/>
-      <c r="K178" s="8"/>
+      <c r="I178" s="8"/>
+      <c r="J178" s="8"/>
+      <c r="K178" s="9"/>
       <c r="L178" s="8"/>
+      <c r="M178" s="8"/>
     </row>
     <row r="179">
       <c r="A179" s="8"/>
@@ -2827,10 +3007,11 @@
       <c r="F179" s="8"/>
       <c r="G179" s="8"/>
       <c r="H179" s="8"/>
-      <c r="I179" s="9"/>
-      <c r="J179" s="10"/>
-      <c r="K179" s="8"/>
+      <c r="I179" s="8"/>
+      <c r="J179" s="8"/>
+      <c r="K179" s="9"/>
       <c r="L179" s="8"/>
+      <c r="M179" s="8"/>
     </row>
     <row r="180">
       <c r="A180" s="8"/>
@@ -2841,10 +3022,11 @@
       <c r="F180" s="8"/>
       <c r="G180" s="8"/>
       <c r="H180" s="8"/>
-      <c r="I180" s="9"/>
-      <c r="J180" s="10"/>
-      <c r="K180" s="8"/>
+      <c r="I180" s="8"/>
+      <c r="J180" s="8"/>
+      <c r="K180" s="9"/>
       <c r="L180" s="8"/>
+      <c r="M180" s="8"/>
     </row>
     <row r="181">
       <c r="A181" s="8"/>
@@ -2855,10 +3037,11 @@
       <c r="F181" s="8"/>
       <c r="G181" s="8"/>
       <c r="H181" s="8"/>
-      <c r="I181" s="9"/>
-      <c r="J181" s="10"/>
-      <c r="K181" s="8"/>
+      <c r="I181" s="8"/>
+      <c r="J181" s="8"/>
+      <c r="K181" s="9"/>
       <c r="L181" s="8"/>
+      <c r="M181" s="8"/>
     </row>
     <row r="182">
       <c r="A182" s="8"/>
@@ -2869,10 +3052,11 @@
       <c r="F182" s="8"/>
       <c r="G182" s="8"/>
       <c r="H182" s="8"/>
-      <c r="I182" s="9"/>
-      <c r="J182" s="10"/>
-      <c r="K182" s="8"/>
+      <c r="I182" s="8"/>
+      <c r="J182" s="8"/>
+      <c r="K182" s="9"/>
       <c r="L182" s="8"/>
+      <c r="M182" s="8"/>
     </row>
     <row r="183">
       <c r="A183" s="8"/>
@@ -2883,10 +3067,11 @@
       <c r="F183" s="8"/>
       <c r="G183" s="8"/>
       <c r="H183" s="8"/>
-      <c r="I183" s="9"/>
-      <c r="J183" s="10"/>
-      <c r="K183" s="8"/>
+      <c r="I183" s="8"/>
+      <c r="J183" s="8"/>
+      <c r="K183" s="9"/>
       <c r="L183" s="8"/>
+      <c r="M183" s="8"/>
     </row>
     <row r="184">
       <c r="A184" s="8"/>
@@ -2897,10 +3082,11 @@
       <c r="F184" s="8"/>
       <c r="G184" s="8"/>
       <c r="H184" s="8"/>
-      <c r="I184" s="9"/>
-      <c r="J184" s="10"/>
-      <c r="K184" s="8"/>
+      <c r="I184" s="8"/>
+      <c r="J184" s="8"/>
+      <c r="K184" s="9"/>
       <c r="L184" s="8"/>
+      <c r="M184" s="8"/>
     </row>
     <row r="185">
       <c r="A185" s="8"/>
@@ -2911,10 +3097,11 @@
       <c r="F185" s="8"/>
       <c r="G185" s="8"/>
       <c r="H185" s="8"/>
-      <c r="I185" s="9"/>
-      <c r="J185" s="10"/>
-      <c r="K185" s="8"/>
+      <c r="I185" s="8"/>
+      <c r="J185" s="8"/>
+      <c r="K185" s="9"/>
       <c r="L185" s="8"/>
+      <c r="M185" s="8"/>
     </row>
     <row r="186">
       <c r="A186" s="8"/>
@@ -2925,10 +3112,11 @@
       <c r="F186" s="8"/>
       <c r="G186" s="8"/>
       <c r="H186" s="8"/>
-      <c r="I186" s="9"/>
-      <c r="J186" s="10"/>
-      <c r="K186" s="8"/>
+      <c r="I186" s="8"/>
+      <c r="J186" s="8"/>
+      <c r="K186" s="9"/>
       <c r="L186" s="8"/>
+      <c r="M186" s="8"/>
     </row>
     <row r="187">
       <c r="A187" s="8"/>
@@ -2939,10 +3127,11 @@
       <c r="F187" s="8"/>
       <c r="G187" s="8"/>
       <c r="H187" s="8"/>
-      <c r="I187" s="9"/>
-      <c r="J187" s="10"/>
-      <c r="K187" s="8"/>
+      <c r="I187" s="8"/>
+      <c r="J187" s="8"/>
+      <c r="K187" s="9"/>
       <c r="L187" s="8"/>
+      <c r="M187" s="8"/>
     </row>
     <row r="188">
       <c r="A188" s="8"/>
@@ -2953,10 +3142,11 @@
       <c r="F188" s="8"/>
       <c r="G188" s="8"/>
       <c r="H188" s="8"/>
-      <c r="I188" s="9"/>
-      <c r="J188" s="10"/>
-      <c r="K188" s="8"/>
+      <c r="I188" s="8"/>
+      <c r="J188" s="8"/>
+      <c r="K188" s="9"/>
       <c r="L188" s="8"/>
+      <c r="M188" s="8"/>
     </row>
     <row r="189">
       <c r="A189" s="8"/>
@@ -2967,10 +3157,11 @@
       <c r="F189" s="8"/>
       <c r="G189" s="8"/>
       <c r="H189" s="8"/>
-      <c r="I189" s="9"/>
-      <c r="J189" s="10"/>
-      <c r="K189" s="8"/>
+      <c r="I189" s="8"/>
+      <c r="J189" s="8"/>
+      <c r="K189" s="9"/>
       <c r="L189" s="8"/>
+      <c r="M189" s="8"/>
     </row>
     <row r="190">
       <c r="A190" s="8"/>
@@ -2981,10 +3172,11 @@
       <c r="F190" s="8"/>
       <c r="G190" s="8"/>
       <c r="H190" s="8"/>
-      <c r="I190" s="9"/>
-      <c r="J190" s="10"/>
-      <c r="K190" s="8"/>
+      <c r="I190" s="8"/>
+      <c r="J190" s="8"/>
+      <c r="K190" s="9"/>
       <c r="L190" s="8"/>
+      <c r="M190" s="8"/>
     </row>
     <row r="191">
       <c r="A191" s="8"/>
@@ -2995,10 +3187,11 @@
       <c r="F191" s="8"/>
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
-      <c r="I191" s="9"/>
-      <c r="J191" s="10"/>
-      <c r="K191" s="8"/>
+      <c r="I191" s="8"/>
+      <c r="J191" s="8"/>
+      <c r="K191" s="9"/>
       <c r="L191" s="8"/>
+      <c r="M191" s="8"/>
     </row>
     <row r="192">
       <c r="A192" s="8"/>
@@ -3009,10 +3202,11 @@
       <c r="F192" s="8"/>
       <c r="G192" s="8"/>
       <c r="H192" s="8"/>
-      <c r="I192" s="9"/>
-      <c r="J192" s="10"/>
-      <c r="K192" s="8"/>
+      <c r="I192" s="8"/>
+      <c r="J192" s="8"/>
+      <c r="K192" s="9"/>
       <c r="L192" s="8"/>
+      <c r="M192" s="8"/>
     </row>
     <row r="193">
       <c r="A193" s="8"/>
@@ -3023,10 +3217,11 @@
       <c r="F193" s="8"/>
       <c r="G193" s="8"/>
       <c r="H193" s="8"/>
-      <c r="I193" s="9"/>
-      <c r="J193" s="10"/>
-      <c r="K193" s="8"/>
+      <c r="I193" s="8"/>
+      <c r="J193" s="8"/>
+      <c r="K193" s="9"/>
       <c r="L193" s="8"/>
+      <c r="M193" s="8"/>
     </row>
     <row r="194">
       <c r="A194" s="8"/>
@@ -3037,10 +3232,11 @@
       <c r="F194" s="8"/>
       <c r="G194" s="8"/>
       <c r="H194" s="8"/>
-      <c r="I194" s="9"/>
-      <c r="J194" s="10"/>
-      <c r="K194" s="8"/>
+      <c r="I194" s="8"/>
+      <c r="J194" s="8"/>
+      <c r="K194" s="9"/>
       <c r="L194" s="8"/>
+      <c r="M194" s="8"/>
     </row>
     <row r="195">
       <c r="A195" s="8"/>
@@ -3051,10 +3247,11 @@
       <c r="F195" s="8"/>
       <c r="G195" s="8"/>
       <c r="H195" s="8"/>
-      <c r="I195" s="9"/>
-      <c r="J195" s="10"/>
-      <c r="K195" s="8"/>
+      <c r="I195" s="8"/>
+      <c r="J195" s="8"/>
+      <c r="K195" s="9"/>
       <c r="L195" s="8"/>
+      <c r="M195" s="8"/>
     </row>
     <row r="196">
       <c r="A196" s="8"/>
@@ -3065,10 +3262,11 @@
       <c r="F196" s="8"/>
       <c r="G196" s="8"/>
       <c r="H196" s="8"/>
-      <c r="I196" s="9"/>
-      <c r="J196" s="10"/>
-      <c r="K196" s="8"/>
+      <c r="I196" s="8"/>
+      <c r="J196" s="8"/>
+      <c r="K196" s="9"/>
       <c r="L196" s="8"/>
+      <c r="M196" s="8"/>
     </row>
     <row r="197">
       <c r="A197" s="8"/>
@@ -3079,10 +3277,11 @@
       <c r="F197" s="8"/>
       <c r="G197" s="8"/>
       <c r="H197" s="8"/>
-      <c r="I197" s="9"/>
-      <c r="J197" s="10"/>
-      <c r="K197" s="8"/>
+      <c r="I197" s="8"/>
+      <c r="J197" s="8"/>
+      <c r="K197" s="9"/>
       <c r="L197" s="8"/>
+      <c r="M197" s="8"/>
     </row>
     <row r="198">
       <c r="A198" s="8"/>
@@ -3093,10 +3292,11 @@
       <c r="F198" s="8"/>
       <c r="G198" s="8"/>
       <c r="H198" s="8"/>
-      <c r="I198" s="9"/>
-      <c r="J198" s="10"/>
-      <c r="K198" s="8"/>
+      <c r="I198" s="8"/>
+      <c r="J198" s="8"/>
+      <c r="K198" s="9"/>
       <c r="L198" s="8"/>
+      <c r="M198" s="8"/>
     </row>
     <row r="199">
       <c r="A199" s="8"/>
@@ -3107,10 +3307,11 @@
       <c r="F199" s="8"/>
       <c r="G199" s="8"/>
       <c r="H199" s="8"/>
-      <c r="I199" s="9"/>
-      <c r="J199" s="10"/>
-      <c r="K199" s="8"/>
+      <c r="I199" s="8"/>
+      <c r="J199" s="8"/>
+      <c r="K199" s="9"/>
       <c r="L199" s="8"/>
+      <c r="M199" s="8"/>
     </row>
     <row r="200">
       <c r="A200" s="8"/>
@@ -3121,10 +3322,11 @@
       <c r="F200" s="8"/>
       <c r="G200" s="8"/>
       <c r="H200" s="8"/>
-      <c r="I200" s="9"/>
-      <c r="J200" s="10"/>
-      <c r="K200" s="8"/>
+      <c r="I200" s="8"/>
+      <c r="J200" s="8"/>
+      <c r="K200" s="9"/>
       <c r="L200" s="8"/>
+      <c r="M200" s="8"/>
     </row>
     <row r="201">
       <c r="A201" s="8"/>
@@ -3135,10 +3337,11 @@
       <c r="F201" s="8"/>
       <c r="G201" s="8"/>
       <c r="H201" s="8"/>
-      <c r="I201" s="9"/>
-      <c r="J201" s="10"/>
-      <c r="K201" s="8"/>
+      <c r="I201" s="8"/>
+      <c r="J201" s="8"/>
+      <c r="K201" s="9"/>
       <c r="L201" s="8"/>
+      <c r="M201" s="8"/>
     </row>
     <row r="202">
       <c r="A202" s="8"/>
@@ -3149,10 +3352,11 @@
       <c r="F202" s="8"/>
       <c r="G202" s="8"/>
       <c r="H202" s="8"/>
-      <c r="I202" s="9"/>
-      <c r="J202" s="10"/>
-      <c r="K202" s="8"/>
+      <c r="I202" s="8"/>
+      <c r="J202" s="8"/>
+      <c r="K202" s="9"/>
       <c r="L202" s="8"/>
+      <c r="M202" s="8"/>
     </row>
     <row r="203">
       <c r="A203" s="8"/>
@@ -3163,10 +3367,11 @@
       <c r="F203" s="8"/>
       <c r="G203" s="8"/>
       <c r="H203" s="8"/>
-      <c r="I203" s="9"/>
-      <c r="J203" s="10"/>
-      <c r="K203" s="8"/>
+      <c r="I203" s="8"/>
+      <c r="J203" s="8"/>
+      <c r="K203" s="9"/>
       <c r="L203" s="8"/>
+      <c r="M203" s="8"/>
     </row>
     <row r="204">
       <c r="A204" s="8"/>
@@ -3177,10 +3382,11 @@
       <c r="F204" s="8"/>
       <c r="G204" s="8"/>
       <c r="H204" s="8"/>
-      <c r="I204" s="9"/>
-      <c r="J204" s="10"/>
-      <c r="K204" s="8"/>
+      <c r="I204" s="8"/>
+      <c r="J204" s="8"/>
+      <c r="K204" s="9"/>
       <c r="L204" s="8"/>
+      <c r="M204" s="8"/>
     </row>
     <row r="205">
       <c r="A205" s="8"/>
@@ -3191,10 +3397,11 @@
       <c r="F205" s="8"/>
       <c r="G205" s="8"/>
       <c r="H205" s="8"/>
-      <c r="I205" s="9"/>
-      <c r="J205" s="10"/>
-      <c r="K205" s="8"/>
+      <c r="I205" s="8"/>
+      <c r="J205" s="8"/>
+      <c r="K205" s="9"/>
       <c r="L205" s="8"/>
+      <c r="M205" s="8"/>
     </row>
     <row r="206">
       <c r="A206" s="8"/>
@@ -3205,10 +3412,11 @@
       <c r="F206" s="8"/>
       <c r="G206" s="8"/>
       <c r="H206" s="8"/>
-      <c r="I206" s="9"/>
-      <c r="J206" s="10"/>
-      <c r="K206" s="8"/>
+      <c r="I206" s="8"/>
+      <c r="J206" s="8"/>
+      <c r="K206" s="9"/>
       <c r="L206" s="8"/>
+      <c r="M206" s="8"/>
     </row>
     <row r="207">
       <c r="A207" s="8"/>
@@ -3219,10 +3427,11 @@
       <c r="F207" s="8"/>
       <c r="G207" s="8"/>
       <c r="H207" s="8"/>
-      <c r="I207" s="9"/>
-      <c r="J207" s="10"/>
-      <c r="K207" s="8"/>
+      <c r="I207" s="8"/>
+      <c r="J207" s="8"/>
+      <c r="K207" s="9"/>
       <c r="L207" s="8"/>
+      <c r="M207" s="8"/>
     </row>
     <row r="208">
       <c r="A208" s="8"/>
@@ -3233,10 +3442,11 @@
       <c r="F208" s="8"/>
       <c r="G208" s="8"/>
       <c r="H208" s="8"/>
-      <c r="I208" s="9"/>
-      <c r="J208" s="10"/>
-      <c r="K208" s="8"/>
+      <c r="I208" s="8"/>
+      <c r="J208" s="8"/>
+      <c r="K208" s="9"/>
       <c r="L208" s="8"/>
+      <c r="M208" s="8"/>
     </row>
     <row r="209">
       <c r="A209" s="8"/>
@@ -3247,10 +3457,11 @@
       <c r="F209" s="8"/>
       <c r="G209" s="8"/>
       <c r="H209" s="8"/>
-      <c r="I209" s="9"/>
-      <c r="J209" s="10"/>
-      <c r="K209" s="8"/>
+      <c r="I209" s="8"/>
+      <c r="J209" s="8"/>
+      <c r="K209" s="9"/>
       <c r="L209" s="8"/>
+      <c r="M209" s="8"/>
     </row>
     <row r="210">
       <c r="A210" s="8"/>
@@ -3261,10 +3472,11 @@
       <c r="F210" s="8"/>
       <c r="G210" s="8"/>
       <c r="H210" s="8"/>
-      <c r="I210" s="9"/>
-      <c r="J210" s="10"/>
-      <c r="K210" s="8"/>
+      <c r="I210" s="8"/>
+      <c r="J210" s="8"/>
+      <c r="K210" s="9"/>
       <c r="L210" s="8"/>
+      <c r="M210" s="8"/>
     </row>
     <row r="211">
       <c r="A211" s="8"/>
@@ -3275,10 +3487,11 @@
       <c r="F211" s="8"/>
       <c r="G211" s="8"/>
       <c r="H211" s="8"/>
-      <c r="I211" s="9"/>
-      <c r="J211" s="10"/>
-      <c r="K211" s="8"/>
+      <c r="I211" s="8"/>
+      <c r="J211" s="8"/>
+      <c r="K211" s="9"/>
       <c r="L211" s="8"/>
+      <c r="M211" s="8"/>
     </row>
     <row r="212">
       <c r="A212" s="8"/>
@@ -3289,10 +3502,11 @@
       <c r="F212" s="8"/>
       <c r="G212" s="8"/>
       <c r="H212" s="8"/>
-      <c r="I212" s="9"/>
-      <c r="J212" s="10"/>
-      <c r="K212" s="8"/>
+      <c r="I212" s="8"/>
+      <c r="J212" s="8"/>
+      <c r="K212" s="9"/>
       <c r="L212" s="8"/>
+      <c r="M212" s="8"/>
     </row>
     <row r="213">
       <c r="A213" s="8"/>
@@ -3303,10 +3517,11 @@
       <c r="F213" s="8"/>
       <c r="G213" s="8"/>
       <c r="H213" s="8"/>
-      <c r="I213" s="9"/>
-      <c r="J213" s="10"/>
-      <c r="K213" s="8"/>
+      <c r="I213" s="8"/>
+      <c r="J213" s="8"/>
+      <c r="K213" s="9"/>
       <c r="L213" s="8"/>
+      <c r="M213" s="8"/>
     </row>
     <row r="214">
       <c r="A214" s="8"/>
@@ -3317,10 +3532,11 @@
       <c r="F214" s="8"/>
       <c r="G214" s="8"/>
       <c r="H214" s="8"/>
-      <c r="I214" s="9"/>
-      <c r="J214" s="10"/>
-      <c r="K214" s="8"/>
+      <c r="I214" s="8"/>
+      <c r="J214" s="8"/>
+      <c r="K214" s="9"/>
       <c r="L214" s="8"/>
+      <c r="M214" s="8"/>
     </row>
     <row r="215">
       <c r="A215" s="8"/>
@@ -3331,10 +3547,11 @@
       <c r="F215" s="8"/>
       <c r="G215" s="8"/>
       <c r="H215" s="8"/>
-      <c r="I215" s="9"/>
-      <c r="J215" s="10"/>
-      <c r="K215" s="8"/>
+      <c r="I215" s="8"/>
+      <c r="J215" s="8"/>
+      <c r="K215" s="9"/>
       <c r="L215" s="8"/>
+      <c r="M215" s="8"/>
     </row>
     <row r="216">
       <c r="A216" s="8"/>
@@ -3345,10 +3562,11 @@
       <c r="F216" s="8"/>
       <c r="G216" s="8"/>
       <c r="H216" s="8"/>
-      <c r="I216" s="9"/>
-      <c r="J216" s="10"/>
-      <c r="K216" s="8"/>
+      <c r="I216" s="8"/>
+      <c r="J216" s="8"/>
+      <c r="K216" s="9"/>
       <c r="L216" s="8"/>
+      <c r="M216" s="8"/>
     </row>
     <row r="217">
       <c r="A217" s="8"/>
@@ -3359,10 +3577,11 @@
       <c r="F217" s="8"/>
       <c r="G217" s="8"/>
       <c r="H217" s="8"/>
-      <c r="I217" s="9"/>
-      <c r="J217" s="10"/>
-      <c r="K217" s="8"/>
+      <c r="I217" s="8"/>
+      <c r="J217" s="8"/>
+      <c r="K217" s="9"/>
       <c r="L217" s="8"/>
+      <c r="M217" s="8"/>
     </row>
     <row r="218">
       <c r="A218" s="8"/>
@@ -3373,10 +3592,11 @@
       <c r="F218" s="8"/>
       <c r="G218" s="8"/>
       <c r="H218" s="8"/>
-      <c r="I218" s="9"/>
-      <c r="J218" s="10"/>
-      <c r="K218" s="8"/>
+      <c r="I218" s="8"/>
+      <c r="J218" s="8"/>
+      <c r="K218" s="9"/>
       <c r="L218" s="8"/>
+      <c r="M218" s="8"/>
     </row>
     <row r="219">
       <c r="A219" s="8"/>
@@ -3387,10 +3607,11 @@
       <c r="F219" s="8"/>
       <c r="G219" s="8"/>
       <c r="H219" s="8"/>
-      <c r="I219" s="9"/>
-      <c r="J219" s="10"/>
-      <c r="K219" s="8"/>
+      <c r="I219" s="8"/>
+      <c r="J219" s="8"/>
+      <c r="K219" s="9"/>
       <c r="L219" s="8"/>
+      <c r="M219" s="8"/>
     </row>
     <row r="220">
       <c r="A220" s="8"/>
@@ -3401,10 +3622,11 @@
       <c r="F220" s="8"/>
       <c r="G220" s="8"/>
       <c r="H220" s="8"/>
-      <c r="I220" s="9"/>
-      <c r="J220" s="10"/>
-      <c r="K220" s="8"/>
+      <c r="I220" s="8"/>
+      <c r="J220" s="8"/>
+      <c r="K220" s="9"/>
       <c r="L220" s="8"/>
+      <c r="M220" s="8"/>
     </row>
     <row r="221">
       <c r="A221" s="8"/>
@@ -3415,10 +3637,11 @@
       <c r="F221" s="8"/>
       <c r="G221" s="8"/>
       <c r="H221" s="8"/>
-      <c r="I221" s="9"/>
-      <c r="J221" s="10"/>
-      <c r="K221" s="8"/>
+      <c r="I221" s="8"/>
+      <c r="J221" s="8"/>
+      <c r="K221" s="9"/>
       <c r="L221" s="8"/>
+      <c r="M221" s="8"/>
     </row>
     <row r="222">
       <c r="A222" s="8"/>
@@ -3429,10 +3652,11 @@
       <c r="F222" s="8"/>
       <c r="G222" s="8"/>
       <c r="H222" s="8"/>
-      <c r="I222" s="9"/>
-      <c r="J222" s="10"/>
-      <c r="K222" s="8"/>
+      <c r="I222" s="8"/>
+      <c r="J222" s="8"/>
+      <c r="K222" s="9"/>
       <c r="L222" s="8"/>
+      <c r="M222" s="8"/>
     </row>
     <row r="223">
       <c r="A223" s="8"/>
@@ -3443,10 +3667,11 @@
       <c r="F223" s="8"/>
       <c r="G223" s="8"/>
       <c r="H223" s="8"/>
-      <c r="I223" s="9"/>
-      <c r="J223" s="10"/>
-      <c r="K223" s="8"/>
+      <c r="I223" s="8"/>
+      <c r="J223" s="8"/>
+      <c r="K223" s="9"/>
       <c r="L223" s="8"/>
+      <c r="M223" s="8"/>
     </row>
     <row r="224">
       <c r="A224" s="8"/>
@@ -3457,10 +3682,11 @@
       <c r="F224" s="8"/>
       <c r="G224" s="8"/>
       <c r="H224" s="8"/>
-      <c r="I224" s="9"/>
-      <c r="J224" s="10"/>
-      <c r="K224" s="8"/>
+      <c r="I224" s="8"/>
+      <c r="J224" s="8"/>
+      <c r="K224" s="9"/>
       <c r="L224" s="8"/>
+      <c r="M224" s="8"/>
     </row>
     <row r="225">
       <c r="A225" s="8"/>
@@ -3471,10 +3697,11 @@
       <c r="F225" s="8"/>
       <c r="G225" s="8"/>
       <c r="H225" s="8"/>
-      <c r="I225" s="9"/>
-      <c r="J225" s="10"/>
-      <c r="K225" s="8"/>
+      <c r="I225" s="8"/>
+      <c r="J225" s="8"/>
+      <c r="K225" s="9"/>
       <c r="L225" s="8"/>
+      <c r="M225" s="8"/>
     </row>
     <row r="226">
       <c r="A226" s="8"/>
@@ -3485,10 +3712,11 @@
       <c r="F226" s="8"/>
       <c r="G226" s="8"/>
       <c r="H226" s="8"/>
-      <c r="I226" s="9"/>
-      <c r="J226" s="10"/>
-      <c r="K226" s="8"/>
+      <c r="I226" s="8"/>
+      <c r="J226" s="8"/>
+      <c r="K226" s="9"/>
       <c r="L226" s="8"/>
+      <c r="M226" s="8"/>
     </row>
     <row r="227">
       <c r="A227" s="8"/>
@@ -3499,10 +3727,11 @@
       <c r="F227" s="8"/>
       <c r="G227" s="8"/>
       <c r="H227" s="8"/>
-      <c r="I227" s="9"/>
-      <c r="J227" s="10"/>
-      <c r="K227" s="8"/>
+      <c r="I227" s="8"/>
+      <c r="J227" s="8"/>
+      <c r="K227" s="9"/>
       <c r="L227" s="8"/>
+      <c r="M227" s="8"/>
     </row>
     <row r="228">
       <c r="A228" s="8"/>
@@ -3513,10 +3742,11 @@
       <c r="F228" s="8"/>
       <c r="G228" s="8"/>
       <c r="H228" s="8"/>
-      <c r="I228" s="9"/>
-      <c r="J228" s="10"/>
-      <c r="K228" s="8"/>
+      <c r="I228" s="8"/>
+      <c r="J228" s="8"/>
+      <c r="K228" s="9"/>
       <c r="L228" s="8"/>
+      <c r="M228" s="8"/>
     </row>
     <row r="229">
       <c r="A229" s="8"/>
@@ -3527,10 +3757,11 @@
       <c r="F229" s="8"/>
       <c r="G229" s="8"/>
       <c r="H229" s="8"/>
-      <c r="I229" s="9"/>
-      <c r="J229" s="10"/>
-      <c r="K229" s="8"/>
+      <c r="I229" s="8"/>
+      <c r="J229" s="8"/>
+      <c r="K229" s="9"/>
       <c r="L229" s="8"/>
+      <c r="M229" s="8"/>
     </row>
     <row r="230">
       <c r="A230" s="8"/>
@@ -3541,10 +3772,11 @@
       <c r="F230" s="8"/>
       <c r="G230" s="8"/>
       <c r="H230" s="8"/>
-      <c r="I230" s="9"/>
-      <c r="J230" s="10"/>
-      <c r="K230" s="8"/>
+      <c r="I230" s="8"/>
+      <c r="J230" s="8"/>
+      <c r="K230" s="9"/>
       <c r="L230" s="8"/>
+      <c r="M230" s="8"/>
     </row>
     <row r="231">
       <c r="A231" s="8"/>
@@ -3555,10 +3787,11 @@
       <c r="F231" s="8"/>
       <c r="G231" s="8"/>
       <c r="H231" s="8"/>
-      <c r="I231" s="9"/>
-      <c r="J231" s="10"/>
-      <c r="K231" s="8"/>
+      <c r="I231" s="8"/>
+      <c r="J231" s="8"/>
+      <c r="K231" s="9"/>
       <c r="L231" s="8"/>
+      <c r="M231" s="8"/>
     </row>
     <row r="232">
       <c r="A232" s="8"/>
@@ -3569,10 +3802,11 @@
       <c r="F232" s="8"/>
       <c r="G232" s="8"/>
       <c r="H232" s="8"/>
-      <c r="I232" s="9"/>
-      <c r="J232" s="10"/>
-      <c r="K232" s="8"/>
+      <c r="I232" s="8"/>
+      <c r="J232" s="8"/>
+      <c r="K232" s="9"/>
       <c r="L232" s="8"/>
+      <c r="M232" s="8"/>
     </row>
     <row r="233">
       <c r="A233" s="8"/>
@@ -3583,10 +3817,11 @@
       <c r="F233" s="8"/>
       <c r="G233" s="8"/>
       <c r="H233" s="8"/>
-      <c r="I233" s="9"/>
-      <c r="J233" s="10"/>
-      <c r="K233" s="8"/>
+      <c r="I233" s="8"/>
+      <c r="J233" s="8"/>
+      <c r="K233" s="9"/>
       <c r="L233" s="8"/>
+      <c r="M233" s="8"/>
     </row>
     <row r="234">
       <c r="A234" s="8"/>
@@ -3597,10 +3832,11 @@
       <c r="F234" s="8"/>
       <c r="G234" s="8"/>
       <c r="H234" s="8"/>
-      <c r="I234" s="9"/>
-      <c r="J234" s="10"/>
-      <c r="K234" s="8"/>
+      <c r="I234" s="8"/>
+      <c r="J234" s="8"/>
+      <c r="K234" s="9"/>
       <c r="L234" s="8"/>
+      <c r="M234" s="8"/>
     </row>
     <row r="235">
       <c r="A235" s="8"/>
@@ -3611,10 +3847,11 @@
       <c r="F235" s="8"/>
       <c r="G235" s="8"/>
       <c r="H235" s="8"/>
-      <c r="I235" s="9"/>
-      <c r="J235" s="10"/>
-      <c r="K235" s="8"/>
+      <c r="I235" s="8"/>
+      <c r="J235" s="8"/>
+      <c r="K235" s="9"/>
       <c r="L235" s="8"/>
+      <c r="M235" s="8"/>
     </row>
     <row r="236">
       <c r="A236" s="8"/>
@@ -3625,10 +3862,11 @@
       <c r="F236" s="8"/>
       <c r="G236" s="8"/>
       <c r="H236" s="8"/>
-      <c r="I236" s="9"/>
-      <c r="J236" s="10"/>
-      <c r="K236" s="8"/>
+      <c r="I236" s="8"/>
+      <c r="J236" s="8"/>
+      <c r="K236" s="9"/>
       <c r="L236" s="8"/>
+      <c r="M236" s="8"/>
     </row>
     <row r="237">
       <c r="A237" s="8"/>
@@ -3639,10 +3877,11 @@
       <c r="F237" s="8"/>
       <c r="G237" s="8"/>
       <c r="H237" s="8"/>
-      <c r="I237" s="9"/>
-      <c r="J237" s="10"/>
-      <c r="K237" s="8"/>
+      <c r="I237" s="8"/>
+      <c r="J237" s="8"/>
+      <c r="K237" s="9"/>
       <c r="L237" s="8"/>
+      <c r="M237" s="8"/>
     </row>
     <row r="238">
       <c r="A238" s="8"/>
@@ -3653,10 +3892,11 @@
       <c r="F238" s="8"/>
       <c r="G238" s="8"/>
       <c r="H238" s="8"/>
-      <c r="I238" s="9"/>
-      <c r="J238" s="10"/>
-      <c r="K238" s="8"/>
+      <c r="I238" s="8"/>
+      <c r="J238" s="8"/>
+      <c r="K238" s="9"/>
       <c r="L238" s="8"/>
+      <c r="M238" s="8"/>
     </row>
     <row r="239">
       <c r="A239" s="8"/>
@@ -3667,10 +3907,11 @@
       <c r="F239" s="8"/>
       <c r="G239" s="8"/>
       <c r="H239" s="8"/>
-      <c r="I239" s="9"/>
-      <c r="J239" s="10"/>
-      <c r="K239" s="8"/>
+      <c r="I239" s="8"/>
+      <c r="J239" s="8"/>
+      <c r="K239" s="9"/>
       <c r="L239" s="8"/>
+      <c r="M239" s="8"/>
     </row>
     <row r="240">
       <c r="A240" s="8"/>
@@ -3681,10 +3922,11 @@
       <c r="F240" s="8"/>
       <c r="G240" s="8"/>
       <c r="H240" s="8"/>
-      <c r="I240" s="9"/>
-      <c r="J240" s="10"/>
-      <c r="K240" s="8"/>
+      <c r="I240" s="8"/>
+      <c r="J240" s="8"/>
+      <c r="K240" s="9"/>
       <c r="L240" s="8"/>
+      <c r="M240" s="8"/>
     </row>
     <row r="241">
       <c r="A241" s="8"/>
@@ -3695,10 +3937,11 @@
       <c r="F241" s="8"/>
       <c r="G241" s="8"/>
       <c r="H241" s="8"/>
-      <c r="I241" s="9"/>
-      <c r="J241" s="10"/>
-      <c r="K241" s="8"/>
+      <c r="I241" s="8"/>
+      <c r="J241" s="8"/>
+      <c r="K241" s="9"/>
       <c r="L241" s="8"/>
+      <c r="M241" s="8"/>
     </row>
     <row r="242">
       <c r="A242" s="8"/>
@@ -3709,10 +3952,11 @@
       <c r="F242" s="8"/>
       <c r="G242" s="8"/>
       <c r="H242" s="8"/>
-      <c r="I242" s="9"/>
-      <c r="J242" s="10"/>
-      <c r="K242" s="8"/>
+      <c r="I242" s="8"/>
+      <c r="J242" s="8"/>
+      <c r="K242" s="9"/>
       <c r="L242" s="8"/>
+      <c r="M242" s="8"/>
     </row>
     <row r="243">
       <c r="A243" s="8"/>
@@ -3723,10 +3967,11 @@
       <c r="F243" s="8"/>
       <c r="G243" s="8"/>
       <c r="H243" s="8"/>
-      <c r="I243" s="9"/>
-      <c r="J243" s="10"/>
-      <c r="K243" s="8"/>
+      <c r="I243" s="8"/>
+      <c r="J243" s="8"/>
+      <c r="K243" s="9"/>
       <c r="L243" s="8"/>
+      <c r="M243" s="8"/>
     </row>
     <row r="244">
       <c r="A244" s="8"/>
@@ -3737,10 +3982,11 @@
       <c r="F244" s="8"/>
       <c r="G244" s="8"/>
       <c r="H244" s="8"/>
-      <c r="I244" s="9"/>
-      <c r="J244" s="10"/>
-      <c r="K244" s="8"/>
+      <c r="I244" s="8"/>
+      <c r="J244" s="8"/>
+      <c r="K244" s="9"/>
       <c r="L244" s="8"/>
+      <c r="M244" s="8"/>
     </row>
     <row r="245">
       <c r="A245" s="8"/>
@@ -3751,10 +3997,11 @@
       <c r="F245" s="8"/>
       <c r="G245" s="8"/>
       <c r="H245" s="8"/>
-      <c r="I245" s="9"/>
-      <c r="J245" s="10"/>
-      <c r="K245" s="8"/>
+      <c r="I245" s="8"/>
+      <c r="J245" s="8"/>
+      <c r="K245" s="9"/>
       <c r="L245" s="8"/>
+      <c r="M245" s="8"/>
     </row>
     <row r="246">
       <c r="A246" s="8"/>
@@ -3765,10 +4012,11 @@
       <c r="F246" s="8"/>
       <c r="G246" s="8"/>
       <c r="H246" s="8"/>
-      <c r="I246" s="9"/>
-      <c r="J246" s="10"/>
-      <c r="K246" s="8"/>
+      <c r="I246" s="8"/>
+      <c r="J246" s="8"/>
+      <c r="K246" s="9"/>
       <c r="L246" s="8"/>
+      <c r="M246" s="8"/>
     </row>
     <row r="247">
       <c r="A247" s="8"/>
@@ -3779,10 +4027,11 @@
       <c r="F247" s="8"/>
       <c r="G247" s="8"/>
       <c r="H247" s="8"/>
-      <c r="I247" s="9"/>
-      <c r="J247" s="10"/>
-      <c r="K247" s="8"/>
+      <c r="I247" s="8"/>
+      <c r="J247" s="8"/>
+      <c r="K247" s="9"/>
       <c r="L247" s="8"/>
+      <c r="M247" s="8"/>
     </row>
     <row r="248">
       <c r="A248" s="8"/>
@@ -3793,10 +4042,11 @@
       <c r="F248" s="8"/>
       <c r="G248" s="8"/>
       <c r="H248" s="8"/>
-      <c r="I248" s="9"/>
-      <c r="J248" s="10"/>
-      <c r="K248" s="8"/>
+      <c r="I248" s="8"/>
+      <c r="J248" s="8"/>
+      <c r="K248" s="9"/>
       <c r="L248" s="8"/>
+      <c r="M248" s="8"/>
     </row>
     <row r="249">
       <c r="A249" s="8"/>
@@ -3807,10 +4057,11 @@
       <c r="F249" s="8"/>
       <c r="G249" s="8"/>
       <c r="H249" s="8"/>
-      <c r="I249" s="9"/>
-      <c r="J249" s="10"/>
-      <c r="K249" s="8"/>
+      <c r="I249" s="8"/>
+      <c r="J249" s="8"/>
+      <c r="K249" s="9"/>
       <c r="L249" s="8"/>
+      <c r="M249" s="8"/>
     </row>
     <row r="250">
       <c r="A250" s="8"/>
@@ -3821,10 +4072,11 @@
       <c r="F250" s="8"/>
       <c r="G250" s="8"/>
       <c r="H250" s="8"/>
-      <c r="I250" s="9"/>
-      <c r="J250" s="10"/>
-      <c r="K250" s="8"/>
+      <c r="I250" s="8"/>
+      <c r="J250" s="8"/>
+      <c r="K250" s="9"/>
       <c r="L250" s="8"/>
+      <c r="M250" s="8"/>
     </row>
     <row r="251">
       <c r="A251" s="8"/>
@@ -3835,10 +4087,11 @@
       <c r="F251" s="8"/>
       <c r="G251" s="8"/>
       <c r="H251" s="8"/>
-      <c r="I251" s="9"/>
-      <c r="J251" s="10"/>
-      <c r="K251" s="8"/>
+      <c r="I251" s="8"/>
+      <c r="J251" s="8"/>
+      <c r="K251" s="9"/>
       <c r="L251" s="8"/>
+      <c r="M251" s="8"/>
     </row>
     <row r="252">
       <c r="A252" s="8"/>
@@ -3849,10 +4102,11 @@
       <c r="F252" s="8"/>
       <c r="G252" s="8"/>
       <c r="H252" s="8"/>
-      <c r="I252" s="9"/>
-      <c r="J252" s="10"/>
-      <c r="K252" s="8"/>
+      <c r="I252" s="8"/>
+      <c r="J252" s="8"/>
+      <c r="K252" s="9"/>
       <c r="L252" s="8"/>
+      <c r="M252" s="8"/>
     </row>
     <row r="253">
       <c r="A253" s="8"/>
@@ -3863,10 +4117,11 @@
       <c r="F253" s="8"/>
       <c r="G253" s="8"/>
       <c r="H253" s="8"/>
-      <c r="I253" s="9"/>
-      <c r="J253" s="10"/>
-      <c r="K253" s="8"/>
+      <c r="I253" s="8"/>
+      <c r="J253" s="8"/>
+      <c r="K253" s="9"/>
       <c r="L253" s="8"/>
+      <c r="M253" s="8"/>
     </row>
     <row r="254">
       <c r="A254" s="8"/>
@@ -3877,10 +4132,11 @@
       <c r="F254" s="8"/>
       <c r="G254" s="8"/>
       <c r="H254" s="8"/>
-      <c r="I254" s="9"/>
-      <c r="J254" s="10"/>
-      <c r="K254" s="8"/>
+      <c r="I254" s="8"/>
+      <c r="J254" s="8"/>
+      <c r="K254" s="9"/>
       <c r="L254" s="8"/>
+      <c r="M254" s="8"/>
     </row>
     <row r="255">
       <c r="A255" s="8"/>
@@ -3891,10 +4147,11 @@
       <c r="F255" s="8"/>
       <c r="G255" s="8"/>
       <c r="H255" s="8"/>
-      <c r="I255" s="9"/>
-      <c r="J255" s="10"/>
-      <c r="K255" s="8"/>
+      <c r="I255" s="8"/>
+      <c r="J255" s="8"/>
+      <c r="K255" s="9"/>
       <c r="L255" s="8"/>
+      <c r="M255" s="8"/>
     </row>
     <row r="256">
       <c r="A256" s="8"/>
@@ -3905,10 +4162,11 @@
       <c r="F256" s="8"/>
       <c r="G256" s="8"/>
       <c r="H256" s="8"/>
-      <c r="I256" s="9"/>
-      <c r="J256" s="10"/>
-      <c r="K256" s="8"/>
+      <c r="I256" s="8"/>
+      <c r="J256" s="8"/>
+      <c r="K256" s="9"/>
       <c r="L256" s="8"/>
+      <c r="M256" s="8"/>
     </row>
     <row r="257">
       <c r="A257" s="8"/>
@@ -3919,10 +4177,11 @@
       <c r="F257" s="8"/>
       <c r="G257" s="8"/>
       <c r="H257" s="8"/>
-      <c r="I257" s="9"/>
-      <c r="J257" s="10"/>
-      <c r="K257" s="8"/>
+      <c r="I257" s="8"/>
+      <c r="J257" s="8"/>
+      <c r="K257" s="9"/>
       <c r="L257" s="8"/>
+      <c r="M257" s="8"/>
     </row>
     <row r="258">
       <c r="A258" s="8"/>
@@ -3933,10 +4192,11 @@
       <c r="F258" s="8"/>
       <c r="G258" s="8"/>
       <c r="H258" s="8"/>
-      <c r="I258" s="9"/>
-      <c r="J258" s="10"/>
-      <c r="K258" s="8"/>
+      <c r="I258" s="8"/>
+      <c r="J258" s="8"/>
+      <c r="K258" s="9"/>
       <c r="L258" s="8"/>
+      <c r="M258" s="8"/>
     </row>
     <row r="259">
       <c r="A259" s="8"/>
@@ -3947,10 +4207,11 @@
       <c r="F259" s="8"/>
       <c r="G259" s="8"/>
       <c r="H259" s="8"/>
-      <c r="I259" s="9"/>
-      <c r="J259" s="10"/>
-      <c r="K259" s="8"/>
+      <c r="I259" s="8"/>
+      <c r="J259" s="8"/>
+      <c r="K259" s="9"/>
       <c r="L259" s="8"/>
+      <c r="M259" s="8"/>
     </row>
     <row r="260">
       <c r="A260" s="8"/>
@@ -3961,10 +4222,11 @@
       <c r="F260" s="8"/>
       <c r="G260" s="8"/>
       <c r="H260" s="8"/>
-      <c r="I260" s="9"/>
-      <c r="J260" s="10"/>
-      <c r="K260" s="8"/>
+      <c r="I260" s="8"/>
+      <c r="J260" s="8"/>
+      <c r="K260" s="9"/>
       <c r="L260" s="8"/>
+      <c r="M260" s="8"/>
     </row>
     <row r="261">
       <c r="A261" s="8"/>
@@ -3975,10 +4237,11 @@
       <c r="F261" s="8"/>
       <c r="G261" s="8"/>
       <c r="H261" s="8"/>
-      <c r="I261" s="9"/>
-      <c r="J261" s="10"/>
-      <c r="K261" s="8"/>
+      <c r="I261" s="8"/>
+      <c r="J261" s="8"/>
+      <c r="K261" s="9"/>
       <c r="L261" s="8"/>
+      <c r="M261" s="8"/>
     </row>
     <row r="262">
       <c r="A262" s="8"/>
@@ -3989,10 +4252,11 @@
       <c r="F262" s="8"/>
       <c r="G262" s="8"/>
       <c r="H262" s="8"/>
-      <c r="I262" s="9"/>
-      <c r="J262" s="10"/>
-      <c r="K262" s="8"/>
+      <c r="I262" s="8"/>
+      <c r="J262" s="8"/>
+      <c r="K262" s="9"/>
       <c r="L262" s="8"/>
+      <c r="M262" s="8"/>
     </row>
     <row r="263">
       <c r="A263" s="8"/>
@@ -4003,10 +4267,11 @@
       <c r="F263" s="8"/>
       <c r="G263" s="8"/>
       <c r="H263" s="8"/>
-      <c r="I263" s="9"/>
-      <c r="J263" s="10"/>
-      <c r="K263" s="8"/>
+      <c r="I263" s="8"/>
+      <c r="J263" s="8"/>
+      <c r="K263" s="9"/>
       <c r="L263" s="8"/>
+      <c r="M263" s="8"/>
     </row>
     <row r="264">
       <c r="A264" s="8"/>
@@ -4017,10 +4282,11 @@
       <c r="F264" s="8"/>
       <c r="G264" s="8"/>
       <c r="H264" s="8"/>
-      <c r="I264" s="9"/>
-      <c r="J264" s="10"/>
-      <c r="K264" s="8"/>
+      <c r="I264" s="8"/>
+      <c r="J264" s="8"/>
+      <c r="K264" s="9"/>
       <c r="L264" s="8"/>
+      <c r="M264" s="8"/>
     </row>
     <row r="265">
       <c r="A265" s="8"/>
@@ -4031,10 +4297,11 @@
       <c r="F265" s="8"/>
       <c r="G265" s="8"/>
       <c r="H265" s="8"/>
-      <c r="I265" s="9"/>
-      <c r="J265" s="10"/>
-      <c r="K265" s="8"/>
+      <c r="I265" s="8"/>
+      <c r="J265" s="8"/>
+      <c r="K265" s="9"/>
       <c r="L265" s="8"/>
+      <c r="M265" s="8"/>
     </row>
     <row r="266">
       <c r="A266" s="8"/>
@@ -4045,10 +4312,11 @@
       <c r="F266" s="8"/>
       <c r="G266" s="8"/>
       <c r="H266" s="8"/>
-      <c r="I266" s="9"/>
-      <c r="J266" s="10"/>
-      <c r="K266" s="8"/>
+      <c r="I266" s="8"/>
+      <c r="J266" s="8"/>
+      <c r="K266" s="9"/>
       <c r="L266" s="8"/>
+      <c r="M266" s="8"/>
     </row>
     <row r="267">
       <c r="A267" s="8"/>
@@ -4059,10 +4327,11 @@
       <c r="F267" s="8"/>
       <c r="G267" s="8"/>
       <c r="H267" s="8"/>
-      <c r="I267" s="9"/>
-      <c r="J267" s="10"/>
-      <c r="K267" s="8"/>
+      <c r="I267" s="8"/>
+      <c r="J267" s="8"/>
+      <c r="K267" s="9"/>
       <c r="L267" s="8"/>
+      <c r="M267" s="8"/>
     </row>
     <row r="268">
       <c r="A268" s="8"/>
@@ -4073,10 +4342,11 @@
       <c r="F268" s="8"/>
       <c r="G268" s="8"/>
       <c r="H268" s="8"/>
-      <c r="I268" s="9"/>
-      <c r="J268" s="10"/>
-      <c r="K268" s="8"/>
+      <c r="I268" s="8"/>
+      <c r="J268" s="8"/>
+      <c r="K268" s="9"/>
       <c r="L268" s="8"/>
+      <c r="M268" s="8"/>
     </row>
     <row r="269">
       <c r="A269" s="8"/>
@@ -4087,10 +4357,11 @@
       <c r="F269" s="8"/>
       <c r="G269" s="8"/>
       <c r="H269" s="8"/>
-      <c r="I269" s="9"/>
-      <c r="J269" s="10"/>
-      <c r="K269" s="8"/>
+      <c r="I269" s="8"/>
+      <c r="J269" s="8"/>
+      <c r="K269" s="9"/>
       <c r="L269" s="8"/>
+      <c r="M269" s="8"/>
     </row>
     <row r="270">
       <c r="A270" s="8"/>
@@ -4101,10 +4372,11 @@
       <c r="F270" s="8"/>
       <c r="G270" s="8"/>
       <c r="H270" s="8"/>
-      <c r="I270" s="9"/>
-      <c r="J270" s="10"/>
-      <c r="K270" s="8"/>
+      <c r="I270" s="8"/>
+      <c r="J270" s="8"/>
+      <c r="K270" s="9"/>
       <c r="L270" s="8"/>
+      <c r="M270" s="8"/>
     </row>
     <row r="271">
       <c r="A271" s="8"/>
@@ -4115,10 +4387,11 @@
       <c r="F271" s="8"/>
       <c r="G271" s="8"/>
       <c r="H271" s="8"/>
-      <c r="I271" s="9"/>
-      <c r="J271" s="10"/>
-      <c r="K271" s="8"/>
+      <c r="I271" s="8"/>
+      <c r="J271" s="8"/>
+      <c r="K271" s="9"/>
       <c r="L271" s="8"/>
+      <c r="M271" s="8"/>
     </row>
     <row r="272">
       <c r="A272" s="8"/>
@@ -4129,10 +4402,11 @@
       <c r="F272" s="8"/>
       <c r="G272" s="8"/>
       <c r="H272" s="8"/>
-      <c r="I272" s="9"/>
-      <c r="J272" s="10"/>
-      <c r="K272" s="8"/>
+      <c r="I272" s="8"/>
+      <c r="J272" s="8"/>
+      <c r="K272" s="9"/>
       <c r="L272" s="8"/>
+      <c r="M272" s="8"/>
     </row>
     <row r="273">
       <c r="A273" s="8"/>
@@ -4143,10 +4417,11 @@
       <c r="F273" s="8"/>
       <c r="G273" s="8"/>
       <c r="H273" s="8"/>
-      <c r="I273" s="9"/>
-      <c r="J273" s="10"/>
-      <c r="K273" s="8"/>
+      <c r="I273" s="8"/>
+      <c r="J273" s="8"/>
+      <c r="K273" s="9"/>
       <c r="L273" s="8"/>
+      <c r="M273" s="8"/>
     </row>
     <row r="274">
       <c r="A274" s="8"/>
@@ -4157,10 +4432,11 @@
       <c r="F274" s="8"/>
       <c r="G274" s="8"/>
       <c r="H274" s="8"/>
-      <c r="I274" s="9"/>
-      <c r="J274" s="10"/>
-      <c r="K274" s="8"/>
+      <c r="I274" s="8"/>
+      <c r="J274" s="8"/>
+      <c r="K274" s="9"/>
       <c r="L274" s="8"/>
+      <c r="M274" s="8"/>
     </row>
     <row r="275">
       <c r="A275" s="8"/>
@@ -4171,10 +4447,11 @@
       <c r="F275" s="8"/>
       <c r="G275" s="8"/>
       <c r="H275" s="8"/>
-      <c r="I275" s="9"/>
-      <c r="J275" s="10"/>
-      <c r="K275" s="8"/>
+      <c r="I275" s="8"/>
+      <c r="J275" s="8"/>
+      <c r="K275" s="9"/>
       <c r="L275" s="8"/>
+      <c r="M275" s="8"/>
     </row>
     <row r="276">
       <c r="A276" s="8"/>
@@ -4185,10 +4462,11 @@
       <c r="F276" s="8"/>
       <c r="G276" s="8"/>
       <c r="H276" s="8"/>
-      <c r="I276" s="9"/>
-      <c r="J276" s="10"/>
-      <c r="K276" s="8"/>
+      <c r="I276" s="8"/>
+      <c r="J276" s="8"/>
+      <c r="K276" s="9"/>
       <c r="L276" s="8"/>
+      <c r="M276" s="8"/>
     </row>
     <row r="277">
       <c r="A277" s="8"/>
@@ -4199,10 +4477,11 @@
       <c r="F277" s="8"/>
       <c r="G277" s="8"/>
       <c r="H277" s="8"/>
-      <c r="I277" s="9"/>
-      <c r="J277" s="10"/>
-      <c r="K277" s="8"/>
+      <c r="I277" s="8"/>
+      <c r="J277" s="8"/>
+      <c r="K277" s="9"/>
       <c r="L277" s="8"/>
+      <c r="M277" s="8"/>
     </row>
     <row r="278">
       <c r="A278" s="8"/>
@@ -4213,10 +4492,11 @@
       <c r="F278" s="8"/>
       <c r="G278" s="8"/>
       <c r="H278" s="8"/>
-      <c r="I278" s="9"/>
-      <c r="J278" s="10"/>
-      <c r="K278" s="8"/>
+      <c r="I278" s="8"/>
+      <c r="J278" s="8"/>
+      <c r="K278" s="9"/>
       <c r="L278" s="8"/>
+      <c r="M278" s="8"/>
     </row>
     <row r="279">
       <c r="A279" s="8"/>
@@ -4227,10 +4507,11 @@
       <c r="F279" s="8"/>
       <c r="G279" s="8"/>
       <c r="H279" s="8"/>
-      <c r="I279" s="9"/>
-      <c r="J279" s="10"/>
-      <c r="K279" s="8"/>
+      <c r="I279" s="8"/>
+      <c r="J279" s="8"/>
+      <c r="K279" s="9"/>
       <c r="L279" s="8"/>
+      <c r="M279" s="8"/>
     </row>
     <row r="280">
       <c r="A280" s="8"/>
@@ -4241,10 +4522,11 @@
       <c r="F280" s="8"/>
       <c r="G280" s="8"/>
       <c r="H280" s="8"/>
-      <c r="I280" s="9"/>
-      <c r="J280" s="10"/>
-      <c r="K280" s="8"/>
+      <c r="I280" s="8"/>
+      <c r="J280" s="8"/>
+      <c r="K280" s="9"/>
       <c r="L280" s="8"/>
+      <c r="M280" s="8"/>
     </row>
     <row r="281">
       <c r="A281" s="8"/>
@@ -4255,10 +4537,11 @@
       <c r="F281" s="8"/>
       <c r="G281" s="8"/>
       <c r="H281" s="8"/>
-      <c r="I281" s="9"/>
-      <c r="J281" s="10"/>
-      <c r="K281" s="8"/>
+      <c r="I281" s="8"/>
+      <c r="J281" s="8"/>
+      <c r="K281" s="9"/>
       <c r="L281" s="8"/>
+      <c r="M281" s="8"/>
     </row>
     <row r="282">
       <c r="A282" s="8"/>
@@ -4269,10 +4552,11 @@
       <c r="F282" s="8"/>
       <c r="G282" s="8"/>
       <c r="H282" s="8"/>
-      <c r="I282" s="9"/>
-      <c r="J282" s="10"/>
-      <c r="K282" s="8"/>
+      <c r="I282" s="8"/>
+      <c r="J282" s="8"/>
+      <c r="K282" s="9"/>
       <c r="L282" s="8"/>
+      <c r="M282" s="8"/>
     </row>
     <row r="283">
       <c r="A283" s="8"/>
@@ -4283,10 +4567,11 @@
       <c r="F283" s="8"/>
       <c r="G283" s="8"/>
       <c r="H283" s="8"/>
-      <c r="I283" s="9"/>
-      <c r="J283" s="10"/>
-      <c r="K283" s="8"/>
+      <c r="I283" s="8"/>
+      <c r="J283" s="8"/>
+      <c r="K283" s="9"/>
       <c r="L283" s="8"/>
+      <c r="M283" s="8"/>
     </row>
     <row r="284">
       <c r="A284" s="8"/>
@@ -4297,10 +4582,11 @@
       <c r="F284" s="8"/>
       <c r="G284" s="8"/>
       <c r="H284" s="8"/>
-      <c r="I284" s="9"/>
-      <c r="J284" s="10"/>
-      <c r="K284" s="8"/>
+      <c r="I284" s="8"/>
+      <c r="J284" s="8"/>
+      <c r="K284" s="9"/>
       <c r="L284" s="8"/>
+      <c r="M284" s="8"/>
     </row>
     <row r="285">
       <c r="A285" s="8"/>
@@ -4311,10 +4597,11 @@
       <c r="F285" s="8"/>
       <c r="G285" s="8"/>
       <c r="H285" s="8"/>
-      <c r="I285" s="9"/>
-      <c r="J285" s="10"/>
-      <c r="K285" s="8"/>
+      <c r="I285" s="8"/>
+      <c r="J285" s="8"/>
+      <c r="K285" s="9"/>
       <c r="L285" s="8"/>
+      <c r="M285" s="8"/>
     </row>
     <row r="286">
       <c r="A286" s="8"/>
@@ -4325,10 +4612,11 @@
       <c r="F286" s="8"/>
       <c r="G286" s="8"/>
       <c r="H286" s="8"/>
-      <c r="I286" s="9"/>
-      <c r="J286" s="10"/>
-      <c r="K286" s="8"/>
+      <c r="I286" s="8"/>
+      <c r="J286" s="8"/>
+      <c r="K286" s="9"/>
       <c r="L286" s="8"/>
+      <c r="M286" s="8"/>
     </row>
     <row r="287">
       <c r="A287" s="8"/>
@@ -4339,10 +4627,11 @@
       <c r="F287" s="8"/>
       <c r="G287" s="8"/>
       <c r="H287" s="8"/>
-      <c r="I287" s="9"/>
-      <c r="J287" s="10"/>
-      <c r="K287" s="8"/>
+      <c r="I287" s="8"/>
+      <c r="J287" s="8"/>
+      <c r="K287" s="9"/>
       <c r="L287" s="8"/>
+      <c r="M287" s="8"/>
     </row>
     <row r="288">
       <c r="A288" s="8"/>
@@ -4353,10 +4642,11 @@
       <c r="F288" s="8"/>
       <c r="G288" s="8"/>
       <c r="H288" s="8"/>
-      <c r="I288" s="9"/>
-      <c r="J288" s="10"/>
-      <c r="K288" s="8"/>
+      <c r="I288" s="8"/>
+      <c r="J288" s="8"/>
+      <c r="K288" s="9"/>
       <c r="L288" s="8"/>
+      <c r="M288" s="8"/>
     </row>
     <row r="289">
       <c r="A289" s="8"/>
@@ -4367,10 +4657,11 @@
       <c r="F289" s="8"/>
       <c r="G289" s="8"/>
       <c r="H289" s="8"/>
-      <c r="I289" s="9"/>
-      <c r="J289" s="10"/>
-      <c r="K289" s="8"/>
+      <c r="I289" s="8"/>
+      <c r="J289" s="8"/>
+      <c r="K289" s="9"/>
       <c r="L289" s="8"/>
+      <c r="M289" s="8"/>
     </row>
     <row r="290">
       <c r="A290" s="8"/>
@@ -4381,10 +4672,11 @@
       <c r="F290" s="8"/>
       <c r="G290" s="8"/>
       <c r="H290" s="8"/>
-      <c r="I290" s="9"/>
-      <c r="J290" s="10"/>
-      <c r="K290" s="8"/>
+      <c r="I290" s="8"/>
+      <c r="J290" s="8"/>
+      <c r="K290" s="9"/>
       <c r="L290" s="8"/>
+      <c r="M290" s="8"/>
     </row>
     <row r="291">
       <c r="A291" s="8"/>
@@ -4395,10 +4687,11 @@
       <c r="F291" s="8"/>
       <c r="G291" s="8"/>
       <c r="H291" s="8"/>
-      <c r="I291" s="9"/>
-      <c r="J291" s="10"/>
-      <c r="K291" s="8"/>
+      <c r="I291" s="8"/>
+      <c r="J291" s="8"/>
+      <c r="K291" s="9"/>
       <c r="L291" s="8"/>
+      <c r="M291" s="8"/>
     </row>
     <row r="292">
       <c r="A292" s="8"/>
@@ -4409,10 +4702,11 @@
       <c r="F292" s="8"/>
       <c r="G292" s="8"/>
       <c r="H292" s="8"/>
-      <c r="I292" s="9"/>
-      <c r="J292" s="10"/>
-      <c r="K292" s="8"/>
+      <c r="I292" s="8"/>
+      <c r="J292" s="8"/>
+      <c r="K292" s="9"/>
       <c r="L292" s="8"/>
+      <c r="M292" s="8"/>
     </row>
     <row r="293">
       <c r="A293" s="8"/>
@@ -4423,10 +4717,11 @@
       <c r="F293" s="8"/>
       <c r="G293" s="8"/>
       <c r="H293" s="8"/>
-      <c r="I293" s="9"/>
-      <c r="J293" s="10"/>
-      <c r="K293" s="8"/>
+      <c r="I293" s="8"/>
+      <c r="J293" s="8"/>
+      <c r="K293" s="9"/>
       <c r="L293" s="8"/>
+      <c r="M293" s="8"/>
     </row>
     <row r="294">
       <c r="A294" s="8"/>
@@ -4437,10 +4732,11 @@
       <c r="F294" s="8"/>
       <c r="G294" s="8"/>
       <c r="H294" s="8"/>
-      <c r="I294" s="9"/>
-      <c r="J294" s="10"/>
-      <c r="K294" s="8"/>
+      <c r="I294" s="8"/>
+      <c r="J294" s="8"/>
+      <c r="K294" s="9"/>
       <c r="L294" s="8"/>
+      <c r="M294" s="8"/>
     </row>
     <row r="295">
       <c r="A295" s="8"/>
@@ -4451,10 +4747,11 @@
       <c r="F295" s="8"/>
       <c r="G295" s="8"/>
       <c r="H295" s="8"/>
-      <c r="I295" s="9"/>
-      <c r="J295" s="10"/>
-      <c r="K295" s="8"/>
+      <c r="I295" s="8"/>
+      <c r="J295" s="8"/>
+      <c r="K295" s="9"/>
       <c r="L295" s="8"/>
+      <c r="M295" s="8"/>
     </row>
     <row r="296">
       <c r="A296" s="8"/>
@@ -4465,10 +4762,11 @@
       <c r="F296" s="8"/>
       <c r="G296" s="8"/>
       <c r="H296" s="8"/>
-      <c r="I296" s="9"/>
-      <c r="J296" s="10"/>
-      <c r="K296" s="8"/>
+      <c r="I296" s="8"/>
+      <c r="J296" s="8"/>
+      <c r="K296" s="9"/>
       <c r="L296" s="8"/>
+      <c r="M296" s="8"/>
     </row>
     <row r="297">
       <c r="A297" s="8"/>
@@ -4479,10 +4777,11 @@
       <c r="F297" s="8"/>
       <c r="G297" s="8"/>
       <c r="H297" s="8"/>
-      <c r="I297" s="9"/>
-      <c r="J297" s="10"/>
-      <c r="K297" s="8"/>
+      <c r="I297" s="8"/>
+      <c r="J297" s="8"/>
+      <c r="K297" s="9"/>
       <c r="L297" s="8"/>
+      <c r="M297" s="8"/>
     </row>
     <row r="298">
       <c r="A298" s="8"/>
@@ -4493,10 +4792,11 @@
       <c r="F298" s="8"/>
       <c r="G298" s="8"/>
       <c r="H298" s="8"/>
-      <c r="I298" s="9"/>
-      <c r="J298" s="10"/>
-      <c r="K298" s="8"/>
+      <c r="I298" s="8"/>
+      <c r="J298" s="8"/>
+      <c r="K298" s="9"/>
       <c r="L298" s="8"/>
+      <c r="M298" s="8"/>
     </row>
     <row r="299">
       <c r="A299" s="8"/>
@@ -4507,10 +4807,11 @@
       <c r="F299" s="8"/>
       <c r="G299" s="8"/>
       <c r="H299" s="8"/>
-      <c r="I299" s="9"/>
-      <c r="J299" s="10"/>
-      <c r="K299" s="8"/>
+      <c r="I299" s="8"/>
+      <c r="J299" s="8"/>
+      <c r="K299" s="9"/>
       <c r="L299" s="8"/>
+      <c r="M299" s="8"/>
     </row>
     <row r="300">
       <c r="A300" s="8"/>
@@ -4521,10 +4822,11 @@
       <c r="F300" s="8"/>
       <c r="G300" s="8"/>
       <c r="H300" s="8"/>
-      <c r="I300" s="9"/>
-      <c r="J300" s="10"/>
-      <c r="K300" s="8"/>
+      <c r="I300" s="8"/>
+      <c r="J300" s="8"/>
+      <c r="K300" s="9"/>
       <c r="L300" s="8"/>
+      <c r="M300" s="8"/>
     </row>
     <row r="301">
       <c r="A301" s="8"/>
@@ -4535,10 +4837,11 @@
       <c r="F301" s="8"/>
       <c r="G301" s="8"/>
       <c r="H301" s="8"/>
-      <c r="I301" s="9"/>
-      <c r="J301" s="10"/>
-      <c r="K301" s="8"/>
+      <c r="I301" s="8"/>
+      <c r="J301" s="8"/>
+      <c r="K301" s="9"/>
       <c r="L301" s="8"/>
+      <c r="M301" s="8"/>
     </row>
     <row r="302">
       <c r="A302" s="8"/>
@@ -4549,10 +4852,11 @@
       <c r="F302" s="8"/>
       <c r="G302" s="8"/>
       <c r="H302" s="8"/>
-      <c r="I302" s="9"/>
-      <c r="J302" s="10"/>
-      <c r="K302" s="8"/>
+      <c r="I302" s="8"/>
+      <c r="J302" s="8"/>
+      <c r="K302" s="9"/>
       <c r="L302" s="8"/>
+      <c r="M302" s="8"/>
     </row>
     <row r="303">
       <c r="A303" s="8"/>
@@ -4563,10 +4867,11 @@
       <c r="F303" s="8"/>
       <c r="G303" s="8"/>
       <c r="H303" s="8"/>
-      <c r="I303" s="9"/>
-      <c r="J303" s="10"/>
-      <c r="K303" s="8"/>
+      <c r="I303" s="8"/>
+      <c r="J303" s="8"/>
+      <c r="K303" s="9"/>
       <c r="L303" s="8"/>
+      <c r="M303" s="8"/>
     </row>
     <row r="304">
       <c r="A304" s="8"/>
@@ -4577,10 +4882,11 @@
       <c r="F304" s="8"/>
       <c r="G304" s="8"/>
       <c r="H304" s="8"/>
-      <c r="I304" s="9"/>
-      <c r="J304" s="10"/>
-      <c r="K304" s="8"/>
+      <c r="I304" s="8"/>
+      <c r="J304" s="8"/>
+      <c r="K304" s="9"/>
       <c r="L304" s="8"/>
+      <c r="M304" s="8"/>
     </row>
     <row r="305">
       <c r="A305" s="8"/>
@@ -4591,10 +4897,11 @@
       <c r="F305" s="8"/>
       <c r="G305" s="8"/>
       <c r="H305" s="8"/>
-      <c r="I305" s="9"/>
-      <c r="J305" s="10"/>
-      <c r="K305" s="8"/>
+      <c r="I305" s="8"/>
+      <c r="J305" s="8"/>
+      <c r="K305" s="9"/>
       <c r="L305" s="8"/>
+      <c r="M305" s="8"/>
     </row>
     <row r="306">
       <c r="A306" s="8"/>
@@ -4605,10 +4912,11 @@
       <c r="F306" s="8"/>
       <c r="G306" s="8"/>
       <c r="H306" s="8"/>
-      <c r="I306" s="9"/>
-      <c r="J306" s="10"/>
-      <c r="K306" s="8"/>
+      <c r="I306" s="8"/>
+      <c r="J306" s="8"/>
+      <c r="K306" s="9"/>
       <c r="L306" s="8"/>
+      <c r="M306" s="8"/>
     </row>
     <row r="307">
       <c r="A307" s="8"/>
@@ -4619,10 +4927,11 @@
       <c r="F307" s="8"/>
       <c r="G307" s="8"/>
       <c r="H307" s="8"/>
-      <c r="I307" s="9"/>
-      <c r="J307" s="10"/>
-      <c r="K307" s="8"/>
+      <c r="I307" s="8"/>
+      <c r="J307" s="8"/>
+      <c r="K307" s="9"/>
       <c r="L307" s="8"/>
+      <c r="M307" s="8"/>
     </row>
     <row r="308">
       <c r="A308" s="8"/>
@@ -4633,10 +4942,11 @@
       <c r="F308" s="8"/>
       <c r="G308" s="8"/>
       <c r="H308" s="8"/>
-      <c r="I308" s="9"/>
-      <c r="J308" s="10"/>
-      <c r="K308" s="8"/>
+      <c r="I308" s="8"/>
+      <c r="J308" s="8"/>
+      <c r="K308" s="9"/>
       <c r="L308" s="8"/>
+      <c r="M308" s="8"/>
     </row>
     <row r="309">
       <c r="A309" s="8"/>
@@ -4647,10 +4957,11 @@
       <c r="F309" s="8"/>
       <c r="G309" s="8"/>
       <c r="H309" s="8"/>
-      <c r="I309" s="9"/>
-      <c r="J309" s="10"/>
-      <c r="K309" s="8"/>
+      <c r="I309" s="8"/>
+      <c r="J309" s="8"/>
+      <c r="K309" s="9"/>
       <c r="L309" s="8"/>
+      <c r="M309" s="8"/>
     </row>
     <row r="310">
       <c r="A310" s="8"/>
@@ -4661,10 +4972,11 @@
       <c r="F310" s="8"/>
       <c r="G310" s="8"/>
       <c r="H310" s="8"/>
-      <c r="I310" s="9"/>
-      <c r="J310" s="10"/>
-      <c r="K310" s="8"/>
+      <c r="I310" s="8"/>
+      <c r="J310" s="8"/>
+      <c r="K310" s="9"/>
       <c r="L310" s="8"/>
+      <c r="M310" s="8"/>
     </row>
     <row r="311">
       <c r="A311" s="8"/>
@@ -4675,10 +4987,11 @@
       <c r="F311" s="8"/>
       <c r="G311" s="8"/>
       <c r="H311" s="8"/>
-      <c r="I311" s="9"/>
-      <c r="J311" s="10"/>
-      <c r="K311" s="8"/>
+      <c r="I311" s="8"/>
+      <c r="J311" s="8"/>
+      <c r="K311" s="9"/>
       <c r="L311" s="8"/>
+      <c r="M311" s="8"/>
     </row>
     <row r="312">
       <c r="A312" s="8"/>
@@ -4689,10 +5002,11 @@
       <c r="F312" s="8"/>
       <c r="G312" s="8"/>
       <c r="H312" s="8"/>
-      <c r="I312" s="9"/>
-      <c r="J312" s="10"/>
-      <c r="K312" s="8"/>
+      <c r="I312" s="8"/>
+      <c r="J312" s="8"/>
+      <c r="K312" s="9"/>
       <c r="L312" s="8"/>
+      <c r="M312" s="8"/>
     </row>
     <row r="313">
       <c r="A313" s="8"/>
@@ -4703,10 +5017,11 @@
       <c r="F313" s="8"/>
       <c r="G313" s="8"/>
       <c r="H313" s="8"/>
-      <c r="I313" s="9"/>
-      <c r="J313" s="10"/>
-      <c r="K313" s="8"/>
+      <c r="I313" s="8"/>
+      <c r="J313" s="8"/>
+      <c r="K313" s="9"/>
       <c r="L313" s="8"/>
+      <c r="M313" s="8"/>
     </row>
     <row r="314">
       <c r="A314" s="8"/>
@@ -4717,10 +5032,11 @@
       <c r="F314" s="8"/>
       <c r="G314" s="8"/>
       <c r="H314" s="8"/>
-      <c r="I314" s="9"/>
-      <c r="J314" s="10"/>
-      <c r="K314" s="8"/>
+      <c r="I314" s="8"/>
+      <c r="J314" s="8"/>
+      <c r="K314" s="9"/>
       <c r="L314" s="8"/>
+      <c r="M314" s="8"/>
     </row>
     <row r="315">
       <c r="A315" s="8"/>
@@ -4731,10 +5047,11 @@
       <c r="F315" s="8"/>
       <c r="G315" s="8"/>
       <c r="H315" s="8"/>
-      <c r="I315" s="9"/>
-      <c r="J315" s="10"/>
-      <c r="K315" s="8"/>
+      <c r="I315" s="8"/>
+      <c r="J315" s="8"/>
+      <c r="K315" s="9"/>
       <c r="L315" s="8"/>
+      <c r="M315" s="8"/>
     </row>
     <row r="316">
       <c r="A316" s="8"/>
@@ -4745,10 +5062,11 @@
       <c r="F316" s="8"/>
       <c r="G316" s="8"/>
       <c r="H316" s="8"/>
-      <c r="I316" s="9"/>
-      <c r="J316" s="10"/>
-      <c r="K316" s="8"/>
+      <c r="I316" s="8"/>
+      <c r="J316" s="8"/>
+      <c r="K316" s="9"/>
       <c r="L316" s="8"/>
+      <c r="M316" s="8"/>
     </row>
     <row r="317">
       <c r="A317" s="8"/>
@@ -4759,10 +5077,11 @@
       <c r="F317" s="8"/>
       <c r="G317" s="8"/>
       <c r="H317" s="8"/>
-      <c r="I317" s="9"/>
-      <c r="J317" s="10"/>
-      <c r="K317" s="8"/>
+      <c r="I317" s="8"/>
+      <c r="J317" s="8"/>
+      <c r="K317" s="9"/>
       <c r="L317" s="8"/>
+      <c r="M317" s="8"/>
     </row>
     <row r="318">
       <c r="A318" s="8"/>
@@ -4773,10 +5092,11 @@
       <c r="F318" s="8"/>
       <c r="G318" s="8"/>
       <c r="H318" s="8"/>
-      <c r="I318" s="9"/>
-      <c r="J318" s="10"/>
-      <c r="K318" s="8"/>
+      <c r="I318" s="8"/>
+      <c r="J318" s="8"/>
+      <c r="K318" s="9"/>
       <c r="L318" s="8"/>
+      <c r="M318" s="8"/>
     </row>
     <row r="319">
       <c r="A319" s="8"/>
@@ -4787,10 +5107,11 @@
       <c r="F319" s="8"/>
       <c r="G319" s="8"/>
       <c r="H319" s="8"/>
-      <c r="I319" s="9"/>
-      <c r="J319" s="10"/>
-      <c r="K319" s="8"/>
+      <c r="I319" s="8"/>
+      <c r="J319" s="8"/>
+      <c r="K319" s="9"/>
       <c r="L319" s="8"/>
+      <c r="M319" s="8"/>
     </row>
     <row r="320">
       <c r="A320" s="8"/>
@@ -4801,10 +5122,11 @@
       <c r="F320" s="8"/>
       <c r="G320" s="8"/>
       <c r="H320" s="8"/>
-      <c r="I320" s="9"/>
-      <c r="J320" s="10"/>
-      <c r="K320" s="8"/>
+      <c r="I320" s="8"/>
+      <c r="J320" s="8"/>
+      <c r="K320" s="9"/>
       <c r="L320" s="8"/>
+      <c r="M320" s="8"/>
     </row>
     <row r="321">
       <c r="A321" s="8"/>
@@ -4815,10 +5137,11 @@
       <c r="F321" s="8"/>
       <c r="G321" s="8"/>
       <c r="H321" s="8"/>
-      <c r="I321" s="9"/>
-      <c r="J321" s="10"/>
-      <c r="K321" s="8"/>
+      <c r="I321" s="8"/>
+      <c r="J321" s="8"/>
+      <c r="K321" s="9"/>
       <c r="L321" s="8"/>
+      <c r="M321" s="8"/>
     </row>
     <row r="322">
       <c r="A322" s="8"/>
@@ -4829,10 +5152,11 @@
       <c r="F322" s="8"/>
       <c r="G322" s="8"/>
       <c r="H322" s="8"/>
-      <c r="I322" s="9"/>
-      <c r="J322" s="10"/>
-      <c r="K322" s="8"/>
+      <c r="I322" s="8"/>
+      <c r="J322" s="8"/>
+      <c r="K322" s="9"/>
       <c r="L322" s="8"/>
+      <c r="M322" s="8"/>
     </row>
     <row r="323">
       <c r="A323" s="8"/>
@@ -4843,10 +5167,11 @@
       <c r="F323" s="8"/>
       <c r="G323" s="8"/>
       <c r="H323" s="8"/>
-      <c r="I323" s="9"/>
-      <c r="J323" s="10"/>
-      <c r="K323" s="8"/>
+      <c r="I323" s="8"/>
+      <c r="J323" s="8"/>
+      <c r="K323" s="9"/>
       <c r="L323" s="8"/>
+      <c r="M323" s="8"/>
     </row>
     <row r="324">
       <c r="A324" s="8"/>
@@ -4857,10 +5182,11 @@
       <c r="F324" s="8"/>
       <c r="G324" s="8"/>
       <c r="H324" s="8"/>
-      <c r="I324" s="9"/>
-      <c r="J324" s="10"/>
-      <c r="K324" s="8"/>
+      <c r="I324" s="8"/>
+      <c r="J324" s="8"/>
+      <c r="K324" s="9"/>
       <c r="L324" s="8"/>
+      <c r="M324" s="8"/>
     </row>
     <row r="325">
       <c r="A325" s="8"/>
@@ -4871,10 +5197,11 @@
       <c r="F325" s="8"/>
       <c r="G325" s="8"/>
       <c r="H325" s="8"/>
-      <c r="I325" s="9"/>
-      <c r="J325" s="10"/>
-      <c r="K325" s="8"/>
+      <c r="I325" s="8"/>
+      <c r="J325" s="8"/>
+      <c r="K325" s="9"/>
       <c r="L325" s="8"/>
+      <c r="M325" s="8"/>
     </row>
     <row r="326">
       <c r="A326" s="8"/>
@@ -4885,10 +5212,11 @@
       <c r="F326" s="8"/>
       <c r="G326" s="8"/>
       <c r="H326" s="8"/>
-      <c r="I326" s="9"/>
-      <c r="J326" s="10"/>
-      <c r="K326" s="8"/>
+      <c r="I326" s="8"/>
+      <c r="J326" s="8"/>
+      <c r="K326" s="9"/>
       <c r="L326" s="8"/>
+      <c r="M326" s="8"/>
     </row>
     <row r="327">
       <c r="A327" s="8"/>
@@ -4899,10 +5227,11 @@
       <c r="F327" s="8"/>
       <c r="G327" s="8"/>
       <c r="H327" s="8"/>
-      <c r="I327" s="9"/>
-      <c r="J327" s="10"/>
-      <c r="K327" s="8"/>
+      <c r="I327" s="8"/>
+      <c r="J327" s="8"/>
+      <c r="K327" s="9"/>
       <c r="L327" s="8"/>
+      <c r="M327" s="8"/>
     </row>
     <row r="328">
       <c r="A328" s="8"/>
@@ -4913,10 +5242,11 @@
       <c r="F328" s="8"/>
       <c r="G328" s="8"/>
       <c r="H328" s="8"/>
-      <c r="I328" s="9"/>
-      <c r="J328" s="10"/>
-      <c r="K328" s="8"/>
+      <c r="I328" s="8"/>
+      <c r="J328" s="8"/>
+      <c r="K328" s="9"/>
       <c r="L328" s="8"/>
+      <c r="M328" s="8"/>
     </row>
     <row r="329">
       <c r="A329" s="8"/>
@@ -4927,10 +5257,11 @@
       <c r="F329" s="8"/>
       <c r="G329" s="8"/>
       <c r="H329" s="8"/>
-      <c r="I329" s="9"/>
-      <c r="J329" s="10"/>
-      <c r="K329" s="8"/>
+      <c r="I329" s="8"/>
+      <c r="J329" s="8"/>
+      <c r="K329" s="9"/>
       <c r="L329" s="8"/>
+      <c r="M329" s="8"/>
     </row>
     <row r="330">
       <c r="A330" s="8"/>
@@ -4941,10 +5272,11 @@
       <c r="F330" s="8"/>
       <c r="G330" s="8"/>
       <c r="H330" s="8"/>
-      <c r="I330" s="9"/>
-      <c r="J330" s="10"/>
-      <c r="K330" s="8"/>
+      <c r="I330" s="8"/>
+      <c r="J330" s="8"/>
+      <c r="K330" s="9"/>
       <c r="L330" s="8"/>
+      <c r="M330" s="8"/>
     </row>
     <row r="331">
       <c r="A331" s="8"/>
@@ -4955,10 +5287,11 @@
       <c r="F331" s="8"/>
       <c r="G331" s="8"/>
       <c r="H331" s="8"/>
-      <c r="I331" s="9"/>
-      <c r="J331" s="10"/>
-      <c r="K331" s="8"/>
+      <c r="I331" s="8"/>
+      <c r="J331" s="8"/>
+      <c r="K331" s="9"/>
       <c r="L331" s="8"/>
+      <c r="M331" s="8"/>
     </row>
     <row r="332">
       <c r="A332" s="8"/>
@@ -4969,10 +5302,11 @@
       <c r="F332" s="8"/>
       <c r="G332" s="8"/>
       <c r="H332" s="8"/>
-      <c r="I332" s="9"/>
-      <c r="J332" s="10"/>
-      <c r="K332" s="8"/>
+      <c r="I332" s="8"/>
+      <c r="J332" s="8"/>
+      <c r="K332" s="9"/>
       <c r="L332" s="8"/>
+      <c r="M332" s="8"/>
     </row>
     <row r="333">
       <c r="A333" s="8"/>
@@ -4983,10 +5317,11 @@
       <c r="F333" s="8"/>
       <c r="G333" s="8"/>
       <c r="H333" s="8"/>
-      <c r="I333" s="9"/>
-      <c r="J333" s="10"/>
-      <c r="K333" s="8"/>
+      <c r="I333" s="8"/>
+      <c r="J333" s="8"/>
+      <c r="K333" s="9"/>
       <c r="L333" s="8"/>
+      <c r="M333" s="8"/>
     </row>
     <row r="334">
       <c r="A334" s="8"/>
@@ -4997,10 +5332,11 @@
       <c r="F334" s="8"/>
       <c r="G334" s="8"/>
       <c r="H334" s="8"/>
-      <c r="I334" s="9"/>
-      <c r="J334" s="10"/>
-      <c r="K334" s="8"/>
+      <c r="I334" s="8"/>
+      <c r="J334" s="8"/>
+      <c r="K334" s="9"/>
       <c r="L334" s="8"/>
+      <c r="M334" s="8"/>
     </row>
     <row r="335">
       <c r="A335" s="8"/>
@@ -5011,10 +5347,11 @@
       <c r="F335" s="8"/>
       <c r="G335" s="8"/>
       <c r="H335" s="8"/>
-      <c r="I335" s="9"/>
-      <c r="J335" s="10"/>
-      <c r="K335" s="8"/>
+      <c r="I335" s="8"/>
+      <c r="J335" s="8"/>
+      <c r="K335" s="9"/>
       <c r="L335" s="8"/>
+      <c r="M335" s="8"/>
     </row>
     <row r="336">
       <c r="A336" s="8"/>
@@ -5025,10 +5362,11 @@
       <c r="F336" s="8"/>
       <c r="G336" s="8"/>
       <c r="H336" s="8"/>
-      <c r="I336" s="9"/>
-      <c r="J336" s="10"/>
-      <c r="K336" s="8"/>
+      <c r="I336" s="8"/>
+      <c r="J336" s="8"/>
+      <c r="K336" s="9"/>
       <c r="L336" s="8"/>
+      <c r="M336" s="8"/>
     </row>
     <row r="337">
       <c r="A337" s="8"/>
@@ -5039,10 +5377,11 @@
       <c r="F337" s="8"/>
       <c r="G337" s="8"/>
       <c r="H337" s="8"/>
-      <c r="I337" s="9"/>
-      <c r="J337" s="10"/>
-      <c r="K337" s="8"/>
+      <c r="I337" s="8"/>
+      <c r="J337" s="8"/>
+      <c r="K337" s="9"/>
       <c r="L337" s="8"/>
+      <c r="M337" s="8"/>
     </row>
     <row r="338">
       <c r="A338" s="8"/>
@@ -5053,10 +5392,11 @@
       <c r="F338" s="8"/>
       <c r="G338" s="8"/>
       <c r="H338" s="8"/>
-      <c r="I338" s="9"/>
-      <c r="J338" s="10"/>
-      <c r="K338" s="8"/>
+      <c r="I338" s="8"/>
+      <c r="J338" s="8"/>
+      <c r="K338" s="9"/>
       <c r="L338" s="8"/>
+      <c r="M338" s="8"/>
     </row>
     <row r="339">
       <c r="A339" s="8"/>
@@ -5067,10 +5407,11 @@
       <c r="F339" s="8"/>
       <c r="G339" s="8"/>
       <c r="H339" s="8"/>
-      <c r="I339" s="9"/>
-      <c r="J339" s="10"/>
-      <c r="K339" s="8"/>
+      <c r="I339" s="8"/>
+      <c r="J339" s="8"/>
+      <c r="K339" s="9"/>
       <c r="L339" s="8"/>
+      <c r="M339" s="8"/>
     </row>
     <row r="340">
       <c r="A340" s="8"/>
@@ -5081,10 +5422,11 @@
       <c r="F340" s="8"/>
       <c r="G340" s="8"/>
       <c r="H340" s="8"/>
-      <c r="I340" s="9"/>
-      <c r="J340" s="10"/>
-      <c r="K340" s="8"/>
+      <c r="I340" s="8"/>
+      <c r="J340" s="8"/>
+      <c r="K340" s="9"/>
       <c r="L340" s="8"/>
+      <c r="M340" s="8"/>
     </row>
     <row r="341">
       <c r="A341" s="8"/>
@@ -5095,10 +5437,11 @@
       <c r="F341" s="8"/>
       <c r="G341" s="8"/>
       <c r="H341" s="8"/>
-      <c r="I341" s="9"/>
-      <c r="J341" s="10"/>
-      <c r="K341" s="8"/>
+      <c r="I341" s="8"/>
+      <c r="J341" s="8"/>
+      <c r="K341" s="9"/>
       <c r="L341" s="8"/>
+      <c r="M341" s="8"/>
     </row>
     <row r="342">
       <c r="A342" s="8"/>
@@ -5109,10 +5452,11 @@
       <c r="F342" s="8"/>
       <c r="G342" s="8"/>
       <c r="H342" s="8"/>
-      <c r="I342" s="9"/>
-      <c r="J342" s="10"/>
-      <c r="K342" s="8"/>
+      <c r="I342" s="8"/>
+      <c r="J342" s="8"/>
+      <c r="K342" s="9"/>
       <c r="L342" s="8"/>
+      <c r="M342" s="8"/>
     </row>
     <row r="343">
       <c r="A343" s="8"/>
@@ -5123,10 +5467,11 @@
       <c r="F343" s="8"/>
       <c r="G343" s="8"/>
       <c r="H343" s="8"/>
-      <c r="I343" s="9"/>
-      <c r="J343" s="10"/>
-      <c r="K343" s="8"/>
+      <c r="I343" s="8"/>
+      <c r="J343" s="8"/>
+      <c r="K343" s="9"/>
       <c r="L343" s="8"/>
+      <c r="M343" s="8"/>
     </row>
     <row r="344">
       <c r="A344" s="8"/>
@@ -5137,10 +5482,11 @@
       <c r="F344" s="8"/>
       <c r="G344" s="8"/>
       <c r="H344" s="8"/>
-      <c r="I344" s="9"/>
-      <c r="J344" s="10"/>
-      <c r="K344" s="8"/>
+      <c r="I344" s="8"/>
+      <c r="J344" s="8"/>
+      <c r="K344" s="9"/>
       <c r="L344" s="8"/>
+      <c r="M344" s="8"/>
     </row>
     <row r="345">
       <c r="A345" s="8"/>
@@ -5151,10 +5497,11 @@
       <c r="F345" s="8"/>
       <c r="G345" s="8"/>
       <c r="H345" s="8"/>
-      <c r="I345" s="9"/>
-      <c r="J345" s="10"/>
-      <c r="K345" s="8"/>
+      <c r="I345" s="8"/>
+      <c r="J345" s="8"/>
+      <c r="K345" s="9"/>
       <c r="L345" s="8"/>
+      <c r="M345" s="8"/>
     </row>
     <row r="346">
       <c r="A346" s="8"/>
@@ -5165,10 +5512,11 @@
       <c r="F346" s="8"/>
       <c r="G346" s="8"/>
       <c r="H346" s="8"/>
-      <c r="I346" s="9"/>
-      <c r="J346" s="10"/>
-      <c r="K346" s="8"/>
+      <c r="I346" s="8"/>
+      <c r="J346" s="8"/>
+      <c r="K346" s="9"/>
       <c r="L346" s="8"/>
+      <c r="M346" s="8"/>
     </row>
     <row r="347">
       <c r="A347" s="8"/>
@@ -5179,10 +5527,11 @@
       <c r="F347" s="8"/>
       <c r="G347" s="8"/>
       <c r="H347" s="8"/>
-      <c r="I347" s="9"/>
-      <c r="J347" s="10"/>
-      <c r="K347" s="8"/>
+      <c r="I347" s="8"/>
+      <c r="J347" s="8"/>
+      <c r="K347" s="9"/>
       <c r="L347" s="8"/>
+      <c r="M347" s="8"/>
     </row>
     <row r="348">
       <c r="A348" s="8"/>
@@ -5193,10 +5542,11 @@
       <c r="F348" s="8"/>
       <c r="G348" s="8"/>
       <c r="H348" s="8"/>
-      <c r="I348" s="9"/>
-      <c r="J348" s="10"/>
-      <c r="K348" s="8"/>
+      <c r="I348" s="8"/>
+      <c r="J348" s="8"/>
+      <c r="K348" s="9"/>
       <c r="L348" s="8"/>
+      <c r="M348" s="8"/>
     </row>
     <row r="349">
       <c r="A349" s="8"/>
@@ -5207,10 +5557,11 @@
       <c r="F349" s="8"/>
       <c r="G349" s="8"/>
       <c r="H349" s="8"/>
-      <c r="I349" s="9"/>
-      <c r="J349" s="10"/>
-      <c r="K349" s="8"/>
+      <c r="I349" s="8"/>
+      <c r="J349" s="8"/>
+      <c r="K349" s="9"/>
       <c r="L349" s="8"/>
+      <c r="M349" s="8"/>
     </row>
     <row r="350">
       <c r="A350" s="8"/>
@@ -5221,10 +5572,11 @@
       <c r="F350" s="8"/>
       <c r="G350" s="8"/>
       <c r="H350" s="8"/>
-      <c r="I350" s="9"/>
-      <c r="J350" s="10"/>
-      <c r="K350" s="8"/>
+      <c r="I350" s="8"/>
+      <c r="J350" s="8"/>
+      <c r="K350" s="9"/>
       <c r="L350" s="8"/>
+      <c r="M350" s="8"/>
     </row>
     <row r="351">
       <c r="A351" s="8"/>
@@ -5235,10 +5587,11 @@
       <c r="F351" s="8"/>
       <c r="G351" s="8"/>
       <c r="H351" s="8"/>
-      <c r="I351" s="9"/>
-      <c r="J351" s="10"/>
-      <c r="K351" s="8"/>
+      <c r="I351" s="8"/>
+      <c r="J351" s="8"/>
+      <c r="K351" s="9"/>
       <c r="L351" s="8"/>
+      <c r="M351" s="8"/>
     </row>
     <row r="352">
       <c r="A352" s="8"/>
@@ -5249,10 +5602,11 @@
       <c r="F352" s="8"/>
       <c r="G352" s="8"/>
       <c r="H352" s="8"/>
-      <c r="I352" s="9"/>
-      <c r="J352" s="10"/>
-      <c r="K352" s="8"/>
+      <c r="I352" s="8"/>
+      <c r="J352" s="8"/>
+      <c r="K352" s="9"/>
       <c r="L352" s="8"/>
+      <c r="M352" s="8"/>
     </row>
     <row r="353">
       <c r="A353" s="8"/>
@@ -5263,10 +5617,11 @@
       <c r="F353" s="8"/>
       <c r="G353" s="8"/>
       <c r="H353" s="8"/>
-      <c r="I353" s="9"/>
-      <c r="J353" s="10"/>
-      <c r="K353" s="8"/>
+      <c r="I353" s="8"/>
+      <c r="J353" s="8"/>
+      <c r="K353" s="9"/>
       <c r="L353" s="8"/>
+      <c r="M353" s="8"/>
     </row>
     <row r="354">
       <c r="A354" s="8"/>
@@ -5277,10 +5632,11 @@
       <c r="F354" s="8"/>
       <c r="G354" s="8"/>
       <c r="H354" s="8"/>
-      <c r="I354" s="9"/>
-      <c r="J354" s="10"/>
-      <c r="K354" s="8"/>
+      <c r="I354" s="8"/>
+      <c r="J354" s="8"/>
+      <c r="K354" s="9"/>
       <c r="L354" s="8"/>
+      <c r="M354" s="8"/>
     </row>
     <row r="355">
       <c r="A355" s="8"/>
@@ -5291,10 +5647,11 @@
       <c r="F355" s="8"/>
       <c r="G355" s="8"/>
       <c r="H355" s="8"/>
-      <c r="I355" s="9"/>
-      <c r="J355" s="10"/>
-      <c r="K355" s="8"/>
+      <c r="I355" s="8"/>
+      <c r="J355" s="8"/>
+      <c r="K355" s="9"/>
       <c r="L355" s="8"/>
+      <c r="M355" s="8"/>
     </row>
     <row r="356">
       <c r="A356" s="8"/>
@@ -5305,10 +5662,11 @@
       <c r="F356" s="8"/>
       <c r="G356" s="8"/>
       <c r="H356" s="8"/>
-      <c r="I356" s="9"/>
-      <c r="J356" s="10"/>
-      <c r="K356" s="8"/>
+      <c r="I356" s="8"/>
+      <c r="J356" s="8"/>
+      <c r="K356" s="9"/>
       <c r="L356" s="8"/>
+      <c r="M356" s="8"/>
     </row>
     <row r="357">
       <c r="A357" s="8"/>
@@ -5319,10 +5677,11 @@
       <c r="F357" s="8"/>
       <c r="G357" s="8"/>
       <c r="H357" s="8"/>
-      <c r="I357" s="9"/>
-      <c r="J357" s="10"/>
-      <c r="K357" s="8"/>
+      <c r="I357" s="8"/>
+      <c r="J357" s="8"/>
+      <c r="K357" s="9"/>
       <c r="L357" s="8"/>
+      <c r="M357" s="8"/>
     </row>
     <row r="358">
       <c r="A358" s="8"/>
@@ -5333,10 +5692,11 @@
       <c r="F358" s="8"/>
       <c r="G358" s="8"/>
       <c r="H358" s="8"/>
-      <c r="I358" s="9"/>
-      <c r="J358" s="10"/>
-      <c r="K358" s="8"/>
+      <c r="I358" s="8"/>
+      <c r="J358" s="8"/>
+      <c r="K358" s="9"/>
       <c r="L358" s="8"/>
+      <c r="M358" s="8"/>
     </row>
     <row r="359">
       <c r="A359" s="8"/>
@@ -5347,10 +5707,11 @@
       <c r="F359" s="8"/>
       <c r="G359" s="8"/>
       <c r="H359" s="8"/>
-      <c r="I359" s="9"/>
-      <c r="J359" s="10"/>
-      <c r="K359" s="8"/>
+      <c r="I359" s="8"/>
+      <c r="J359" s="8"/>
+      <c r="K359" s="9"/>
       <c r="L359" s="8"/>
+      <c r="M359" s="8"/>
     </row>
     <row r="360">
       <c r="A360" s="8"/>
@@ -5361,10 +5722,11 @@
       <c r="F360" s="8"/>
       <c r="G360" s="8"/>
       <c r="H360" s="8"/>
-      <c r="I360" s="9"/>
-      <c r="J360" s="10"/>
-      <c r="K360" s="8"/>
+      <c r="I360" s="8"/>
+      <c r="J360" s="8"/>
+      <c r="K360" s="9"/>
       <c r="L360" s="8"/>
+      <c r="M360" s="8"/>
     </row>
     <row r="361">
       <c r="A361" s="8"/>
@@ -5375,10 +5737,11 @@
       <c r="F361" s="8"/>
       <c r="G361" s="8"/>
       <c r="H361" s="8"/>
-      <c r="I361" s="9"/>
-      <c r="J361" s="10"/>
-      <c r="K361" s="8"/>
+      <c r="I361" s="8"/>
+      <c r="J361" s="8"/>
+      <c r="K361" s="9"/>
       <c r="L361" s="8"/>
+      <c r="M361" s="8"/>
     </row>
     <row r="362">
       <c r="A362" s="8"/>
@@ -5389,10 +5752,11 @@
       <c r="F362" s="8"/>
       <c r="G362" s="8"/>
       <c r="H362" s="8"/>
-      <c r="I362" s="9"/>
-      <c r="J362" s="10"/>
-      <c r="K362" s="8"/>
+      <c r="I362" s="8"/>
+      <c r="J362" s="8"/>
+      <c r="K362" s="9"/>
       <c r="L362" s="8"/>
+      <c r="M362" s="8"/>
     </row>
     <row r="363">
       <c r="A363" s="8"/>
@@ -5403,10 +5767,11 @@
       <c r="F363" s="8"/>
       <c r="G363" s="8"/>
       <c r="H363" s="8"/>
-      <c r="I363" s="9"/>
-      <c r="J363" s="10"/>
-      <c r="K363" s="8"/>
+      <c r="I363" s="8"/>
+      <c r="J363" s="8"/>
+      <c r="K363" s="9"/>
       <c r="L363" s="8"/>
+      <c r="M363" s="8"/>
     </row>
     <row r="364">
       <c r="A364" s="8"/>
@@ -5417,10 +5782,11 @@
       <c r="F364" s="8"/>
       <c r="G364" s="8"/>
       <c r="H364" s="8"/>
-      <c r="I364" s="9"/>
-      <c r="J364" s="10"/>
-      <c r="K364" s="8"/>
+      <c r="I364" s="8"/>
+      <c r="J364" s="8"/>
+      <c r="K364" s="9"/>
       <c r="L364" s="8"/>
+      <c r="M364" s="8"/>
     </row>
     <row r="365">
       <c r="A365" s="8"/>
@@ -5431,10 +5797,11 @@
       <c r="F365" s="8"/>
       <c r="G365" s="8"/>
       <c r="H365" s="8"/>
-      <c r="I365" s="9"/>
-      <c r="J365" s="10"/>
-      <c r="K365" s="8"/>
+      <c r="I365" s="8"/>
+      <c r="J365" s="8"/>
+      <c r="K365" s="9"/>
       <c r="L365" s="8"/>
+      <c r="M365" s="8"/>
     </row>
     <row r="366">
       <c r="A366" s="8"/>
@@ -5445,10 +5812,11 @@
       <c r="F366" s="8"/>
       <c r="G366" s="8"/>
       <c r="H366" s="8"/>
-      <c r="I366" s="9"/>
-      <c r="J366" s="10"/>
-      <c r="K366" s="8"/>
+      <c r="I366" s="8"/>
+      <c r="J366" s="8"/>
+      <c r="K366" s="9"/>
       <c r="L366" s="8"/>
+      <c r="M366" s="8"/>
     </row>
     <row r="367">
       <c r="A367" s="8"/>
@@ -5459,10 +5827,11 @@
       <c r="F367" s="8"/>
       <c r="G367" s="8"/>
       <c r="H367" s="8"/>
-      <c r="I367" s="9"/>
-      <c r="J367" s="10"/>
-      <c r="K367" s="8"/>
+      <c r="I367" s="8"/>
+      <c r="J367" s="8"/>
+      <c r="K367" s="9"/>
       <c r="L367" s="8"/>
+      <c r="M367" s="8"/>
     </row>
     <row r="368">
       <c r="A368" s="8"/>
@@ -5473,10 +5842,11 @@
       <c r="F368" s="8"/>
       <c r="G368" s="8"/>
       <c r="H368" s="8"/>
-      <c r="I368" s="9"/>
-      <c r="J368" s="10"/>
-      <c r="K368" s="8"/>
+      <c r="I368" s="8"/>
+      <c r="J368" s="8"/>
+      <c r="K368" s="9"/>
       <c r="L368" s="8"/>
+      <c r="M368" s="8"/>
     </row>
     <row r="369">
       <c r="A369" s="8"/>
@@ -5487,10 +5857,11 @@
       <c r="F369" s="8"/>
       <c r="G369" s="8"/>
       <c r="H369" s="8"/>
-      <c r="I369" s="9"/>
-      <c r="J369" s="10"/>
-      <c r="K369" s="8"/>
+      <c r="I369" s="8"/>
+      <c r="J369" s="8"/>
+      <c r="K369" s="9"/>
       <c r="L369" s="8"/>
+      <c r="M369" s="8"/>
     </row>
     <row r="370">
       <c r="A370" s="8"/>
@@ -5501,10 +5872,11 @@
       <c r="F370" s="8"/>
       <c r="G370" s="8"/>
       <c r="H370" s="8"/>
-      <c r="I370" s="9"/>
-      <c r="J370" s="10"/>
-      <c r="K370" s="8"/>
+      <c r="I370" s="8"/>
+      <c r="J370" s="8"/>
+      <c r="K370" s="9"/>
       <c r="L370" s="8"/>
+      <c r="M370" s="8"/>
     </row>
     <row r="371">
       <c r="A371" s="8"/>
@@ -5515,10 +5887,11 @@
       <c r="F371" s="8"/>
       <c r="G371" s="8"/>
       <c r="H371" s="8"/>
-      <c r="I371" s="9"/>
-      <c r="J371" s="10"/>
-      <c r="K371" s="8"/>
+      <c r="I371" s="8"/>
+      <c r="J371" s="8"/>
+      <c r="K371" s="9"/>
       <c r="L371" s="8"/>
+      <c r="M371" s="8"/>
     </row>
     <row r="372">
       <c r="A372" s="8"/>
@@ -5529,10 +5902,11 @@
       <c r="F372" s="8"/>
       <c r="G372" s="8"/>
       <c r="H372" s="8"/>
-      <c r="I372" s="9"/>
-      <c r="J372" s="10"/>
-      <c r="K372" s="8"/>
+      <c r="I372" s="8"/>
+      <c r="J372" s="8"/>
+      <c r="K372" s="9"/>
       <c r="L372" s="8"/>
+      <c r="M372" s="8"/>
     </row>
     <row r="373">
       <c r="A373" s="8"/>
@@ -5543,10 +5917,11 @@
       <c r="F373" s="8"/>
       <c r="G373" s="8"/>
       <c r="H373" s="8"/>
-      <c r="I373" s="9"/>
-      <c r="J373" s="10"/>
-      <c r="K373" s="8"/>
+      <c r="I373" s="8"/>
+      <c r="J373" s="8"/>
+      <c r="K373" s="9"/>
       <c r="L373" s="8"/>
+      <c r="M373" s="8"/>
     </row>
     <row r="374">
       <c r="A374" s="8"/>
@@ -5557,10 +5932,11 @@
       <c r="F374" s="8"/>
       <c r="G374" s="8"/>
       <c r="H374" s="8"/>
-      <c r="I374" s="9"/>
-      <c r="J374" s="10"/>
-      <c r="K374" s="8"/>
+      <c r="I374" s="8"/>
+      <c r="J374" s="8"/>
+      <c r="K374" s="9"/>
       <c r="L374" s="8"/>
+      <c r="M374" s="8"/>
     </row>
     <row r="375">
       <c r="A375" s="8"/>
@@ -5571,10 +5947,11 @@
       <c r="F375" s="8"/>
       <c r="G375" s="8"/>
       <c r="H375" s="8"/>
-      <c r="I375" s="9"/>
-      <c r="J375" s="10"/>
-      <c r="K375" s="8"/>
+      <c r="I375" s="8"/>
+      <c r="J375" s="8"/>
+      <c r="K375" s="9"/>
       <c r="L375" s="8"/>
+      <c r="M375" s="8"/>
     </row>
     <row r="376">
       <c r="A376" s="8"/>
@@ -5585,10 +5962,11 @@
       <c r="F376" s="8"/>
       <c r="G376" s="8"/>
       <c r="H376" s="8"/>
-      <c r="I376" s="9"/>
-      <c r="J376" s="10"/>
-      <c r="K376" s="8"/>
+      <c r="I376" s="8"/>
+      <c r="J376" s="8"/>
+      <c r="K376" s="9"/>
       <c r="L376" s="8"/>
+      <c r="M376" s="8"/>
     </row>
     <row r="377">
       <c r="A377" s="8"/>
@@ -5599,10 +5977,11 @@
       <c r="F377" s="8"/>
       <c r="G377" s="8"/>
       <c r="H377" s="8"/>
-      <c r="I377" s="9"/>
-      <c r="J377" s="10"/>
-      <c r="K377" s="8"/>
+      <c r="I377" s="8"/>
+      <c r="J377" s="8"/>
+      <c r="K377" s="9"/>
       <c r="L377" s="8"/>
+      <c r="M377" s="8"/>
     </row>
     <row r="378">
       <c r="A378" s="8"/>
@@ -5613,10 +5992,11 @@
       <c r="F378" s="8"/>
       <c r="G378" s="8"/>
       <c r="H378" s="8"/>
-      <c r="I378" s="9"/>
-      <c r="J378" s="10"/>
-      <c r="K378" s="8"/>
+      <c r="I378" s="8"/>
+      <c r="J378" s="8"/>
+      <c r="K378" s="9"/>
       <c r="L378" s="8"/>
+      <c r="M378" s="8"/>
     </row>
     <row r="379">
       <c r="A379" s="8"/>
@@ -5627,10 +6007,11 @@
       <c r="F379" s="8"/>
       <c r="G379" s="8"/>
       <c r="H379" s="8"/>
-      <c r="I379" s="9"/>
-      <c r="J379" s="10"/>
-      <c r="K379" s="8"/>
+      <c r="I379" s="8"/>
+      <c r="J379" s="8"/>
+      <c r="K379" s="9"/>
       <c r="L379" s="8"/>
+      <c r="M379" s="8"/>
     </row>
     <row r="380">
       <c r="A380" s="8"/>
@@ -5641,10 +6022,11 @@
       <c r="F380" s="8"/>
       <c r="G380" s="8"/>
       <c r="H380" s="8"/>
-      <c r="I380" s="9"/>
-      <c r="J380" s="10"/>
-      <c r="K380" s="8"/>
+      <c r="I380" s="8"/>
+      <c r="J380" s="8"/>
+      <c r="K380" s="9"/>
       <c r="L380" s="8"/>
+      <c r="M380" s="8"/>
     </row>
     <row r="381">
       <c r="A381" s="8"/>
@@ -5655,10 +6037,11 @@
       <c r="F381" s="8"/>
       <c r="G381" s="8"/>
       <c r="H381" s="8"/>
-      <c r="I381" s="9"/>
-      <c r="J381" s="10"/>
-      <c r="K381" s="8"/>
+      <c r="I381" s="8"/>
+      <c r="J381" s="8"/>
+      <c r="K381" s="9"/>
       <c r="L381" s="8"/>
+      <c r="M381" s="8"/>
     </row>
     <row r="382">
       <c r="A382" s="8"/>
@@ -5669,10 +6052,11 @@
       <c r="F382" s="8"/>
       <c r="G382" s="8"/>
       <c r="H382" s="8"/>
-      <c r="I382" s="9"/>
-      <c r="J382" s="10"/>
-      <c r="K382" s="8"/>
+      <c r="I382" s="8"/>
+      <c r="J382" s="8"/>
+      <c r="K382" s="9"/>
       <c r="L382" s="8"/>
+      <c r="M382" s="8"/>
     </row>
     <row r="383">
       <c r="A383" s="8"/>
@@ -5683,10 +6067,11 @@
       <c r="F383" s="8"/>
       <c r="G383" s="8"/>
       <c r="H383" s="8"/>
-      <c r="I383" s="9"/>
-      <c r="J383" s="10"/>
-      <c r="K383" s="8"/>
+      <c r="I383" s="8"/>
+      <c r="J383" s="8"/>
+      <c r="K383" s="9"/>
       <c r="L383" s="8"/>
+      <c r="M383" s="8"/>
     </row>
     <row r="384">
       <c r="A384" s="8"/>
@@ -5697,10 +6082,11 @@
       <c r="F384" s="8"/>
       <c r="G384" s="8"/>
       <c r="H384" s="8"/>
-      <c r="I384" s="9"/>
-      <c r="J384" s="10"/>
-      <c r="K384" s="8"/>
+      <c r="I384" s="8"/>
+      <c r="J384" s="8"/>
+      <c r="K384" s="9"/>
       <c r="L384" s="8"/>
+      <c r="M384" s="8"/>
     </row>
     <row r="385">
       <c r="A385" s="8"/>
@@ -5711,10 +6097,11 @@
       <c r="F385" s="8"/>
       <c r="G385" s="8"/>
       <c r="H385" s="8"/>
-      <c r="I385" s="9"/>
-      <c r="J385" s="10"/>
-      <c r="K385" s="8"/>
+      <c r="I385" s="8"/>
+      <c r="J385" s="8"/>
+      <c r="K385" s="9"/>
       <c r="L385" s="8"/>
+      <c r="M385" s="8"/>
     </row>
     <row r="386">
       <c r="A386" s="8"/>
@@ -5725,10 +6112,11 @@
       <c r="F386" s="8"/>
       <c r="G386" s="8"/>
       <c r="H386" s="8"/>
-      <c r="I386" s="9"/>
-      <c r="J386" s="10"/>
-      <c r="K386" s="8"/>
+      <c r="I386" s="8"/>
+      <c r="J386" s="8"/>
+      <c r="K386" s="9"/>
       <c r="L386" s="8"/>
+      <c r="M386" s="8"/>
     </row>
     <row r="387">
       <c r="A387" s="8"/>
@@ -5739,10 +6127,11 @@
       <c r="F387" s="8"/>
       <c r="G387" s="8"/>
       <c r="H387" s="8"/>
-      <c r="I387" s="9"/>
-      <c r="J387" s="10"/>
-      <c r="K387" s="8"/>
+      <c r="I387" s="8"/>
+      <c r="J387" s="8"/>
+      <c r="K387" s="9"/>
       <c r="L387" s="8"/>
+      <c r="M387" s="8"/>
     </row>
     <row r="388">
       <c r="A388" s="8"/>
@@ -5753,10 +6142,11 @@
       <c r="F388" s="8"/>
       <c r="G388" s="8"/>
       <c r="H388" s="8"/>
-      <c r="I388" s="9"/>
-      <c r="J388" s="10"/>
-      <c r="K388" s="8"/>
+      <c r="I388" s="8"/>
+      <c r="J388" s="8"/>
+      <c r="K388" s="9"/>
       <c r="L388" s="8"/>
+      <c r="M388" s="8"/>
     </row>
     <row r="389">
       <c r="A389" s="8"/>
@@ -5767,10 +6157,11 @@
       <c r="F389" s="8"/>
       <c r="G389" s="8"/>
       <c r="H389" s="8"/>
-      <c r="I389" s="9"/>
-      <c r="J389" s="10"/>
-      <c r="K389" s="8"/>
+      <c r="I389" s="8"/>
+      <c r="J389" s="8"/>
+      <c r="K389" s="9"/>
       <c r="L389" s="8"/>
+      <c r="M389" s="8"/>
     </row>
     <row r="390">
       <c r="A390" s="8"/>
@@ -5781,10 +6172,11 @@
       <c r="F390" s="8"/>
       <c r="G390" s="8"/>
       <c r="H390" s="8"/>
-      <c r="I390" s="9"/>
-      <c r="J390" s="10"/>
-      <c r="K390" s="8"/>
+      <c r="I390" s="8"/>
+      <c r="J390" s="8"/>
+      <c r="K390" s="9"/>
       <c r="L390" s="8"/>
+      <c r="M390" s="8"/>
     </row>
     <row r="391">
       <c r="A391" s="8"/>
@@ -5795,10 +6187,11 @@
       <c r="F391" s="8"/>
       <c r="G391" s="8"/>
       <c r="H391" s="8"/>
-      <c r="I391" s="9"/>
-      <c r="J391" s="10"/>
-      <c r="K391" s="8"/>
+      <c r="I391" s="8"/>
+      <c r="J391" s="8"/>
+      <c r="K391" s="9"/>
       <c r="L391" s="8"/>
+      <c r="M391" s="8"/>
     </row>
     <row r="392">
       <c r="A392" s="8"/>
@@ -5809,10 +6202,11 @@
       <c r="F392" s="8"/>
       <c r="G392" s="8"/>
       <c r="H392" s="8"/>
-      <c r="I392" s="9"/>
-      <c r="J392" s="10"/>
-      <c r="K392" s="8"/>
+      <c r="I392" s="8"/>
+      <c r="J392" s="8"/>
+      <c r="K392" s="9"/>
       <c r="L392" s="8"/>
+      <c r="M392" s="8"/>
     </row>
     <row r="393">
       <c r="A393" s="8"/>
@@ -5823,10 +6217,11 @@
       <c r="F393" s="8"/>
       <c r="G393" s="8"/>
       <c r="H393" s="8"/>
-      <c r="I393" s="9"/>
-      <c r="J393" s="10"/>
-      <c r="K393" s="8"/>
+      <c r="I393" s="8"/>
+      <c r="J393" s="8"/>
+      <c r="K393" s="9"/>
       <c r="L393" s="8"/>
+      <c r="M393" s="8"/>
     </row>
     <row r="394">
       <c r="A394" s="8"/>
@@ -5837,10 +6232,11 @@
       <c r="F394" s="8"/>
       <c r="G394" s="8"/>
       <c r="H394" s="8"/>
-      <c r="I394" s="9"/>
-      <c r="J394" s="10"/>
-      <c r="K394" s="8"/>
+      <c r="I394" s="8"/>
+      <c r="J394" s="8"/>
+      <c r="K394" s="9"/>
       <c r="L394" s="8"/>
+      <c r="M394" s="8"/>
     </row>
     <row r="395">
       <c r="A395" s="8"/>
@@ -5851,10 +6247,11 @@
       <c r="F395" s="8"/>
       <c r="G395" s="8"/>
       <c r="H395" s="8"/>
-      <c r="I395" s="9"/>
-      <c r="J395" s="10"/>
-      <c r="K395" s="8"/>
+      <c r="I395" s="8"/>
+      <c r="J395" s="8"/>
+      <c r="K395" s="9"/>
       <c r="L395" s="8"/>
+      <c r="M395" s="8"/>
     </row>
     <row r="396">
       <c r="A396" s="8"/>
@@ -5865,10 +6262,11 @@
       <c r="F396" s="8"/>
       <c r="G396" s="8"/>
       <c r="H396" s="8"/>
-      <c r="I396" s="9"/>
-      <c r="J396" s="10"/>
-      <c r="K396" s="8"/>
+      <c r="I396" s="8"/>
+      <c r="J396" s="8"/>
+      <c r="K396" s="9"/>
       <c r="L396" s="8"/>
+      <c r="M396" s="8"/>
     </row>
     <row r="397">
       <c r="A397" s="8"/>
@@ -5879,10 +6277,11 @@
       <c r="F397" s="8"/>
       <c r="G397" s="8"/>
       <c r="H397" s="8"/>
-      <c r="I397" s="9"/>
-      <c r="J397" s="10"/>
-      <c r="K397" s="8"/>
+      <c r="I397" s="8"/>
+      <c r="J397" s="8"/>
+      <c r="K397" s="9"/>
       <c r="L397" s="8"/>
+      <c r="M397" s="8"/>
     </row>
     <row r="398">
       <c r="A398" s="8"/>
@@ -5893,10 +6292,11 @@
       <c r="F398" s="8"/>
       <c r="G398" s="8"/>
       <c r="H398" s="8"/>
-      <c r="I398" s="9"/>
-      <c r="J398" s="10"/>
-      <c r="K398" s="8"/>
+      <c r="I398" s="8"/>
+      <c r="J398" s="8"/>
+      <c r="K398" s="9"/>
       <c r="L398" s="8"/>
+      <c r="M398" s="8"/>
     </row>
     <row r="399">
       <c r="A399" s="8"/>
@@ -5907,10 +6307,11 @@
       <c r="F399" s="8"/>
       <c r="G399" s="8"/>
       <c r="H399" s="8"/>
-      <c r="I399" s="9"/>
-      <c r="J399" s="10"/>
-      <c r="K399" s="8"/>
+      <c r="I399" s="8"/>
+      <c r="J399" s="8"/>
+      <c r="K399" s="9"/>
       <c r="L399" s="8"/>
+      <c r="M399" s="8"/>
     </row>
     <row r="400">
       <c r="A400" s="8"/>
@@ -5921,10 +6322,11 @@
       <c r="F400" s="8"/>
       <c r="G400" s="8"/>
       <c r="H400" s="8"/>
-      <c r="I400" s="9"/>
-      <c r="J400" s="10"/>
-      <c r="K400" s="8"/>
+      <c r="I400" s="8"/>
+      <c r="J400" s="8"/>
+      <c r="K400" s="9"/>
       <c r="L400" s="8"/>
+      <c r="M400" s="8"/>
     </row>
     <row r="401">
       <c r="A401" s="8"/>
@@ -5935,10 +6337,11 @@
       <c r="F401" s="8"/>
       <c r="G401" s="8"/>
       <c r="H401" s="8"/>
-      <c r="I401" s="9"/>
-      <c r="J401" s="10"/>
-      <c r="K401" s="8"/>
+      <c r="I401" s="8"/>
+      <c r="J401" s="8"/>
+      <c r="K401" s="9"/>
       <c r="L401" s="8"/>
+      <c r="M401" s="8"/>
     </row>
     <row r="402">
       <c r="A402" s="8"/>
@@ -5949,10 +6352,11 @@
       <c r="F402" s="8"/>
       <c r="G402" s="8"/>
       <c r="H402" s="8"/>
-      <c r="I402" s="9"/>
-      <c r="J402" s="10"/>
-      <c r="K402" s="8"/>
+      <c r="I402" s="8"/>
+      <c r="J402" s="8"/>
+      <c r="K402" s="9"/>
       <c r="L402" s="8"/>
+      <c r="M402" s="8"/>
     </row>
     <row r="403">
       <c r="A403" s="8"/>
@@ -5963,10 +6367,11 @@
       <c r="F403" s="8"/>
       <c r="G403" s="8"/>
       <c r="H403" s="8"/>
-      <c r="I403" s="9"/>
-      <c r="J403" s="10"/>
-      <c r="K403" s="8"/>
+      <c r="I403" s="8"/>
+      <c r="J403" s="8"/>
+      <c r="K403" s="9"/>
       <c r="L403" s="8"/>
+      <c r="M403" s="8"/>
     </row>
     <row r="404">
       <c r="A404" s="8"/>
@@ -5977,10 +6382,11 @@
       <c r="F404" s="8"/>
       <c r="G404" s="8"/>
       <c r="H404" s="8"/>
-      <c r="I404" s="9"/>
-      <c r="J404" s="10"/>
-      <c r="K404" s="8"/>
+      <c r="I404" s="8"/>
+      <c r="J404" s="8"/>
+      <c r="K404" s="9"/>
       <c r="L404" s="8"/>
+      <c r="M404" s="8"/>
     </row>
     <row r="405">
       <c r="A405" s="8"/>
@@ -5991,10 +6397,11 @@
       <c r="F405" s="8"/>
       <c r="G405" s="8"/>
       <c r="H405" s="8"/>
-      <c r="I405" s="9"/>
-      <c r="J405" s="10"/>
-      <c r="K405" s="8"/>
+      <c r="I405" s="8"/>
+      <c r="J405" s="8"/>
+      <c r="K405" s="9"/>
       <c r="L405" s="8"/>
+      <c r="M405" s="8"/>
     </row>
     <row r="406">
       <c r="A406" s="8"/>
@@ -6005,10 +6412,11 @@
       <c r="F406" s="8"/>
       <c r="G406" s="8"/>
       <c r="H406" s="8"/>
-      <c r="I406" s="9"/>
-      <c r="J406" s="10"/>
-      <c r="K406" s="8"/>
+      <c r="I406" s="8"/>
+      <c r="J406" s="8"/>
+      <c r="K406" s="9"/>
       <c r="L406" s="8"/>
+      <c r="M406" s="8"/>
     </row>
     <row r="407">
       <c r="A407" s="8"/>
@@ -6019,10 +6427,11 @@
       <c r="F407" s="8"/>
       <c r="G407" s="8"/>
       <c r="H407" s="8"/>
-      <c r="I407" s="9"/>
-      <c r="J407" s="10"/>
-      <c r="K407" s="8"/>
+      <c r="I407" s="8"/>
+      <c r="J407" s="8"/>
+      <c r="K407" s="9"/>
       <c r="L407" s="8"/>
+      <c r="M407" s="8"/>
     </row>
     <row r="408">
       <c r="A408" s="8"/>
@@ -6033,10 +6442,11 @@
       <c r="F408" s="8"/>
       <c r="G408" s="8"/>
       <c r="H408" s="8"/>
-      <c r="I408" s="9"/>
-      <c r="J408" s="10"/>
-      <c r="K408" s="8"/>
+      <c r="I408" s="8"/>
+      <c r="J408" s="8"/>
+      <c r="K408" s="9"/>
       <c r="L408" s="8"/>
+      <c r="M408" s="8"/>
     </row>
     <row r="409">
       <c r="A409" s="8"/>
@@ -6047,10 +6457,11 @@
       <c r="F409" s="8"/>
       <c r="G409" s="8"/>
       <c r="H409" s="8"/>
-      <c r="I409" s="9"/>
-      <c r="J409" s="10"/>
-      <c r="K409" s="8"/>
+      <c r="I409" s="8"/>
+      <c r="J409" s="8"/>
+      <c r="K409" s="9"/>
       <c r="L409" s="8"/>
+      <c r="M409" s="8"/>
     </row>
     <row r="410">
       <c r="A410" s="8"/>
@@ -6061,10 +6472,11 @@
       <c r="F410" s="8"/>
       <c r="G410" s="8"/>
       <c r="H410" s="8"/>
-      <c r="I410" s="9"/>
-      <c r="J410" s="10"/>
-      <c r="K410" s="8"/>
+      <c r="I410" s="8"/>
+      <c r="J410" s="8"/>
+      <c r="K410" s="9"/>
       <c r="L410" s="8"/>
+      <c r="M410" s="8"/>
     </row>
     <row r="411">
       <c r="A411" s="8"/>
@@ -6075,10 +6487,11 @@
       <c r="F411" s="8"/>
       <c r="G411" s="8"/>
       <c r="H411" s="8"/>
-      <c r="I411" s="9"/>
-      <c r="J411" s="10"/>
-      <c r="K411" s="8"/>
+      <c r="I411" s="8"/>
+      <c r="J411" s="8"/>
+      <c r="K411" s="9"/>
       <c r="L411" s="8"/>
+      <c r="M411" s="8"/>
     </row>
     <row r="412">
       <c r="A412" s="8"/>
@@ -6089,10 +6502,11 @@
       <c r="F412" s="8"/>
       <c r="G412" s="8"/>
       <c r="H412" s="8"/>
-      <c r="I412" s="9"/>
-      <c r="J412" s="10"/>
-      <c r="K412" s="8"/>
+      <c r="I412" s="8"/>
+      <c r="J412" s="8"/>
+      <c r="K412" s="9"/>
       <c r="L412" s="8"/>
+      <c r="M412" s="8"/>
     </row>
     <row r="413">
       <c r="A413" s="8"/>
@@ -6103,10 +6517,11 @@
       <c r="F413" s="8"/>
       <c r="G413" s="8"/>
       <c r="H413" s="8"/>
-      <c r="I413" s="9"/>
-      <c r="J413" s="10"/>
-      <c r="K413" s="8"/>
+      <c r="I413" s="8"/>
+      <c r="J413" s="8"/>
+      <c r="K413" s="9"/>
       <c r="L413" s="8"/>
+      <c r="M413" s="8"/>
     </row>
     <row r="414">
       <c r="A414" s="8"/>
@@ -6117,10 +6532,11 @@
       <c r="F414" s="8"/>
       <c r="G414" s="8"/>
       <c r="H414" s="8"/>
-      <c r="I414" s="9"/>
-      <c r="J414" s="10"/>
-      <c r="K414" s="8"/>
+      <c r="I414" s="8"/>
+      <c r="J414" s="8"/>
+      <c r="K414" s="9"/>
       <c r="L414" s="8"/>
+      <c r="M414" s="8"/>
     </row>
     <row r="415">
       <c r="A415" s="8"/>
@@ -6131,10 +6547,11 @@
       <c r="F415" s="8"/>
       <c r="G415" s="8"/>
       <c r="H415" s="8"/>
-      <c r="I415" s="9"/>
-      <c r="J415" s="10"/>
-      <c r="K415" s="8"/>
+      <c r="I415" s="8"/>
+      <c r="J415" s="8"/>
+      <c r="K415" s="9"/>
       <c r="L415" s="8"/>
+      <c r="M415" s="8"/>
     </row>
     <row r="416">
       <c r="A416" s="8"/>
@@ -6145,10 +6562,11 @@
       <c r="F416" s="8"/>
       <c r="G416" s="8"/>
       <c r="H416" s="8"/>
-      <c r="I416" s="9"/>
-      <c r="J416" s="10"/>
-      <c r="K416" s="8"/>
+      <c r="I416" s="8"/>
+      <c r="J416" s="8"/>
+      <c r="K416" s="9"/>
       <c r="L416" s="8"/>
+      <c r="M416" s="8"/>
     </row>
     <row r="417">
       <c r="A417" s="8"/>
@@ -6159,10 +6577,11 @@
       <c r="F417" s="8"/>
       <c r="G417" s="8"/>
       <c r="H417" s="8"/>
-      <c r="I417" s="9"/>
-      <c r="J417" s="10"/>
-      <c r="K417" s="8"/>
+      <c r="I417" s="8"/>
+      <c r="J417" s="8"/>
+      <c r="K417" s="9"/>
       <c r="L417" s="8"/>
+      <c r="M417" s="8"/>
     </row>
     <row r="418">
       <c r="A418" s="8"/>
@@ -6173,10 +6592,11 @@
       <c r="F418" s="8"/>
       <c r="G418" s="8"/>
       <c r="H418" s="8"/>
-      <c r="I418" s="9"/>
-      <c r="J418" s="10"/>
-      <c r="K418" s="8"/>
+      <c r="I418" s="8"/>
+      <c r="J418" s="8"/>
+      <c r="K418" s="9"/>
       <c r="L418" s="8"/>
+      <c r="M418" s="8"/>
     </row>
     <row r="419">
       <c r="A419" s="8"/>
@@ -6187,10 +6607,11 @@
       <c r="F419" s="8"/>
       <c r="G419" s="8"/>
       <c r="H419" s="8"/>
-      <c r="I419" s="9"/>
-      <c r="J419" s="10"/>
-      <c r="K419" s="8"/>
+      <c r="I419" s="8"/>
+      <c r="J419" s="8"/>
+      <c r="K419" s="9"/>
       <c r="L419" s="8"/>
+      <c r="M419" s="8"/>
     </row>
     <row r="420">
       <c r="A420" s="8"/>
@@ -6201,10 +6622,11 @@
       <c r="F420" s="8"/>
       <c r="G420" s="8"/>
       <c r="H420" s="8"/>
-      <c r="I420" s="9"/>
-      <c r="J420" s="10"/>
-      <c r="K420" s="8"/>
+      <c r="I420" s="8"/>
+      <c r="J420" s="8"/>
+      <c r="K420" s="9"/>
       <c r="L420" s="8"/>
+      <c r="M420" s="8"/>
     </row>
     <row r="421">
       <c r="A421" s="8"/>
@@ -6215,10 +6637,11 @@
       <c r="F421" s="8"/>
       <c r="G421" s="8"/>
       <c r="H421" s="8"/>
-      <c r="I421" s="9"/>
-      <c r="J421" s="10"/>
-      <c r="K421" s="8"/>
+      <c r="I421" s="8"/>
+      <c r="J421" s="8"/>
+      <c r="K421" s="9"/>
       <c r="L421" s="8"/>
+      <c r="M421" s="8"/>
     </row>
     <row r="422">
       <c r="A422" s="8"/>
@@ -6229,10 +6652,11 @@
       <c r="F422" s="8"/>
       <c r="G422" s="8"/>
       <c r="H422" s="8"/>
-      <c r="I422" s="9"/>
-      <c r="J422" s="10"/>
-      <c r="K422" s="8"/>
+      <c r="I422" s="8"/>
+      <c r="J422" s="8"/>
+      <c r="K422" s="9"/>
       <c r="L422" s="8"/>
+      <c r="M422" s="8"/>
     </row>
     <row r="423">
       <c r="A423" s="8"/>
@@ -6243,10 +6667,11 @@
       <c r="F423" s="8"/>
       <c r="G423" s="8"/>
       <c r="H423" s="8"/>
-      <c r="I423" s="9"/>
-      <c r="J423" s="10"/>
-      <c r="K423" s="8"/>
+      <c r="I423" s="8"/>
+      <c r="J423" s="8"/>
+      <c r="K423" s="9"/>
       <c r="L423" s="8"/>
+      <c r="M423" s="8"/>
     </row>
     <row r="424">
       <c r="A424" s="8"/>
@@ -6257,10 +6682,11 @@
       <c r="F424" s="8"/>
       <c r="G424" s="8"/>
       <c r="H424" s="8"/>
-      <c r="I424" s="9"/>
-      <c r="J424" s="10"/>
-      <c r="K424" s="8"/>
+      <c r="I424" s="8"/>
+      <c r="J424" s="8"/>
+      <c r="K424" s="9"/>
       <c r="L424" s="8"/>
+      <c r="M424" s="8"/>
     </row>
     <row r="425">
       <c r="A425" s="8"/>
@@ -6271,10 +6697,11 @@
       <c r="F425" s="8"/>
       <c r="G425" s="8"/>
       <c r="H425" s="8"/>
-      <c r="I425" s="9"/>
-      <c r="J425" s="10"/>
-      <c r="K425" s="8"/>
+      <c r="I425" s="8"/>
+      <c r="J425" s="8"/>
+      <c r="K425" s="9"/>
       <c r="L425" s="8"/>
+      <c r="M425" s="8"/>
     </row>
     <row r="426">
       <c r="A426" s="8"/>
@@ -6285,10 +6712,11 @@
       <c r="F426" s="8"/>
       <c r="G426" s="8"/>
       <c r="H426" s="8"/>
-      <c r="I426" s="9"/>
-      <c r="J426" s="10"/>
-      <c r="K426" s="8"/>
+      <c r="I426" s="8"/>
+      <c r="J426" s="8"/>
+      <c r="K426" s="9"/>
       <c r="L426" s="8"/>
+      <c r="M426" s="8"/>
     </row>
     <row r="427">
       <c r="A427" s="8"/>
@@ -6299,10 +6727,11 @@
       <c r="F427" s="8"/>
       <c r="G427" s="8"/>
       <c r="H427" s="8"/>
-      <c r="I427" s="9"/>
-      <c r="J427" s="10"/>
-      <c r="K427" s="8"/>
+      <c r="I427" s="8"/>
+      <c r="J427" s="8"/>
+      <c r="K427" s="9"/>
       <c r="L427" s="8"/>
+      <c r="M427" s="8"/>
     </row>
     <row r="428">
       <c r="A428" s="8"/>
@@ -6313,10 +6742,11 @@
       <c r="F428" s="8"/>
       <c r="G428" s="8"/>
       <c r="H428" s="8"/>
-      <c r="I428" s="9"/>
-      <c r="J428" s="10"/>
-      <c r="K428" s="8"/>
+      <c r="I428" s="8"/>
+      <c r="J428" s="8"/>
+      <c r="K428" s="9"/>
       <c r="L428" s="8"/>
+      <c r="M428" s="8"/>
     </row>
     <row r="429">
       <c r="A429" s="8"/>
@@ -6327,10 +6757,11 @@
       <c r="F429" s="8"/>
       <c r="G429" s="8"/>
       <c r="H429" s="8"/>
-      <c r="I429" s="9"/>
-      <c r="J429" s="10"/>
-      <c r="K429" s="8"/>
+      <c r="I429" s="8"/>
+      <c r="J429" s="8"/>
+      <c r="K429" s="9"/>
       <c r="L429" s="8"/>
+      <c r="M429" s="8"/>
     </row>
     <row r="430">
       <c r="A430" s="8"/>
@@ -6341,10 +6772,11 @@
       <c r="F430" s="8"/>
       <c r="G430" s="8"/>
       <c r="H430" s="8"/>
-      <c r="I430" s="9"/>
-      <c r="J430" s="10"/>
-      <c r="K430" s="8"/>
+      <c r="I430" s="8"/>
+      <c r="J430" s="8"/>
+      <c r="K430" s="9"/>
       <c r="L430" s="8"/>
+      <c r="M430" s="8"/>
     </row>
     <row r="431">
       <c r="A431" s="8"/>
@@ -6355,10 +6787,11 @@
       <c r="F431" s="8"/>
       <c r="G431" s="8"/>
       <c r="H431" s="8"/>
-      <c r="I431" s="9"/>
-      <c r="J431" s="10"/>
-      <c r="K431" s="8"/>
+      <c r="I431" s="8"/>
+      <c r="J431" s="8"/>
+      <c r="K431" s="9"/>
       <c r="L431" s="8"/>
+      <c r="M431" s="8"/>
     </row>
     <row r="432">
       <c r="A432" s="8"/>
@@ -6369,10 +6802,11 @@
       <c r="F432" s="8"/>
       <c r="G432" s="8"/>
       <c r="H432" s="8"/>
-      <c r="I432" s="9"/>
-      <c r="J432" s="10"/>
-      <c r="K432" s="8"/>
+      <c r="I432" s="8"/>
+      <c r="J432" s="8"/>
+      <c r="K432" s="9"/>
       <c r="L432" s="8"/>
+      <c r="M432" s="8"/>
     </row>
     <row r="433">
       <c r="A433" s="8"/>
@@ -6383,10 +6817,11 @@
       <c r="F433" s="8"/>
       <c r="G433" s="8"/>
       <c r="H433" s="8"/>
-      <c r="I433" s="9"/>
-      <c r="J433" s="10"/>
-      <c r="K433" s="8"/>
+      <c r="I433" s="8"/>
+      <c r="J433" s="8"/>
+      <c r="K433" s="9"/>
       <c r="L433" s="8"/>
+      <c r="M433" s="8"/>
     </row>
     <row r="434">
       <c r="A434" s="8"/>
@@ -6397,10 +6832,11 @@
       <c r="F434" s="8"/>
       <c r="G434" s="8"/>
       <c r="H434" s="8"/>
-      <c r="I434" s="9"/>
-      <c r="J434" s="10"/>
-      <c r="K434" s="8"/>
+      <c r="I434" s="8"/>
+      <c r="J434" s="8"/>
+      <c r="K434" s="9"/>
       <c r="L434" s="8"/>
+      <c r="M434" s="8"/>
     </row>
     <row r="435">
       <c r="A435" s="8"/>
@@ -6411,10 +6847,11 @@
       <c r="F435" s="8"/>
       <c r="G435" s="8"/>
       <c r="H435" s="8"/>
-      <c r="I435" s="9"/>
-      <c r="J435" s="10"/>
-      <c r="K435" s="8"/>
+      <c r="I435" s="8"/>
+      <c r="J435" s="8"/>
+      <c r="K435" s="9"/>
       <c r="L435" s="8"/>
+      <c r="M435" s="8"/>
     </row>
     <row r="436">
       <c r="A436" s="8"/>
@@ -6425,10 +6862,11 @@
       <c r="F436" s="8"/>
       <c r="G436" s="8"/>
       <c r="H436" s="8"/>
-      <c r="I436" s="9"/>
-      <c r="J436" s="10"/>
-      <c r="K436" s="8"/>
+      <c r="I436" s="8"/>
+      <c r="J436" s="8"/>
+      <c r="K436" s="9"/>
       <c r="L436" s="8"/>
+      <c r="M436" s="8"/>
     </row>
     <row r="437">
       <c r="A437" s="8"/>
@@ -6439,10 +6877,11 @@
       <c r="F437" s="8"/>
       <c r="G437" s="8"/>
       <c r="H437" s="8"/>
-      <c r="I437" s="9"/>
-      <c r="J437" s="10"/>
-      <c r="K437" s="8"/>
+      <c r="I437" s="8"/>
+      <c r="J437" s="8"/>
+      <c r="K437" s="9"/>
       <c r="L437" s="8"/>
+      <c r="M437" s="8"/>
     </row>
     <row r="438">
       <c r="A438" s="8"/>
@@ -6453,10 +6892,11 @@
       <c r="F438" s="8"/>
       <c r="G438" s="8"/>
       <c r="H438" s="8"/>
-      <c r="I438" s="9"/>
-      <c r="J438" s="10"/>
-      <c r="K438" s="8"/>
+      <c r="I438" s="8"/>
+      <c r="J438" s="8"/>
+      <c r="K438" s="9"/>
       <c r="L438" s="8"/>
+      <c r="M438" s="8"/>
     </row>
     <row r="439">
       <c r="A439" s="8"/>
@@ -6467,10 +6907,11 @@
       <c r="F439" s="8"/>
       <c r="G439" s="8"/>
       <c r="H439" s="8"/>
-      <c r="I439" s="9"/>
-      <c r="J439" s="10"/>
-      <c r="K439" s="8"/>
+      <c r="I439" s="8"/>
+      <c r="J439" s="8"/>
+      <c r="K439" s="9"/>
       <c r="L439" s="8"/>
+      <c r="M439" s="8"/>
     </row>
     <row r="440">
       <c r="A440" s="8"/>
@@ -6481,10 +6922,11 @@
       <c r="F440" s="8"/>
       <c r="G440" s="8"/>
       <c r="H440" s="8"/>
-      <c r="I440" s="9"/>
-      <c r="J440" s="10"/>
-      <c r="K440" s="8"/>
+      <c r="I440" s="8"/>
+      <c r="J440" s="8"/>
+      <c r="K440" s="9"/>
       <c r="L440" s="8"/>
+      <c r="M440" s="8"/>
     </row>
     <row r="441">
       <c r="A441" s="8"/>
@@ -6495,10 +6937,11 @@
       <c r="F441" s="8"/>
       <c r="G441" s="8"/>
       <c r="H441" s="8"/>
-      <c r="I441" s="9"/>
-      <c r="J441" s="10"/>
-      <c r="K441" s="8"/>
+      <c r="I441" s="8"/>
+      <c r="J441" s="8"/>
+      <c r="K441" s="9"/>
       <c r="L441" s="8"/>
+      <c r="M441" s="8"/>
     </row>
     <row r="442">
       <c r="A442" s="8"/>
@@ -6509,10 +6952,11 @@
       <c r="F442" s="8"/>
       <c r="G442" s="8"/>
       <c r="H442" s="8"/>
-      <c r="I442" s="9"/>
-      <c r="J442" s="10"/>
-      <c r="K442" s="8"/>
+      <c r="I442" s="8"/>
+      <c r="J442" s="8"/>
+      <c r="K442" s="9"/>
       <c r="L442" s="8"/>
+      <c r="M442" s="8"/>
     </row>
     <row r="443">
       <c r="A443" s="8"/>
@@ -6523,10 +6967,11 @@
       <c r="F443" s="8"/>
       <c r="G443" s="8"/>
       <c r="H443" s="8"/>
-      <c r="I443" s="9"/>
-      <c r="J443" s="10"/>
-      <c r="K443" s="8"/>
+      <c r="I443" s="8"/>
+      <c r="J443" s="8"/>
+      <c r="K443" s="9"/>
       <c r="L443" s="8"/>
+      <c r="M443" s="8"/>
     </row>
     <row r="444">
       <c r="A444" s="8"/>
@@ -6537,10 +6982,11 @@
       <c r="F444" s="8"/>
       <c r="G444" s="8"/>
       <c r="H444" s="8"/>
-      <c r="I444" s="9"/>
-      <c r="J444" s="10"/>
-      <c r="K444" s="8"/>
+      <c r="I444" s="8"/>
+      <c r="J444" s="8"/>
+      <c r="K444" s="9"/>
       <c r="L444" s="8"/>
+      <c r="M444" s="8"/>
     </row>
     <row r="445">
       <c r="A445" s="8"/>
@@ -6551,10 +6997,11 @@
       <c r="F445" s="8"/>
       <c r="G445" s="8"/>
       <c r="H445" s="8"/>
-      <c r="I445" s="9"/>
-      <c r="J445" s="10"/>
-      <c r="K445" s="8"/>
+      <c r="I445" s="8"/>
+      <c r="J445" s="8"/>
+      <c r="K445" s="9"/>
       <c r="L445" s="8"/>
+      <c r="M445" s="8"/>
     </row>
     <row r="446">
       <c r="A446" s="8"/>
@@ -6565,10 +7012,11 @@
       <c r="F446" s="8"/>
       <c r="G446" s="8"/>
       <c r="H446" s="8"/>
-      <c r="I446" s="9"/>
-      <c r="J446" s="10"/>
-      <c r="K446" s="8"/>
+      <c r="I446" s="8"/>
+      <c r="J446" s="8"/>
+      <c r="K446" s="9"/>
       <c r="L446" s="8"/>
+      <c r="M446" s="8"/>
     </row>
     <row r="447">
       <c r="A447" s="8"/>
@@ -6579,10 +7027,11 @@
       <c r="F447" s="8"/>
       <c r="G447" s="8"/>
       <c r="H447" s="8"/>
-      <c r="I447" s="9"/>
-      <c r="J447" s="10"/>
-      <c r="K447" s="8"/>
+      <c r="I447" s="8"/>
+      <c r="J447" s="8"/>
+      <c r="K447" s="9"/>
       <c r="L447" s="8"/>
+      <c r="M447" s="8"/>
     </row>
     <row r="448">
       <c r="A448" s="8"/>
@@ -6593,10 +7042,11 @@
       <c r="F448" s="8"/>
       <c r="G448" s="8"/>
       <c r="H448" s="8"/>
-      <c r="I448" s="9"/>
-      <c r="J448" s="10"/>
-      <c r="K448" s="8"/>
+      <c r="I448" s="8"/>
+      <c r="J448" s="8"/>
+      <c r="K448" s="9"/>
       <c r="L448" s="8"/>
+      <c r="M448" s="8"/>
     </row>
     <row r="449">
       <c r="A449" s="8"/>
@@ -6607,10 +7057,11 @@
       <c r="F449" s="8"/>
       <c r="G449" s="8"/>
       <c r="H449" s="8"/>
-      <c r="I449" s="9"/>
-      <c r="J449" s="10"/>
-      <c r="K449" s="8"/>
+      <c r="I449" s="8"/>
+      <c r="J449" s="8"/>
+      <c r="K449" s="9"/>
       <c r="L449" s="8"/>
+      <c r="M449" s="8"/>
     </row>
     <row r="450">
       <c r="A450" s="8"/>
@@ -6621,10 +7072,11 @@
       <c r="F450" s="8"/>
       <c r="G450" s="8"/>
       <c r="H450" s="8"/>
-      <c r="I450" s="9"/>
-      <c r="J450" s="10"/>
-      <c r="K450" s="8"/>
+      <c r="I450" s="8"/>
+      <c r="J450" s="8"/>
+      <c r="K450" s="9"/>
       <c r="L450" s="8"/>
+      <c r="M450" s="8"/>
     </row>
     <row r="451">
       <c r="A451" s="8"/>
@@ -6635,10 +7087,11 @@
       <c r="F451" s="8"/>
       <c r="G451" s="8"/>
       <c r="H451" s="8"/>
-      <c r="I451" s="9"/>
-      <c r="J451" s="10"/>
-      <c r="K451" s="8"/>
+      <c r="I451" s="8"/>
+      <c r="J451" s="8"/>
+      <c r="K451" s="9"/>
       <c r="L451" s="8"/>
+      <c r="M451" s="8"/>
     </row>
     <row r="452">
       <c r="A452" s="8"/>
@@ -6649,10 +7102,11 @@
       <c r="F452" s="8"/>
       <c r="G452" s="8"/>
       <c r="H452" s="8"/>
-      <c r="I452" s="9"/>
-      <c r="J452" s="10"/>
-      <c r="K452" s="8"/>
+      <c r="I452" s="8"/>
+      <c r="J452" s="8"/>
+      <c r="K452" s="9"/>
       <c r="L452" s="8"/>
+      <c r="M452" s="8"/>
     </row>
     <row r="453">
       <c r="A453" s="8"/>
@@ -6663,10 +7117,11 @@
       <c r="F453" s="8"/>
       <c r="G453" s="8"/>
       <c r="H453" s="8"/>
-      <c r="I453" s="9"/>
-      <c r="J453" s="10"/>
-      <c r="K453" s="8"/>
+      <c r="I453" s="8"/>
+      <c r="J453" s="8"/>
+      <c r="K453" s="9"/>
       <c r="L453" s="8"/>
+      <c r="M453" s="8"/>
     </row>
     <row r="454">
       <c r="A454" s="8"/>
@@ -6677,10 +7132,11 @@
       <c r="F454" s="8"/>
       <c r="G454" s="8"/>
       <c r="H454" s="8"/>
-      <c r="I454" s="9"/>
-      <c r="J454" s="10"/>
-      <c r="K454" s="8"/>
+      <c r="I454" s="8"/>
+      <c r="J454" s="8"/>
+      <c r="K454" s="9"/>
       <c r="L454" s="8"/>
+      <c r="M454" s="8"/>
     </row>
     <row r="455">
       <c r="A455" s="8"/>
@@ -6691,10 +7147,11 @@
       <c r="F455" s="8"/>
       <c r="G455" s="8"/>
       <c r="H455" s="8"/>
-      <c r="I455" s="9"/>
-      <c r="J455" s="10"/>
-      <c r="K455" s="8"/>
+      <c r="I455" s="8"/>
+      <c r="J455" s="8"/>
+      <c r="K455" s="9"/>
       <c r="L455" s="8"/>
+      <c r="M455" s="8"/>
     </row>
     <row r="456">
       <c r="A456" s="8"/>
@@ -6705,10 +7162,11 @@
       <c r="F456" s="8"/>
       <c r="G456" s="8"/>
       <c r="H456" s="8"/>
-      <c r="I456" s="9"/>
-      <c r="J456" s="10"/>
-      <c r="K456" s="8"/>
+      <c r="I456" s="8"/>
+      <c r="J456" s="8"/>
+      <c r="K456" s="9"/>
       <c r="L456" s="8"/>
+      <c r="M456" s="8"/>
     </row>
     <row r="457">
       <c r="A457" s="8"/>
@@ -6719,10 +7177,11 @@
       <c r="F457" s="8"/>
       <c r="G457" s="8"/>
       <c r="H457" s="8"/>
-      <c r="I457" s="9"/>
-      <c r="J457" s="10"/>
-      <c r="K457" s="8"/>
+      <c r="I457" s="8"/>
+      <c r="J457" s="8"/>
+      <c r="K457" s="9"/>
       <c r="L457" s="8"/>
+      <c r="M457" s="8"/>
     </row>
     <row r="458">
       <c r="A458" s="8"/>
@@ -6733,10 +7192,11 @@
       <c r="F458" s="8"/>
       <c r="G458" s="8"/>
       <c r="H458" s="8"/>
-      <c r="I458" s="9"/>
-      <c r="J458" s="10"/>
-      <c r="K458" s="8"/>
+      <c r="I458" s="8"/>
+      <c r="J458" s="8"/>
+      <c r="K458" s="9"/>
       <c r="L458" s="8"/>
+      <c r="M458" s="8"/>
     </row>
     <row r="459">
       <c r="A459" s="8"/>
@@ -6747,10 +7207,11 @@
       <c r="F459" s="8"/>
       <c r="G459" s="8"/>
       <c r="H459" s="8"/>
-      <c r="I459" s="9"/>
-      <c r="J459" s="10"/>
-      <c r="K459" s="8"/>
+      <c r="I459" s="8"/>
+      <c r="J459" s="8"/>
+      <c r="K459" s="9"/>
       <c r="L459" s="8"/>
+      <c r="M459" s="8"/>
     </row>
     <row r="460">
       <c r="A460" s="8"/>
@@ -6761,10 +7222,11 @@
       <c r="F460" s="8"/>
       <c r="G460" s="8"/>
       <c r="H460" s="8"/>
-      <c r="I460" s="9"/>
-      <c r="J460" s="10"/>
-      <c r="K460" s="8"/>
+      <c r="I460" s="8"/>
+      <c r="J460" s="8"/>
+      <c r="K460" s="9"/>
       <c r="L460" s="8"/>
+      <c r="M460" s="8"/>
     </row>
     <row r="461">
       <c r="A461" s="8"/>
@@ -6775,10 +7237,11 @@
       <c r="F461" s="8"/>
       <c r="G461" s="8"/>
       <c r="H461" s="8"/>
-      <c r="I461" s="9"/>
-      <c r="J461" s="10"/>
-      <c r="K461" s="8"/>
+      <c r="I461" s="8"/>
+      <c r="J461" s="8"/>
+      <c r="K461" s="9"/>
       <c r="L461" s="8"/>
+      <c r="M461" s="8"/>
     </row>
     <row r="462">
       <c r="A462" s="8"/>
@@ -6789,10 +7252,11 @@
       <c r="F462" s="8"/>
       <c r="G462" s="8"/>
       <c r="H462" s="8"/>
-      <c r="I462" s="9"/>
-      <c r="J462" s="10"/>
-      <c r="K462" s="8"/>
+      <c r="I462" s="8"/>
+      <c r="J462" s="8"/>
+      <c r="K462" s="9"/>
       <c r="L462" s="8"/>
+      <c r="M462" s="8"/>
     </row>
     <row r="463">
       <c r="A463" s="8"/>
@@ -6803,10 +7267,11 @@
       <c r="F463" s="8"/>
       <c r="G463" s="8"/>
       <c r="H463" s="8"/>
-      <c r="I463" s="9"/>
-      <c r="J463" s="10"/>
-      <c r="K463" s="8"/>
+      <c r="I463" s="8"/>
+      <c r="J463" s="8"/>
+      <c r="K463" s="9"/>
       <c r="L463" s="8"/>
+      <c r="M463" s="8"/>
     </row>
     <row r="464">
       <c r="A464" s="8"/>
@@ -6817,10 +7282,11 @@
       <c r="F464" s="8"/>
       <c r="G464" s="8"/>
       <c r="H464" s="8"/>
-      <c r="I464" s="9"/>
-      <c r="J464" s="10"/>
-      <c r="K464" s="8"/>
+      <c r="I464" s="8"/>
+      <c r="J464" s="8"/>
+      <c r="K464" s="9"/>
       <c r="L464" s="8"/>
+      <c r="M464" s="8"/>
     </row>
     <row r="465">
       <c r="A465" s="8"/>
@@ -6831,10 +7297,11 @@
       <c r="F465" s="8"/>
       <c r="G465" s="8"/>
       <c r="H465" s="8"/>
-      <c r="I465" s="9"/>
-      <c r="J465" s="10"/>
-      <c r="K465" s="8"/>
+      <c r="I465" s="8"/>
+      <c r="J465" s="8"/>
+      <c r="K465" s="9"/>
       <c r="L465" s="8"/>
+      <c r="M465" s="8"/>
     </row>
     <row r="466">
       <c r="A466" s="8"/>
@@ -6845,10 +7312,11 @@
       <c r="F466" s="8"/>
       <c r="G466" s="8"/>
       <c r="H466" s="8"/>
-      <c r="I466" s="9"/>
-      <c r="J466" s="10"/>
-      <c r="K466" s="8"/>
+      <c r="I466" s="8"/>
+      <c r="J466" s="8"/>
+      <c r="K466" s="9"/>
       <c r="L466" s="8"/>
+      <c r="M466" s="8"/>
     </row>
     <row r="467">
       <c r="A467" s="8"/>
@@ -6859,10 +7327,11 @@
       <c r="F467" s="8"/>
       <c r="G467" s="8"/>
       <c r="H467" s="8"/>
-      <c r="I467" s="9"/>
-      <c r="J467" s="10"/>
-      <c r="K467" s="8"/>
+      <c r="I467" s="8"/>
+      <c r="J467" s="8"/>
+      <c r="K467" s="9"/>
       <c r="L467" s="8"/>
+      <c r="M467" s="8"/>
     </row>
     <row r="468">
       <c r="A468" s="8"/>
@@ -6873,10 +7342,11 @@
       <c r="F468" s="8"/>
       <c r="G468" s="8"/>
       <c r="H468" s="8"/>
-      <c r="I468" s="9"/>
-      <c r="J468" s="10"/>
-      <c r="K468" s="8"/>
+      <c r="I468" s="8"/>
+      <c r="J468" s="8"/>
+      <c r="K468" s="9"/>
       <c r="L468" s="8"/>
+      <c r="M468" s="8"/>
     </row>
     <row r="469">
       <c r="A469" s="8"/>
@@ -6887,10 +7357,11 @@
       <c r="F469" s="8"/>
       <c r="G469" s="8"/>
       <c r="H469" s="8"/>
-      <c r="I469" s="9"/>
-      <c r="J469" s="10"/>
-      <c r="K469" s="8"/>
+      <c r="I469" s="8"/>
+      <c r="J469" s="8"/>
+      <c r="K469" s="9"/>
       <c r="L469" s="8"/>
+      <c r="M469" s="8"/>
     </row>
     <row r="470">
       <c r="A470" s="8"/>
@@ -6901,10 +7372,11 @@
       <c r="F470" s="8"/>
       <c r="G470" s="8"/>
       <c r="H470" s="8"/>
-      <c r="I470" s="9"/>
-      <c r="J470" s="10"/>
-      <c r="K470" s="8"/>
+      <c r="I470" s="8"/>
+      <c r="J470" s="8"/>
+      <c r="K470" s="9"/>
       <c r="L470" s="8"/>
+      <c r="M470" s="8"/>
     </row>
     <row r="471">
       <c r="A471" s="8"/>
@@ -6915,10 +7387,11 @@
       <c r="F471" s="8"/>
       <c r="G471" s="8"/>
       <c r="H471" s="8"/>
-      <c r="I471" s="9"/>
-      <c r="J471" s="10"/>
-      <c r="K471" s="8"/>
+      <c r="I471" s="8"/>
+      <c r="J471" s="8"/>
+      <c r="K471" s="9"/>
       <c r="L471" s="8"/>
+      <c r="M471" s="8"/>
     </row>
     <row r="472">
       <c r="A472" s="8"/>
@@ -6929,10 +7402,11 @@
       <c r="F472" s="8"/>
       <c r="G472" s="8"/>
       <c r="H472" s="8"/>
-      <c r="I472" s="9"/>
-      <c r="J472" s="10"/>
-      <c r="K472" s="8"/>
+      <c r="I472" s="8"/>
+      <c r="J472" s="8"/>
+      <c r="K472" s="9"/>
       <c r="L472" s="8"/>
+      <c r="M472" s="8"/>
     </row>
     <row r="473">
       <c r="A473" s="8"/>
@@ -6943,10 +7417,11 @@
       <c r="F473" s="8"/>
       <c r="G473" s="8"/>
       <c r="H473" s="8"/>
-      <c r="I473" s="9"/>
-      <c r="J473" s="10"/>
-      <c r="K473" s="8"/>
+      <c r="I473" s="8"/>
+      <c r="J473" s="8"/>
+      <c r="K473" s="9"/>
       <c r="L473" s="8"/>
+      <c r="M473" s="8"/>
     </row>
     <row r="474">
       <c r="A474" s="8"/>
@@ -6957,10 +7432,11 @@
       <c r="F474" s="8"/>
       <c r="G474" s="8"/>
       <c r="H474" s="8"/>
-      <c r="I474" s="9"/>
-      <c r="J474" s="10"/>
-      <c r="K474" s="8"/>
+      <c r="I474" s="8"/>
+      <c r="J474" s="8"/>
+      <c r="K474" s="9"/>
       <c r="L474" s="8"/>
+      <c r="M474" s="8"/>
     </row>
     <row r="475">
       <c r="A475" s="8"/>
@@ -6971,10 +7447,11 @@
       <c r="F475" s="8"/>
       <c r="G475" s="8"/>
       <c r="H475" s="8"/>
-      <c r="I475" s="9"/>
-      <c r="J475" s="10"/>
-      <c r="K475" s="8"/>
+      <c r="I475" s="8"/>
+      <c r="J475" s="8"/>
+      <c r="K475" s="9"/>
       <c r="L475" s="8"/>
+      <c r="M475" s="8"/>
     </row>
     <row r="476">
       <c r="A476" s="8"/>
@@ -6985,10 +7462,11 @@
       <c r="F476" s="8"/>
       <c r="G476" s="8"/>
       <c r="H476" s="8"/>
-      <c r="I476" s="9"/>
-      <c r="J476" s="10"/>
-      <c r="K476" s="8"/>
+      <c r="I476" s="8"/>
+      <c r="J476" s="8"/>
+      <c r="K476" s="9"/>
       <c r="L476" s="8"/>
+      <c r="M476" s="8"/>
     </row>
     <row r="477">
       <c r="A477" s="8"/>
@@ -6999,10 +7477,11 @@
       <c r="F477" s="8"/>
       <c r="G477" s="8"/>
       <c r="H477" s="8"/>
-      <c r="I477" s="9"/>
-      <c r="J477" s="10"/>
-      <c r="K477" s="8"/>
+      <c r="I477" s="8"/>
+      <c r="J477" s="8"/>
+      <c r="K477" s="9"/>
       <c r="L477" s="8"/>
+      <c r="M477" s="8"/>
     </row>
     <row r="478">
       <c r="A478" s="8"/>
@@ -7013,10 +7492,11 @@
       <c r="F478" s="8"/>
       <c r="G478" s="8"/>
       <c r="H478" s="8"/>
-      <c r="I478" s="9"/>
-      <c r="J478" s="10"/>
-      <c r="K478" s="8"/>
+      <c r="I478" s="8"/>
+      <c r="J478" s="8"/>
+      <c r="K478" s="9"/>
       <c r="L478" s="8"/>
+      <c r="M478" s="8"/>
     </row>
     <row r="479">
       <c r="A479" s="8"/>
@@ -7027,10 +7507,11 @@
       <c r="F479" s="8"/>
       <c r="G479" s="8"/>
       <c r="H479" s="8"/>
-      <c r="I479" s="9"/>
-      <c r="J479" s="10"/>
-      <c r="K479" s="8"/>
+      <c r="I479" s="8"/>
+      <c r="J479" s="8"/>
+      <c r="K479" s="9"/>
       <c r="L479" s="8"/>
+      <c r="M479" s="8"/>
     </row>
     <row r="480">
       <c r="A480" s="8"/>
@@ -7041,10 +7522,11 @@
       <c r="F480" s="8"/>
       <c r="G480" s="8"/>
       <c r="H480" s="8"/>
-      <c r="I480" s="9"/>
-      <c r="J480" s="10"/>
-      <c r="K480" s="8"/>
+      <c r="I480" s="8"/>
+      <c r="J480" s="8"/>
+      <c r="K480" s="9"/>
       <c r="L480" s="8"/>
+      <c r="M480" s="8"/>
     </row>
     <row r="481">
       <c r="A481" s="8"/>
@@ -7055,10 +7537,11 @@
       <c r="F481" s="8"/>
       <c r="G481" s="8"/>
       <c r="H481" s="8"/>
-      <c r="I481" s="9"/>
-      <c r="J481" s="10"/>
-      <c r="K481" s="8"/>
+      <c r="I481" s="8"/>
+      <c r="J481" s="8"/>
+      <c r="K481" s="9"/>
       <c r="L481" s="8"/>
+      <c r="M481" s="8"/>
     </row>
     <row r="482">
       <c r="A482" s="8"/>
@@ -7069,10 +7552,11 @@
       <c r="F482" s="8"/>
       <c r="G482" s="8"/>
       <c r="H482" s="8"/>
-      <c r="I482" s="9"/>
-      <c r="J482" s="10"/>
-      <c r="K482" s="8"/>
+      <c r="I482" s="8"/>
+      <c r="J482" s="8"/>
+      <c r="K482" s="9"/>
       <c r="L482" s="8"/>
+      <c r="M482" s="8"/>
     </row>
     <row r="483">
       <c r="A483" s="8"/>
@@ -7083,10 +7567,11 @@
       <c r="F483" s="8"/>
       <c r="G483" s="8"/>
       <c r="H483" s="8"/>
-      <c r="I483" s="9"/>
-      <c r="J483" s="10"/>
-      <c r="K483" s="8"/>
+      <c r="I483" s="8"/>
+      <c r="J483" s="8"/>
+      <c r="K483" s="9"/>
       <c r="L483" s="8"/>
+      <c r="M483" s="8"/>
     </row>
     <row r="484">
       <c r="A484" s="8"/>
@@ -7097,10 +7582,11 @@
       <c r="F484" s="8"/>
       <c r="G484" s="8"/>
       <c r="H484" s="8"/>
-      <c r="I484" s="9"/>
-      <c r="J484" s="10"/>
-      <c r="K484" s="8"/>
+      <c r="I484" s="8"/>
+      <c r="J484" s="8"/>
+      <c r="K484" s="9"/>
       <c r="L484" s="8"/>
+      <c r="M484" s="8"/>
     </row>
     <row r="485">
       <c r="A485" s="8"/>
@@ -7111,10 +7597,11 @@
       <c r="F485" s="8"/>
       <c r="G485" s="8"/>
       <c r="H485" s="8"/>
-      <c r="I485" s="9"/>
-      <c r="J485" s="10"/>
-      <c r="K485" s="8"/>
+      <c r="I485" s="8"/>
+      <c r="J485" s="8"/>
+      <c r="K485" s="9"/>
       <c r="L485" s="8"/>
+      <c r="M485" s="8"/>
     </row>
     <row r="486">
       <c r="A486" s="8"/>
@@ -7125,10 +7612,11 @@
       <c r="F486" s="8"/>
       <c r="G486" s="8"/>
       <c r="H486" s="8"/>
-      <c r="I486" s="9"/>
-      <c r="J486" s="10"/>
-      <c r="K486" s="8"/>
+      <c r="I486" s="8"/>
+      <c r="J486" s="8"/>
+      <c r="K486" s="9"/>
       <c r="L486" s="8"/>
+      <c r="M486" s="8"/>
     </row>
     <row r="487">
       <c r="A487" s="8"/>
@@ -7139,10 +7627,11 @@
       <c r="F487" s="8"/>
       <c r="G487" s="8"/>
       <c r="H487" s="8"/>
-      <c r="I487" s="9"/>
-      <c r="J487" s="10"/>
-      <c r="K487" s="8"/>
+      <c r="I487" s="8"/>
+      <c r="J487" s="8"/>
+      <c r="K487" s="9"/>
       <c r="L487" s="8"/>
+      <c r="M487" s="8"/>
     </row>
     <row r="488">
       <c r="A488" s="8"/>
@@ -7153,10 +7642,11 @@
       <c r="F488" s="8"/>
       <c r="G488" s="8"/>
       <c r="H488" s="8"/>
-      <c r="I488" s="9"/>
-      <c r="J488" s="10"/>
-      <c r="K488" s="8"/>
+      <c r="I488" s="8"/>
+      <c r="J488" s="8"/>
+      <c r="K488" s="9"/>
       <c r="L488" s="8"/>
+      <c r="M488" s="8"/>
     </row>
     <row r="489">
       <c r="A489" s="8"/>
@@ -7167,10 +7657,11 @@
       <c r="F489" s="8"/>
       <c r="G489" s="8"/>
       <c r="H489" s="8"/>
-      <c r="I489" s="9"/>
-      <c r="J489" s="10"/>
-      <c r="K489" s="8"/>
+      <c r="I489" s="8"/>
+      <c r="J489" s="8"/>
+      <c r="K489" s="9"/>
       <c r="L489" s="8"/>
+      <c r="M489" s="8"/>
     </row>
     <row r="490">
       <c r="A490" s="8"/>
@@ -7181,10 +7672,11 @@
       <c r="F490" s="8"/>
       <c r="G490" s="8"/>
       <c r="H490" s="8"/>
-      <c r="I490" s="9"/>
-      <c r="J490" s="10"/>
-      <c r="K490" s="8"/>
+      <c r="I490" s="8"/>
+      <c r="J490" s="8"/>
+      <c r="K490" s="9"/>
       <c r="L490" s="8"/>
+      <c r="M490" s="8"/>
     </row>
     <row r="491">
       <c r="A491" s="8"/>
@@ -7195,10 +7687,11 @@
       <c r="F491" s="8"/>
       <c r="G491" s="8"/>
       <c r="H491" s="8"/>
-      <c r="I491" s="9"/>
-      <c r="J491" s="10"/>
-      <c r="K491" s="8"/>
+      <c r="I491" s="8"/>
+      <c r="J491" s="8"/>
+      <c r="K491" s="9"/>
       <c r="L491" s="8"/>
+      <c r="M491" s="8"/>
     </row>
     <row r="492">
       <c r="A492" s="8"/>
@@ -7209,10 +7702,11 @@
       <c r="F492" s="8"/>
       <c r="G492" s="8"/>
       <c r="H492" s="8"/>
-      <c r="I492" s="9"/>
-      <c r="J492" s="10"/>
-      <c r="K492" s="8"/>
+      <c r="I492" s="8"/>
+      <c r="J492" s="8"/>
+      <c r="K492" s="9"/>
       <c r="L492" s="8"/>
+      <c r="M492" s="8"/>
     </row>
     <row r="493">
       <c r="A493" s="8"/>
@@ -7223,10 +7717,11 @@
       <c r="F493" s="8"/>
       <c r="G493" s="8"/>
       <c r="H493" s="8"/>
-      <c r="I493" s="9"/>
-      <c r="J493" s="10"/>
-      <c r="K493" s="8"/>
+      <c r="I493" s="8"/>
+      <c r="J493" s="8"/>
+      <c r="K493" s="9"/>
       <c r="L493" s="8"/>
+      <c r="M493" s="8"/>
     </row>
     <row r="494">
       <c r="A494" s="8"/>
@@ -7237,10 +7732,11 @@
       <c r="F494" s="8"/>
       <c r="G494" s="8"/>
       <c r="H494" s="8"/>
-      <c r="I494" s="9"/>
-      <c r="J494" s="10"/>
-      <c r="K494" s="8"/>
+      <c r="I494" s="8"/>
+      <c r="J494" s="8"/>
+      <c r="K494" s="9"/>
       <c r="L494" s="8"/>
+      <c r="M494" s="8"/>
     </row>
     <row r="495">
       <c r="A495" s="8"/>
@@ -7251,10 +7747,11 @@
       <c r="F495" s="8"/>
       <c r="G495" s="8"/>
       <c r="H495" s="8"/>
-      <c r="I495" s="9"/>
-      <c r="J495" s="10"/>
-      <c r="K495" s="8"/>
+      <c r="I495" s="8"/>
+      <c r="J495" s="8"/>
+      <c r="K495" s="9"/>
       <c r="L495" s="8"/>
+      <c r="M495" s="8"/>
     </row>
     <row r="496">
       <c r="A496" s="8"/>
@@ -7265,10 +7762,11 @@
       <c r="F496" s="8"/>
       <c r="G496" s="8"/>
       <c r="H496" s="8"/>
-      <c r="I496" s="9"/>
-      <c r="J496" s="10"/>
-      <c r="K496" s="8"/>
+      <c r="I496" s="8"/>
+      <c r="J496" s="8"/>
+      <c r="K496" s="9"/>
       <c r="L496" s="8"/>
+      <c r="M496" s="8"/>
     </row>
     <row r="497">
       <c r="A497" s="8"/>
@@ -7279,10 +7777,11 @@
       <c r="F497" s="8"/>
       <c r="G497" s="8"/>
       <c r="H497" s="8"/>
-      <c r="I497" s="9"/>
-      <c r="J497" s="10"/>
-      <c r="K497" s="8"/>
+      <c r="I497" s="8"/>
+      <c r="J497" s="8"/>
+      <c r="K497" s="9"/>
       <c r="L497" s="8"/>
+      <c r="M497" s="8"/>
     </row>
     <row r="498">
       <c r="A498" s="8"/>
@@ -7293,10 +7792,11 @@
       <c r="F498" s="8"/>
       <c r="G498" s="8"/>
       <c r="H498" s="8"/>
-      <c r="I498" s="9"/>
-      <c r="J498" s="10"/>
-      <c r="K498" s="8"/>
+      <c r="I498" s="8"/>
+      <c r="J498" s="8"/>
+      <c r="K498" s="9"/>
       <c r="L498" s="8"/>
+      <c r="M498" s="8"/>
     </row>
     <row r="499">
       <c r="A499" s="8"/>
@@ -7307,10 +7807,11 @@
       <c r="F499" s="8"/>
       <c r="G499" s="8"/>
       <c r="H499" s="8"/>
-      <c r="I499" s="9"/>
-      <c r="J499" s="10"/>
-      <c r="K499" s="8"/>
+      <c r="I499" s="8"/>
+      <c r="J499" s="8"/>
+      <c r="K499" s="9"/>
       <c r="L499" s="8"/>
+      <c r="M499" s="8"/>
     </row>
     <row r="500">
       <c r="A500" s="8"/>
@@ -7321,10 +7822,11 @@
       <c r="F500" s="8"/>
       <c r="G500" s="8"/>
       <c r="H500" s="8"/>
-      <c r="I500" s="9"/>
-      <c r="J500" s="10"/>
-      <c r="K500" s="8"/>
+      <c r="I500" s="8"/>
+      <c r="J500" s="8"/>
+      <c r="K500" s="9"/>
       <c r="L500" s="8"/>
+      <c r="M500" s="8"/>
     </row>
     <row r="501">
       <c r="A501" s="8"/>
@@ -7335,10 +7837,11 @@
       <c r="F501" s="8"/>
       <c r="G501" s="8"/>
       <c r="H501" s="8"/>
-      <c r="I501" s="9"/>
-      <c r="J501" s="10"/>
-      <c r="K501" s="8"/>
+      <c r="I501" s="8"/>
+      <c r="J501" s="8"/>
+      <c r="K501" s="9"/>
       <c r="L501" s="8"/>
+      <c r="M501" s="8"/>
     </row>
     <row r="502">
       <c r="A502" s="8"/>
@@ -7349,10 +7852,11 @@
       <c r="F502" s="8"/>
       <c r="G502" s="8"/>
       <c r="H502" s="8"/>
-      <c r="I502" s="9"/>
-      <c r="J502" s="10"/>
-      <c r="K502" s="8"/>
+      <c r="I502" s="8"/>
+      <c r="J502" s="8"/>
+      <c r="K502" s="9"/>
       <c r="L502" s="8"/>
+      <c r="M502" s="8"/>
     </row>
     <row r="503">
       <c r="A503" s="8"/>
@@ -7363,10 +7867,11 @@
       <c r="F503" s="8"/>
       <c r="G503" s="8"/>
       <c r="H503" s="8"/>
-      <c r="I503" s="9"/>
-      <c r="J503" s="10"/>
-      <c r="K503" s="8"/>
+      <c r="I503" s="8"/>
+      <c r="J503" s="8"/>
+      <c r="K503" s="9"/>
       <c r="L503" s="8"/>
+      <c r="M503" s="8"/>
     </row>
     <row r="504">
       <c r="A504" s="8"/>
@@ -7377,39 +7882,40 @@
       <c r="F504" s="8"/>
       <c r="G504" s="8"/>
       <c r="H504" s="8"/>
-      <c r="I504" s="9"/>
-      <c r="J504" s="10"/>
-      <c r="K504" s="8"/>
+      <c r="I504" s="8"/>
+      <c r="J504" s="8"/>
+      <c r="K504" s="9"/>
       <c r="L504" s="8"/>
+      <c r="M504" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L504"/>
+  <autoFilter ref="A4:M504"/>
   <mergeCells count="4">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:L3"/>
+    <mergeCell ref="F3:M3"/>
   </mergeCells>
   <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="warning" promptTitle="Khách hàng" prompt="Khách hàng (tên viết tắt hoặc tên pháp lý)." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị chưa có trong danh sách (vẫn có thể giữ nếu đúng tên/số)." sqref="A5:A504">
-      <formula1>'Danh mục'!$J$2:$J$2</formula1>
+      <formula1>'Danh mục'!$J$2:$J$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Nhóm nghiệp vụ" prompt="Mã nhóm trong Danh mục." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="D5:D504">
-      <formula1>'Danh mục'!$C$2:$C$3</formula1>
+      <formula1>'Danh mục'!$C$2:$C$2</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Tiền tệ" prompt="Mã tiền tệ." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="E5:E504">
       <formula1>'Danh mục'!$E$2:$E$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Mã dịch vụ" prompt="Mỗi khoản ghi một mã dịch vụ; đơn có thêm mã mới thì được cấp thêm số HSDV." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="F5:F504">
-      <formula1>'Danh mục'!$F$2:$F$4</formula1>
+      <formula1>'Danh mục'!$F$2:$F$2</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="warning" promptTitle="Loại phí" prompt="Tên hoặc mã loại phí." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="G5:G504">
-      <formula1>'Danh mục'!$A$2:$A$6</formula1>
+      <formula1>'Danh mục'!$A$2:$A$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="warning" promptTitle="Thuế" prompt="KCT / số % / trống = chưa xác nhận." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="K5:K504">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorStyle="warning" promptTitle="Thuế" prompt="KCT / số % / trống = chưa xác nhận." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="L5:L504">
       <formula1>'Danh mục'!$H$2:$H$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Thu hộ (1/0)" prompt="1 = thu hộ." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="L5:L504">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Chi hộ (1/0)" prompt="1 = chi hộ (mình chi hộ khách, thu lại của khách)." errorTitle="Giá trị chưa có trong danh mục" error="Giá trị này chưa có trong danh mục. Kiểm tra lại chính tả." sqref="M5:M504">
       <formula1>'Danh mục'!$I$2:$I$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -7424,7 +7930,7 @@
     <tabColor rgb="FF12304A"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -7436,62 +7942,62 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">BIỂU MẪU NHẬP HÀNG LOẠT — PO / DOANH THU</t>
         </is>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" ht="8" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">CÁCH SỬ DỤNG</t>
         </is>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Điền dữ liệu vào sheet "Nhập liệu" từ dòng 5 (mỗi dòng một bản ghi/dòng phí). Xóa dữ liệu mẫu nếu bạn sao chép từ sheet "Ví dụ".</t>
         </is>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">2. Trong ứng dụng: menu Nhập hàng loạt → chọn đúng tab → nút "Chọn tệp" và chọn tệp .xlsx này (hoặc copy vùng dữ liệu kể cả dòng tiêu đề rồi dán).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">3. Bấm "Xem trước" để kiểm tra: lỗi được báo đúng dòng, đúng ô. Có lỗi thì sửa tệp và tải lại — hệ thống KHÔNG ghi gì cho đến khi tất cả dòng hợp lệ.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">4. Khi hợp lệ, bấm ghi. Dữ liệu vào trạng thái nháp/chờ duyệt theo đúng quy trình thông thường.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">• Mỗi dòng là một khoản doanh thu của PO; các dòng cùng Khách + Số PO được gom vào một đơn hàng.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">• Sau khi nhập, lập hóa đơn bán từ các khoản phát sinh ở trang đơn (hoặc dùng mẫu Hóa đơn bán để nhập thẳng hóa đơn kèm tự gắn PO).</t>
         </is>
@@ -7499,423 +8005,451 @@
     </row>
     <row r="10" ht="12" customHeight="1"/>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">GIẢI THÍCH TỪNG CỘT</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Cột</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Tên cột</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Bắt buộc</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Kiểu dữ liệu</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Quy tắc / mô tả</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ví dụ</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">A</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Khách hàng</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Có</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ / chọn từ danh sách</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Khách hàng (tên viết tắt hoặc tên pháp lý).</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">ABC</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">B</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Số PO khách</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Có</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Các dòng cùng Khách + Số PO được gom vào MỘT đơn hàng (tạo mới hoặc gắn vào đơn đang mở).</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">PO-123</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">C</t>
         </is>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ngày</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Có</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ngày dd/MM/yyyy</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="E15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">dd/MM/yyyy; phải trong kỳ đang mở.</t>
         </is>
       </c>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">05/10/2026</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">D</t>
         </is>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Nhóm nghiệp vụ</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Có</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ / chọn từ danh sách</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mã nhóm trong Danh mục.</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">G1</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">E</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Tiền tệ</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Có</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ / chọn từ danh sách</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mã tiền tệ.</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">VND</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">F</t>
         </is>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Mã dịch vụ</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Có</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ / chọn từ danh sách</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Mỗi khoản ghi một mã dịch vụ; đơn có thêm mã mới thì được cấp thêm số HSDV.</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">FWD</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">G</t>
         </is>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Loại phí</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C19" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Có</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ / chọn từ danh sách</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Tên hoặc mã loại phí.</t>
         </is>
       </c>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="F19" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Cước vận chuyển</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">H</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Diễn giải</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Có</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nội dung khoản doanh thu.</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Phí dịch vụ hải quan</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">I</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SL container</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SL (số lượng)</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Không</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Số nguyên</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Số nguyên, tùy chọn.</t>
-        </is>
-      </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chữ</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Số lượng (tối đa 3 số lẻ, tùy chọn).</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">J</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Không</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chữ</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đơn giá (tối đa 4 số lẻ, tùy chọn; cần có SL). Có SL + đơn giá thì để trống Số tiền trước thuế: hệ thống tự tính = SL × đơn giá; nếu nhập cả hai phải khớp.</t>
+        </is>
+      </c>
+      <c r="F22" s="17"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Số tiền trước thuế</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Có</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Số tiền</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Chưa gồm thuế GTGT.</t>
         </is>
       </c>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F23" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">3200000</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">K</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Thuế</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Không</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D24" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ / chọn từ danh sách</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E24" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">KCT / số % / trống = chưa xác nhận.</t>
         </is>
       </c>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="F24" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">L</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thu hộ (1/0)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chi hộ (1/0)</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Không</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Chữ / chọn từ danh sách</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 = thu hộ.</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 = chi hộ (mình chi hộ khách, thu lại của khách).</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
@@ -7942,7 +8476,7 @@
     <tabColor rgb="FF2F855A"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -7954,40 +8488,41 @@
     <col min="7" max="7" width="24" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="20" t="inlineStr">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">VÍ DỤ MINH HỌA — sao chép sang sheet "Nhập liệu" rồi sửa lại cho đúng dữ liệu của bạn (đừng giữ nguyên dòng mẫu)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Khách hàng *</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Số PO khách *</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ngày *</t>
         </is>
       </c>
-      <c r="D2" s="21" t="inlineStr">
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nhóm nghiệp vụ *</t>
         </is>
       </c>
-      <c r="E2" s="21" t="inlineStr">
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">Tiền tệ *</t>
         </is>
@@ -8009,140 +8544,147 @@
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">SL container</t>
+          <t xml:space="preserve">SL (số lượng)</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Đơn giá</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Số tiền trước thuế *</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Thuế</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Thu hộ (1/0)</t>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chi hộ (1/0)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">ABC</t>
         </is>
       </c>
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">PO-123</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">05/10/2026</t>
         </is>
       </c>
-      <c r="D3" s="22" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">G1</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">VND</t>
         </is>
       </c>
-      <c r="F3" s="22" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">FWD</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Cước vận chuyển</t>
         </is>
       </c>
-      <c r="H3" s="22" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Cước vận chuyển 2 container</t>
         </is>
       </c>
-      <c r="I3" s="23" t="inlineStr">
+      <c r="I3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="J3" s="23" t="inlineStr">
+      <c r="J3" s="21"/>
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">10000000</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="L3" s="22" t="inlineStr">
+      <c r="M3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">ABC</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">PO-123</t>
         </is>
       </c>
-      <c r="C4" s="22" t="inlineStr">
+      <c r="C4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">05/10/2026</t>
         </is>
       </c>
-      <c r="D4" s="22" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">G1</t>
         </is>
       </c>
-      <c r="E4" s="22" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">VND</t>
         </is>
       </c>
-      <c r="F4" s="22" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">FWD</t>
         </is>
       </c>
-      <c r="G4" s="22" t="inlineStr">
+      <c r="G4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Phí dịch vụ thủ tục hải quan</t>
         </is>
       </c>
-      <c r="H4" s="22" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Phí thủ tục hải quan</t>
         </is>
       </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23" t="inlineStr">
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">1500000</t>
         </is>
       </c>
-      <c r="K4" s="22" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">KCT</t>
         </is>
       </c>
-      <c r="L4" s="22" t="inlineStr">
+      <c r="M4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
@@ -8150,7 +8692,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -8180,250 +8722,222 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Loại phí (tên)</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mã loại phí</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Nhóm nghiệp vụ (mã)</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Tên nhóm</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Tiền tệ</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mã dịch vụ</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Tên dịch vụ</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Thuế</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chi hộ/thu hộ</t>
-        </is>
-      </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="I1" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chi hộ (phải thu lại) / Thu hộ (phải trả lại)</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Khách hàng (đang hoạt động)</t>
         </is>
       </c>
-      <c r="K1" s="15" t="inlineStr">
+      <c r="K1" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Đơn đang mở (số đơn · PO)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Cước vận chuyển</t>
         </is>
       </c>
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">TRUCKING</t>
         </is>
       </c>
-      <c r="C2" s="24" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">G1</t>
         </is>
       </c>
-      <c r="D2" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nhóm 1</t>
-        </is>
-      </c>
-      <c r="E2" s="24" t="inlineStr">
+      <c r="D2" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nhóm 1 (ví dụ)</t>
+        </is>
+      </c>
+      <c r="E2" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">VND</t>
         </is>
       </c>
-      <c r="F2" s="24" t="inlineStr">
+      <c r="F2" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">FWD</t>
         </is>
       </c>
-      <c r="G2" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forwarding</t>
-        </is>
-      </c>
-      <c r="H2" s="24" t="inlineStr">
+      <c r="G2" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forwarding (ví dụ)</t>
+        </is>
+      </c>
+      <c r="H2" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">KCT</t>
         </is>
       </c>
-      <c r="I2" s="24" t="inlineStr">
+      <c r="I2" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="J2" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(tên viết tắt đối tác của bạn)</t>
-        </is>
-      </c>
-      <c r="K2" s="24" t="inlineStr">
+      <c r="J2" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khách hàng A</t>
+        </is>
+      </c>
+      <c r="K2" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">DH-2026-000001</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Phí nâng/hạ container</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">CONT_LIFT</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">G2</t>
-        </is>
-      </c>
-      <c r="D3" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nhóm 2</t>
-        </is>
-      </c>
-      <c r="E3" s="24" t="inlineStr">
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">USD</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CFN</t>
-        </is>
-      </c>
-      <c r="G3" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chuyển phát nhanh</t>
-        </is>
-      </c>
-      <c r="H3" s="24" t="inlineStr">
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="I3" s="24" t="inlineStr">
+      <c r="I3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cảng Cát Lái</t>
+        </is>
+      </c>
+      <c r="K3" s="23"/>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Phí dịch vụ thủ tục hải quan</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">CUSTOMS_SERVICE</t>
         </is>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CBT</t>
-        </is>
-      </c>
-      <c r="G4" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vận tải xuyên biên giới</t>
-        </is>
-      </c>
-      <c r="H4" s="24" t="inlineStr">
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Phí xin giấy phép</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PERMIT</t>
-        </is>
-      </c>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Khác</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OTHER</t>
+        </is>
+      </c>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Khác</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OTHER</t>
-        </is>
-      </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24" t="inlineStr">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
